--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126862651</v>
+        <v>126864745</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700266</v>
+        <v>700325</v>
       </c>
       <c r="R2" t="n">
-        <v>7114350</v>
+        <v>7114161</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126868144</v>
+        <v>126868122</v>
       </c>
       <c r="B3" t="n">
-        <v>97239</v>
+        <v>4772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +787,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700167</v>
+        <v>700332</v>
       </c>
       <c r="R3" t="n">
-        <v>7114511</v>
+        <v>7114038</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -846,7 +851,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -856,7 +861,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,6 +872,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -890,7 +915,7 @@
         <v>126864711</v>
       </c>
       <c r="B4" t="n">
-        <v>96614</v>
+        <v>96689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,45 +1013,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126864745</v>
+        <v>126862651</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700325</v>
+        <v>700266</v>
       </c>
       <c r="R5" t="n">
-        <v>7114161</v>
+        <v>7114350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1098,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1089,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868122</v>
+        <v>126868144</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>97314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,39 +1125,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700332</v>
+        <v>700167</v>
       </c>
       <c r="R6" t="n">
-        <v>7114038</v>
+        <v>7114511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1174,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,26 +1205,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1225,61 +1225,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126864699</v>
+        <v>126862629</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>80074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700344</v>
+        <v>700301</v>
       </c>
       <c r="R7" t="n">
-        <v>7114307</v>
+        <v>7114163</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,19 +1304,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1346,7 +1329,7 @@
         <v>126864750</v>
       </c>
       <c r="B8" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126851272</v>
+        <v>126867871</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,17 +1458,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700310</v>
+        <v>700323</v>
       </c>
       <c r="R9" t="n">
-        <v>7114176</v>
+        <v>7114124</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,19 +1495,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,12 +1512,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1555,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126867871</v>
+        <v>126864701</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,17 +1556,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700323</v>
+        <v>700283</v>
       </c>
       <c r="R10" t="n">
-        <v>7114124</v>
+        <v>7114393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,18 +1619,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1656,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864701</v>
+        <v>126864699</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,7 +1672,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1694,7 +1680,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1703,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700283</v>
+        <v>700344</v>
       </c>
       <c r="R11" t="n">
-        <v>7114393</v>
+        <v>7114307</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,48 +1760,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126862629</v>
+        <v>126851272</v>
       </c>
       <c r="B12" t="n">
-        <v>80043</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700301</v>
+        <v>700310</v>
       </c>
       <c r="R12" t="n">
-        <v>7114163</v>
+        <v>7114176</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,9 +1828,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,12 +1855,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126865575</v>
+        <v>126863311</v>
       </c>
       <c r="B13" t="n">
-        <v>98278</v>
+        <v>92609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1882,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700236</v>
+        <v>700340</v>
       </c>
       <c r="R13" t="n">
-        <v>7114234</v>
+        <v>7114337</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126863301</v>
+        <v>126867862</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,17 +2000,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700307</v>
+        <v>700364</v>
       </c>
       <c r="R14" t="n">
-        <v>7114151</v>
+        <v>7114084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,18 +2063,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2073,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126867862</v>
+        <v>126867869</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,29 +2114,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700364</v>
+        <v>700339</v>
       </c>
       <c r="R15" t="n">
-        <v>7114084</v>
+        <v>7114086</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2165,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2187,32 +2187,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126863311</v>
+        <v>126863301</v>
       </c>
       <c r="B16" t="n">
-        <v>92535</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700340</v>
+        <v>700307</v>
       </c>
       <c r="R16" t="n">
-        <v>7114337</v>
+        <v>7114151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,32 +2288,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126867869</v>
+        <v>126865575</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>98353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700339</v>
+        <v>700236</v>
       </c>
       <c r="R17" t="n">
-        <v>7114086</v>
+        <v>7114234</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,12 +2373,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2389,32 +2389,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868126</v>
+        <v>126868136</v>
       </c>
       <c r="B18" t="n">
-        <v>80083</v>
+        <v>96562</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700245</v>
+        <v>700114</v>
       </c>
       <c r="R18" t="n">
-        <v>7114154</v>
+        <v>7114614</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,21 +2480,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2518,7 +2503,7 @@
         <v>126864725</v>
       </c>
       <c r="B19" t="n">
-        <v>79004</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126868136</v>
+        <v>126865568</v>
       </c>
       <c r="B20" t="n">
-        <v>96487</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700114</v>
+        <v>700363</v>
       </c>
       <c r="R20" t="n">
-        <v>7114614</v>
+        <v>7114098</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2684,19 +2669,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,12 +2686,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2727,32 +2702,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126865568</v>
+        <v>126868126</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>80114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2762,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700363</v>
+        <v>700245</v>
       </c>
       <c r="R21" t="n">
-        <v>7114098</v>
+        <v>7114154</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,11 +2770,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2808,16 +2793,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2828,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126863310</v>
+        <v>126862588</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>91319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700290</v>
+        <v>700304</v>
       </c>
       <c r="R22" t="n">
-        <v>7114136</v>
+        <v>7114192</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,12 +2913,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2929,57 +2929,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126867858</v>
+        <v>126863310</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700318</v>
+        <v>700290</v>
       </c>
       <c r="R23" t="n">
-        <v>7114179</v>
+        <v>7114136</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,19 +3008,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3043,45 +3030,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126862588</v>
+        <v>126867858</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700304</v>
+        <v>700318</v>
       </c>
       <c r="R24" t="n">
-        <v>7114192</v>
+        <v>7114179</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,18 +3121,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3147,7 +3147,7 @@
         <v>126864710</v>
       </c>
       <c r="B25" t="n">
-        <v>96614</v>
+        <v>96689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>126865571</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>126864739</v>
       </c>
       <c r="B28" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,45 +3567,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126864748</v>
+        <v>126862653</v>
       </c>
       <c r="B29" t="n">
-        <v>98278</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700220</v>
+        <v>700319</v>
       </c>
       <c r="R29" t="n">
-        <v>7114448</v>
+        <v>7114336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,12 +3652,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3668,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126865559</v>
+        <v>126868151</v>
       </c>
       <c r="B30" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700330</v>
+        <v>700306</v>
       </c>
       <c r="R30" t="n">
-        <v>7114328</v>
+        <v>7114337</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,9 +3736,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,12 +3763,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3769,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126862653</v>
+        <v>126865559</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,14 +3810,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700319</v>
+        <v>700330</v>
       </c>
       <c r="R31" t="n">
-        <v>7114336</v>
+        <v>7114328</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3854,12 +3864,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3870,32 +3880,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126868151</v>
+        <v>126864748</v>
       </c>
       <c r="B32" t="n">
-        <v>98361</v>
+        <v>98353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700306</v>
+        <v>700220</v>
       </c>
       <c r="R32" t="n">
-        <v>7114337</v>
+        <v>7114448</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3938,19 +3948,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3965,12 +3965,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3981,32 +3981,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126865556</v>
+        <v>126864698</v>
       </c>
       <c r="B33" t="n">
-        <v>98361</v>
+        <v>91319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700304</v>
+        <v>700320</v>
       </c>
       <c r="R33" t="n">
-        <v>7114364</v>
+        <v>7114182</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4082,60 +4082,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126864703</v>
+        <v>126852356</v>
       </c>
       <c r="B34" t="n">
-        <v>98361</v>
+        <v>92609</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700315</v>
+        <v>700344</v>
       </c>
       <c r="R34" t="n">
-        <v>7114347</v>
+        <v>7114301</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4162,30 +4150,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4196,45 +4193,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126862654</v>
+        <v>126864706</v>
       </c>
       <c r="B35" t="n">
-        <v>98361</v>
+        <v>98353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700337</v>
+        <v>700145</v>
       </c>
       <c r="R35" t="n">
-        <v>7114304</v>
+        <v>7114540</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,12 +4278,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4297,45 +4294,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126864698</v>
+        <v>126864703</v>
       </c>
       <c r="B36" t="n">
-        <v>91245</v>
+        <v>98436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700320</v>
+        <v>700315</v>
       </c>
       <c r="R36" t="n">
-        <v>7114182</v>
+        <v>7114347</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4376,6 +4385,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4398,48 +4408,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126852356</v>
+        <v>126865556</v>
       </c>
       <c r="B37" t="n">
-        <v>92535</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700344</v>
+        <v>700304</v>
       </c>
       <c r="R37" t="n">
-        <v>7114301</v>
+        <v>7114364</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4466,19 +4476,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4493,12 +4493,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4509,45 +4509,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126864706</v>
+        <v>126862654</v>
       </c>
       <c r="B38" t="n">
-        <v>98278</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700145</v>
+        <v>700337</v>
       </c>
       <c r="R38" t="n">
-        <v>7114540</v>
+        <v>7114304</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,12 +4594,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4610,32 +4610,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126865569</v>
+        <v>126865563</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700198</v>
+        <v>700297</v>
       </c>
       <c r="R39" t="n">
-        <v>7114523</v>
+        <v>7114112</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,50 +4711,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126868146</v>
+        <v>126864700</v>
       </c>
       <c r="B40" t="n">
-        <v>41361</v>
+        <v>98436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>215713</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700294</v>
+        <v>700265</v>
       </c>
       <c r="R40" t="n">
-        <v>7114336</v>
+        <v>7114403</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,39 +4791,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4827,45 +4825,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126865578</v>
+        <v>126868146</v>
       </c>
       <c r="B41" t="n">
-        <v>98278</v>
+        <v>41361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>215713</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700147</v>
+        <v>700294</v>
       </c>
       <c r="R41" t="n">
-        <v>7114536</v>
+        <v>7114336</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4895,9 +4898,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4912,12 +4925,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4928,32 +4941,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126867882</v>
+        <v>126865578</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4963,10 +4976,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700181</v>
+        <v>700147</v>
       </c>
       <c r="R42" t="n">
-        <v>7114498</v>
+        <v>7114536</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5013,12 +5026,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5029,32 +5042,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126865563</v>
+        <v>126865569</v>
       </c>
       <c r="B43" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5064,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700297</v>
+        <v>700198</v>
       </c>
       <c r="R43" t="n">
-        <v>7114112</v>
+        <v>7114523</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5130,57 +5143,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126864700</v>
+        <v>126867882</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700265</v>
+        <v>700181</v>
       </c>
       <c r="R44" t="n">
-        <v>7114403</v>
+        <v>7114498</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5221,19 +5222,18 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5247,7 +5247,7 @@
         <v>126864733</v>
       </c>
       <c r="B45" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5345,48 +5345,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126864746</v>
+        <v>126854059</v>
       </c>
       <c r="B46" t="n">
-        <v>98278</v>
+        <v>91319</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lappmyran, Lappmyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700240</v>
+        <v>700098</v>
       </c>
       <c r="R46" t="n">
-        <v>7114242</v>
+        <v>7114648</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5413,9 +5413,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5430,12 +5440,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5582,48 +5592,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126854059</v>
+        <v>126864746</v>
       </c>
       <c r="B48" t="n">
-        <v>91245</v>
+        <v>98353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lappmyran, Lappmyran, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700098</v>
+        <v>700240</v>
       </c>
       <c r="R48" t="n">
-        <v>7114648</v>
+        <v>7114242</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5650,19 +5660,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5677,12 +5677,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5794,45 +5794,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126862656</v>
+        <v>126868129</v>
       </c>
       <c r="B50" t="n">
-        <v>98361</v>
+        <v>80150</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700320</v>
+        <v>700245</v>
       </c>
       <c r="R50" t="n">
-        <v>7114171</v>
+        <v>7114154</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5862,11 +5862,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5875,16 +5885,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5895,45 +5920,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126868129</v>
+        <v>126864704</v>
       </c>
       <c r="B51" t="n">
-        <v>80119</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700245</v>
+        <v>700273</v>
       </c>
       <c r="R51" t="n">
-        <v>7114154</v>
+        <v>7114229</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5963,21 +6000,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5986,31 +6013,16 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6021,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126864704</v>
+        <v>126864738</v>
       </c>
       <c r="B52" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6049,29 +6061,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700273</v>
+        <v>700299</v>
       </c>
       <c r="R52" t="n">
-        <v>7114229</v>
+        <v>7114327</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6134,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126865558</v>
+        <v>126864734</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,17 +6162,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700326</v>
+        <v>700263</v>
       </c>
       <c r="R53" t="n">
-        <v>7114352</v>
+        <v>7114387</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6224,7 +6228,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6235,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126864734</v>
+        <v>126865558</v>
       </c>
       <c r="B54" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,21 +6267,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700263</v>
+        <v>700326</v>
       </c>
       <c r="R54" t="n">
-        <v>7114387</v>
+        <v>7114352</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6340,10 +6340,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126864738</v>
+        <v>126862656</v>
       </c>
       <c r="B55" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6371,14 +6371,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700299</v>
+        <v>700320</v>
       </c>
       <c r="R55" t="n">
-        <v>7114327</v>
+        <v>7114171</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6425,12 +6425,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6441,45 +6441,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126865564</v>
+        <v>126864680</v>
       </c>
       <c r="B56" t="n">
-        <v>98361</v>
+        <v>80114</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700282</v>
+        <v>700363</v>
       </c>
       <c r="R56" t="n">
-        <v>7114135</v>
+        <v>7114127</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6526,12 +6526,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6542,45 +6542,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126864680</v>
+        <v>126864708</v>
       </c>
       <c r="B57" t="n">
-        <v>80083</v>
+        <v>92609</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700363</v>
+        <v>700253</v>
       </c>
       <c r="R57" t="n">
-        <v>7114127</v>
+        <v>7114409</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6627,12 +6627,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6646,7 +6646,7 @@
         <v>126865567</v>
       </c>
       <c r="B58" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126863304</v>
+        <v>126865564</v>
       </c>
       <c r="B59" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6775,14 +6775,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700323</v>
+        <v>700282</v>
       </c>
       <c r="R59" t="n">
-        <v>7114164</v>
+        <v>7114135</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6829,12 +6829,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6845,10 +6845,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126862657</v>
+        <v>126863304</v>
       </c>
       <c r="B60" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700359</v>
+        <v>700323</v>
       </c>
       <c r="R60" t="n">
-        <v>7114097</v>
+        <v>7114164</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6930,12 +6930,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6946,45 +6946,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126864708</v>
+        <v>126862657</v>
       </c>
       <c r="B61" t="n">
-        <v>92535</v>
+        <v>98436</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700253</v>
+        <v>700359</v>
       </c>
       <c r="R61" t="n">
-        <v>7114409</v>
+        <v>7114097</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7031,12 +7031,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7047,45 +7047,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126864687</v>
+        <v>126864719</v>
       </c>
       <c r="B62" t="n">
-        <v>82792</v>
+        <v>98457</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700348</v>
+        <v>700137</v>
       </c>
       <c r="R62" t="n">
-        <v>7114044</v>
+        <v>7114498</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7126,19 +7126,18 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7149,45 +7148,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126864724</v>
+        <v>126864687</v>
       </c>
       <c r="B63" t="n">
-        <v>79004</v>
+        <v>82852</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700243</v>
+        <v>700348</v>
       </c>
       <c r="R63" t="n">
-        <v>7114142</v>
+        <v>7114044</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7228,18 +7227,19 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7250,10 +7250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126864719</v>
+        <v>126864724</v>
       </c>
       <c r="B64" t="n">
-        <v>98382</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7261,21 +7261,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6434</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700137</v>
+        <v>700243</v>
       </c>
       <c r="R64" t="n">
-        <v>7114498</v>
+        <v>7114142</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7354,7 +7354,7 @@
         <v>126864713</v>
       </c>
       <c r="B65" t="n">
-        <v>91603</v>
+        <v>91677</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7456,45 +7456,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126864683</v>
+        <v>126864720</v>
       </c>
       <c r="B66" t="n">
-        <v>98361</v>
+        <v>80018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700345</v>
+        <v>700382</v>
       </c>
       <c r="R66" t="n">
-        <v>7114314</v>
+        <v>7114108</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7529,11 +7529,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7546,12 +7541,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7562,48 +7557,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126864720</v>
+        <v>126851658</v>
       </c>
       <c r="B67" t="n">
-        <v>79987</v>
+        <v>80114</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700382</v>
+        <v>700243</v>
       </c>
       <c r="R67" t="n">
-        <v>7114108</v>
+        <v>7114171</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7630,9 +7625,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7647,12 +7652,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7663,10 +7668,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126862630</v>
+        <v>126864683</v>
       </c>
       <c r="B68" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7698,10 +7703,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700326</v>
+        <v>700345</v>
       </c>
       <c r="R68" t="n">
-        <v>7114161</v>
+        <v>7114314</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7736,25 +7741,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7768,7 +7777,7 @@
         <v>126864736</v>
       </c>
       <c r="B69" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7871,48 +7880,60 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126851658</v>
+        <v>126864702</v>
       </c>
       <c r="B70" t="n">
-        <v>80083</v>
+        <v>98436</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700243</v>
+        <v>700301</v>
       </c>
       <c r="R70" t="n">
-        <v>7114171</v>
+        <v>7114357</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7939,39 +7960,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7982,10 +7994,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126864702</v>
+        <v>126862630</v>
       </c>
       <c r="B71" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8010,29 +8022,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700301</v>
+        <v>700326</v>
       </c>
       <c r="R71" t="n">
-        <v>7114357</v>
+        <v>7114161</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8080,12 +8080,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8096,32 +8096,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126865566</v>
+        <v>126865572</v>
       </c>
       <c r="B72" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700281</v>
+        <v>700229</v>
       </c>
       <c r="R72" t="n">
-        <v>7114184</v>
+        <v>7114231</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, Elke Blöhbaum, Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8197,10 +8197,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126867860</v>
+        <v>126865566</v>
       </c>
       <c r="B73" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8225,29 +8225,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700311</v>
+        <v>700281</v>
       </c>
       <c r="R73" t="n">
-        <v>7114124</v>
+        <v>7114184</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8288,19 +8276,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8311,45 +8298,57 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126865572</v>
+        <v>126867860</v>
       </c>
       <c r="B74" t="n">
-        <v>78980</v>
+        <v>98436</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700229</v>
+        <v>700311</v>
       </c>
       <c r="R74" t="n">
-        <v>7114231</v>
+        <v>7114124</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8390,18 +8389,19 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8415,7 +8415,7 @@
         <v>126868139</v>
       </c>
       <c r="B75" t="n">
-        <v>96487</v>
+        <v>96562</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>126865557</v>
       </c>
       <c r="B76" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>126865562</v>
       </c>
       <c r="B77" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8725,48 +8725,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126867872</v>
+        <v>126856511</v>
       </c>
       <c r="B78" t="n">
-        <v>98361</v>
+        <v>79011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700320</v>
+        <v>700252</v>
       </c>
       <c r="R78" t="n">
-        <v>7114336</v>
+        <v>7114157</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8793,9 +8793,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8810,12 +8820,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8826,48 +8836,56 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126856511</v>
+        <v>126864729</v>
       </c>
       <c r="B79" t="n">
-        <v>78980</v>
+        <v>58027</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700252</v>
+        <v>700152</v>
       </c>
       <c r="R79" t="n">
-        <v>7114157</v>
+        <v>7114491</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8894,19 +8912,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8921,12 +8929,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8940,7 +8948,7 @@
         <v>126864737</v>
       </c>
       <c r="B80" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9038,10 +9046,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126867870</v>
+        <v>126867872</v>
       </c>
       <c r="B81" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9073,10 +9081,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700316</v>
+        <v>700320</v>
       </c>
       <c r="R81" t="n">
-        <v>7114065</v>
+        <v>7114336</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9139,10 +9147,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126864741</v>
+        <v>126867870</v>
       </c>
       <c r="B82" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9167,21 +9175,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700313</v>
+        <v>700316</v>
       </c>
       <c r="R82" t="n">
-        <v>7114166</v>
+        <v>7114065</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9228,12 +9232,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9244,53 +9248,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126864729</v>
+        <v>126864741</v>
       </c>
       <c r="B83" t="n">
-        <v>58027</v>
+        <v>98436</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700152</v>
+        <v>700313</v>
       </c>
       <c r="R83" t="n">
-        <v>7114491</v>
+        <v>7114166</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9356,7 +9356,7 @@
         <v>126862652</v>
       </c>
       <c r="B84" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126864745</v>
+        <v>126864711</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>96695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700325</v>
+        <v>700315</v>
       </c>
       <c r="R2" t="n">
-        <v>7114161</v>
+        <v>7114081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,50 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126868122</v>
+        <v>126864745</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700332</v>
+        <v>700325</v>
       </c>
       <c r="R3" t="n">
-        <v>7114038</v>
+        <v>7114161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,21 +844,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,36 +857,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -912,45 +877,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126864711</v>
+        <v>126868122</v>
       </c>
       <c r="B4" t="n">
-        <v>96689</v>
+        <v>4772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700315</v>
+        <v>700332</v>
       </c>
       <c r="R4" t="n">
-        <v>7114081</v>
+        <v>7114038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,11 +950,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -993,16 +973,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,7 +1016,7 @@
         <v>126862651</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>126868144</v>
       </c>
       <c r="B6" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,48 +1225,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126862629</v>
+        <v>126851272</v>
       </c>
       <c r="B7" t="n">
-        <v>80074</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700301</v>
+        <v>700310</v>
       </c>
       <c r="R7" t="n">
-        <v>7114163</v>
+        <v>7114176</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,9 +1293,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,12 +1320,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1326,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126864750</v>
+        <v>126867871</v>
       </c>
       <c r="B8" t="n">
-        <v>98353</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700151</v>
+        <v>700323</v>
       </c>
       <c r="R8" t="n">
-        <v>7114492</v>
+        <v>7114124</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,12 +1421,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1427,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126867871</v>
+        <v>126864699</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,17 +1465,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700323</v>
+        <v>700344</v>
       </c>
       <c r="R9" t="n">
-        <v>7114124</v>
+        <v>7114307</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,18 +1532,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1531,7 +1558,7 @@
         <v>126864701</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,61 +1669,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864699</v>
+        <v>126864750</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700344</v>
+        <v>700151</v>
       </c>
       <c r="R11" t="n">
-        <v>7114307</v>
+        <v>7114492</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1748,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1749,7 +1759,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1760,48 +1770,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126851272</v>
+        <v>126862629</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>80077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700310</v>
+        <v>700301</v>
       </c>
       <c r="R12" t="n">
-        <v>7114176</v>
+        <v>7114163</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1828,19 +1838,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,12 +1855,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1871,45 +1871,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126863311</v>
+        <v>126867869</v>
       </c>
       <c r="B13" t="n">
-        <v>92609</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700340</v>
+        <v>700339</v>
       </c>
       <c r="R13" t="n">
-        <v>7114337</v>
+        <v>7114086</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126867862</v>
+        <v>126863301</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,29 +2000,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700364</v>
+        <v>700307</v>
       </c>
       <c r="R14" t="n">
-        <v>7114084</v>
+        <v>7114151</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,19 +2051,18 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2086,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126867869</v>
+        <v>126867862</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,17 +2101,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700339</v>
+        <v>700364</v>
       </c>
       <c r="R15" t="n">
-        <v>7114086</v>
+        <v>7114084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,6 +2164,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2187,32 +2187,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126863301</v>
+        <v>126863311</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>92615</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700307</v>
+        <v>700340</v>
       </c>
       <c r="R16" t="n">
-        <v>7114151</v>
+        <v>7114337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2291,7 @@
         <v>126865575</v>
       </c>
       <c r="B17" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,32 +2389,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868136</v>
+        <v>126868126</v>
       </c>
       <c r="B18" t="n">
-        <v>96562</v>
+        <v>80117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700114</v>
+        <v>700245</v>
       </c>
       <c r="R18" t="n">
-        <v>7114614</v>
+        <v>7114154</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,6 +2480,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2503,7 +2518,7 @@
         <v>126864725</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,32 +2616,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126865568</v>
+        <v>126868136</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>96568</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,13 +2651,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700363</v>
+        <v>700114</v>
       </c>
       <c r="R20" t="n">
-        <v>7114098</v>
+        <v>7114614</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2669,9 +2684,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,12 +2711,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2702,32 +2727,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126868126</v>
+        <v>126865568</v>
       </c>
       <c r="B21" t="n">
-        <v>80114</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700245</v>
+        <v>700363</v>
       </c>
       <c r="R21" t="n">
-        <v>7114154</v>
+        <v>7114098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,21 +2795,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2793,31 +2808,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2828,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126862588</v>
+        <v>126863310</v>
       </c>
       <c r="B22" t="n">
-        <v>91319</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700304</v>
+        <v>700290</v>
       </c>
       <c r="R22" t="n">
-        <v>7114192</v>
+        <v>7114136</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,12 +2913,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126863310</v>
+        <v>126862588</v>
       </c>
       <c r="B23" t="n">
-        <v>79011</v>
+        <v>91325</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700290</v>
+        <v>700304</v>
       </c>
       <c r="R23" t="n">
-        <v>7114136</v>
+        <v>7114192</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,12 +3014,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3033,7 +3033,7 @@
         <v>126867858</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>126864710</v>
       </c>
       <c r="B25" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>126865571</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>126864739</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126862653</v>
+        <v>126865559</v>
       </c>
       <c r="B29" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,14 +3598,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700319</v>
+        <v>700330</v>
       </c>
       <c r="R29" t="n">
-        <v>7114336</v>
+        <v>7114328</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,12 +3652,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3668,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126868151</v>
+        <v>126862653</v>
       </c>
       <c r="B30" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,14 +3699,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700306</v>
+        <v>700319</v>
       </c>
       <c r="R30" t="n">
-        <v>7114337</v>
+        <v>7114336</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,19 +3736,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,12 +3753,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3779,10 +3769,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126865559</v>
+        <v>126868151</v>
       </c>
       <c r="B31" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,10 +3804,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700330</v>
+        <v>700306</v>
       </c>
       <c r="R31" t="n">
-        <v>7114328</v>
+        <v>7114337</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3847,9 +3837,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,12 +3864,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3883,7 +3883,7 @@
         <v>126864748</v>
       </c>
       <c r="B32" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>126864698</v>
       </c>
       <c r="B33" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4082,10 +4082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126852356</v>
+        <v>126864706</v>
       </c>
       <c r="B34" t="n">
-        <v>92609</v>
+        <v>98359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4093,37 +4093,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700344</v>
+        <v>700145</v>
       </c>
       <c r="R34" t="n">
-        <v>7114301</v>
+        <v>7114540</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4150,19 +4150,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4177,12 +4167,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4193,10 +4183,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126864706</v>
+        <v>126852356</v>
       </c>
       <c r="B35" t="n">
-        <v>98353</v>
+        <v>92615</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4204,37 +4194,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700145</v>
+        <v>700344</v>
       </c>
       <c r="R35" t="n">
-        <v>7114540</v>
+        <v>7114301</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4261,9 +4251,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,12 +4278,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4297,7 +4297,7 @@
         <v>126864703</v>
       </c>
       <c r="B36" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>126865556</v>
       </c>
       <c r="B37" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>126862654</v>
       </c>
       <c r="B38" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4610,45 +4610,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126865563</v>
+        <v>126868146</v>
       </c>
       <c r="B39" t="n">
-        <v>98436</v>
+        <v>41361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>215713</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700297</v>
+        <v>700294</v>
       </c>
       <c r="R39" t="n">
-        <v>7114112</v>
+        <v>7114336</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,9 +4683,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4695,12 +4710,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4711,10 +4726,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126864700</v>
+        <v>126865563</v>
       </c>
       <c r="B40" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4739,29 +4754,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700265</v>
+        <v>700297</v>
       </c>
       <c r="R40" t="n">
-        <v>7114403</v>
+        <v>7114112</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,7 +4805,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4814,7 +4816,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4825,50 +4827,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126868146</v>
+        <v>126864700</v>
       </c>
       <c r="B41" t="n">
-        <v>41361</v>
+        <v>98442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>215713</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700294</v>
+        <v>700265</v>
       </c>
       <c r="R41" t="n">
-        <v>7114336</v>
+        <v>7114403</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,39 +4907,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4944,7 +4944,7 @@
         <v>126865578</v>
       </c>
       <c r="B42" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126865569</v>
+        <v>126867882</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700198</v>
+        <v>700181</v>
       </c>
       <c r="R43" t="n">
-        <v>7114523</v>
+        <v>7114498</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,12 +5127,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5143,10 +5143,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126867882</v>
+        <v>126865569</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,10 +5178,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700181</v>
+        <v>700198</v>
       </c>
       <c r="R44" t="n">
-        <v>7114498</v>
+        <v>7114523</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5228,12 +5228,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5247,7 +5247,7 @@
         <v>126864733</v>
       </c>
       <c r="B45" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>126854059</v>
       </c>
       <c r="B46" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>126864746</v>
       </c>
       <c r="B48" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5693,45 +5693,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126863285</v>
+        <v>126868129</v>
       </c>
       <c r="B49" t="n">
-        <v>57817</v>
+        <v>80153</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700344</v>
+        <v>700245</v>
       </c>
       <c r="R49" t="n">
-        <v>7114335</v>
+        <v>7114154</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,11 +5761,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5774,16 +5784,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5794,45 +5819,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126868129</v>
+        <v>126863285</v>
       </c>
       <c r="B50" t="n">
-        <v>80150</v>
+        <v>57817</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700245</v>
+        <v>700344</v>
       </c>
       <c r="R50" t="n">
-        <v>7114154</v>
+        <v>7114335</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5862,21 +5887,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5885,31 +5900,16 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5923,7 +5923,7 @@
         <v>126864704</v>
       </c>
       <c r="B51" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6033,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126864738</v>
+        <v>126864734</v>
       </c>
       <c r="B52" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6061,17 +6061,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700299</v>
+        <v>700263</v>
       </c>
       <c r="R52" t="n">
-        <v>7114327</v>
+        <v>7114387</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6134,10 +6138,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126864734</v>
+        <v>126864738</v>
       </c>
       <c r="B53" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,21 +6166,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700263</v>
+        <v>700299</v>
       </c>
       <c r="R53" t="n">
-        <v>7114387</v>
+        <v>7114327</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6242,7 +6242,7 @@
         <v>126865558</v>
       </c>
       <c r="B54" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>126862656</v>
       </c>
       <c r="B55" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6441,45 +6441,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126864680</v>
+        <v>126865564</v>
       </c>
       <c r="B56" t="n">
-        <v>80114</v>
+        <v>98442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700363</v>
+        <v>700282</v>
       </c>
       <c r="R56" t="n">
-        <v>7114127</v>
+        <v>7114135</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6526,12 +6526,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6542,32 +6542,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126864708</v>
+        <v>126865567</v>
       </c>
       <c r="B57" t="n">
-        <v>92609</v>
+        <v>98442</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700253</v>
+        <v>700281</v>
       </c>
       <c r="R57" t="n">
-        <v>7114409</v>
+        <v>7114196</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6643,10 +6643,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126865567</v>
+        <v>126863304</v>
       </c>
       <c r="B58" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6674,14 +6674,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700281</v>
+        <v>700323</v>
       </c>
       <c r="R58" t="n">
-        <v>7114196</v>
+        <v>7114164</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6728,12 +6728,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6744,10 +6744,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126865564</v>
+        <v>126862657</v>
       </c>
       <c r="B59" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6775,14 +6775,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700282</v>
+        <v>700359</v>
       </c>
       <c r="R59" t="n">
-        <v>7114135</v>
+        <v>7114097</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6829,12 +6829,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6845,32 +6845,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126863304</v>
+        <v>126864680</v>
       </c>
       <c r="B60" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700323</v>
+        <v>700363</v>
       </c>
       <c r="R60" t="n">
-        <v>7114164</v>
+        <v>7114127</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6930,12 +6930,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6946,45 +6946,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126862657</v>
+        <v>126864708</v>
       </c>
       <c r="B61" t="n">
-        <v>98436</v>
+        <v>92615</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700359</v>
+        <v>700253</v>
       </c>
       <c r="R61" t="n">
-        <v>7114097</v>
+        <v>7114409</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7031,12 +7031,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7047,45 +7047,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126864719</v>
+        <v>126864687</v>
       </c>
       <c r="B62" t="n">
-        <v>98457</v>
+        <v>82855</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700137</v>
+        <v>700348</v>
       </c>
       <c r="R62" t="n">
-        <v>7114498</v>
+        <v>7114044</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7126,18 +7126,19 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7148,45 +7149,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126864687</v>
+        <v>126864719</v>
       </c>
       <c r="B63" t="n">
-        <v>82852</v>
+        <v>98463</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700348</v>
+        <v>700137</v>
       </c>
       <c r="R63" t="n">
-        <v>7114044</v>
+        <v>7114498</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7227,19 +7228,18 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7253,7 +7253,7 @@
         <v>126864724</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>79038</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7351,48 +7351,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126864713</v>
+        <v>126864720</v>
       </c>
       <c r="B65" t="n">
-        <v>91677</v>
+        <v>80021</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700335</v>
+        <v>700382</v>
       </c>
       <c r="R65" t="n">
-        <v>7114031</v>
+        <v>7114108</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7433,7 +7430,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7456,45 +7452,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126864720</v>
+        <v>126864713</v>
       </c>
       <c r="B66" t="n">
-        <v>80018</v>
+        <v>91683</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700382</v>
+        <v>700335</v>
       </c>
       <c r="R66" t="n">
-        <v>7114108</v>
+        <v>7114031</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7535,6 +7534,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7557,48 +7557,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126851658</v>
+        <v>126862630</v>
       </c>
       <c r="B67" t="n">
-        <v>80114</v>
+        <v>98442</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700243</v>
+        <v>700326</v>
       </c>
       <c r="R67" t="n">
-        <v>7114171</v>
+        <v>7114161</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7625,39 +7625,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7668,10 +7659,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126864683</v>
+        <v>126864702</v>
       </c>
       <c r="B68" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7696,17 +7687,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700345</v>
+        <v>700301</v>
       </c>
       <c r="R68" t="n">
-        <v>7114314</v>
+        <v>7114357</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7741,29 +7744,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7774,10 +7773,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126864736</v>
+        <v>126864683</v>
       </c>
       <c r="B69" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7803,20 +7802,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700346</v>
+        <v>700345</v>
       </c>
       <c r="R69" t="n">
-        <v>7114313</v>
+        <v>7114314</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7851,25 +7846,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7880,10 +7879,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126864702</v>
+        <v>126864736</v>
       </c>
       <c r="B70" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7908,16 +7907,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -7927,10 +7918,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700301</v>
+        <v>700346</v>
       </c>
       <c r="R70" t="n">
-        <v>7114357</v>
+        <v>7114313</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7983,7 +7974,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7994,48 +7985,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126862630</v>
+        <v>126851658</v>
       </c>
       <c r="B71" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700326</v>
+        <v>700243</v>
       </c>
       <c r="R71" t="n">
-        <v>7114161</v>
+        <v>7114171</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8062,30 +8053,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8096,45 +8096,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126865572</v>
+        <v>126867860</v>
       </c>
       <c r="B72" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700229</v>
+        <v>700311</v>
       </c>
       <c r="R72" t="n">
-        <v>7114231</v>
+        <v>7114124</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8175,18 +8187,19 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elke Blöhbaum, Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8200,7 +8213,7 @@
         <v>126865566</v>
       </c>
       <c r="B73" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8298,57 +8311,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126867860</v>
+        <v>126865572</v>
       </c>
       <c r="B74" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700311</v>
+        <v>700229</v>
       </c>
       <c r="R74" t="n">
-        <v>7114124</v>
+        <v>7114231</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8389,19 +8390,18 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8415,7 +8415,7 @@
         <v>126868139</v>
       </c>
       <c r="B75" t="n">
-        <v>96562</v>
+        <v>96568</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8523,10 +8523,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126865557</v>
+        <v>126865562</v>
       </c>
       <c r="B76" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700328</v>
+        <v>700345</v>
       </c>
       <c r="R76" t="n">
-        <v>7114346</v>
+        <v>7114076</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8624,10 +8624,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126865562</v>
+        <v>126865557</v>
       </c>
       <c r="B77" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700345</v>
+        <v>700328</v>
       </c>
       <c r="R77" t="n">
-        <v>7114076</v>
+        <v>7114346</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8728,7 +8728,7 @@
         <v>126856511</v>
       </c>
       <c r="B78" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8945,10 +8945,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126864737</v>
+        <v>126864741</v>
       </c>
       <c r="B80" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8973,17 +8973,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700304</v>
+        <v>700313</v>
       </c>
       <c r="R80" t="n">
-        <v>7114381</v>
+        <v>7114166</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9046,10 +9050,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126867872</v>
+        <v>126867870</v>
       </c>
       <c r="B81" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9081,10 +9085,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700320</v>
+        <v>700316</v>
       </c>
       <c r="R81" t="n">
-        <v>7114336</v>
+        <v>7114065</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9147,10 +9151,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126867870</v>
+        <v>126864737</v>
       </c>
       <c r="B82" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9182,10 +9186,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700316</v>
+        <v>700304</v>
       </c>
       <c r="R82" t="n">
-        <v>7114065</v>
+        <v>7114381</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9232,12 +9236,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9248,10 +9252,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126864741</v>
+        <v>126867872</v>
       </c>
       <c r="B83" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9276,21 +9280,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700313</v>
+        <v>700320</v>
       </c>
       <c r="R83" t="n">
-        <v>7114166</v>
+        <v>7114336</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9337,12 +9337,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9356,7 +9356,7 @@
         <v>126862652</v>
       </c>
       <c r="B84" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -776,45 +776,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126864745</v>
+        <v>126868122</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>4772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700325</v>
+        <v>700332</v>
       </c>
       <c r="R3" t="n">
-        <v>7114161</v>
+        <v>7114038</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -844,11 +849,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -857,16 +872,36 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126868122</v>
+        <v>126868144</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>97320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,39 +923,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700332</v>
+        <v>700167</v>
       </c>
       <c r="R4" t="n">
-        <v>7114038</v>
+        <v>7114511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -962,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,26 +1003,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1103,7 +1113,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1114,32 +1124,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868144</v>
+        <v>126864745</v>
       </c>
       <c r="B6" t="n">
-        <v>97320</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700167</v>
+        <v>700325</v>
       </c>
       <c r="R6" t="n">
-        <v>7114511</v>
+        <v>7114161</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,19 +1192,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,12 +1209,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1225,48 +1225,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126851272</v>
+        <v>126864750</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700310</v>
+        <v>700151</v>
       </c>
       <c r="R7" t="n">
-        <v>7114176</v>
+        <v>7114492</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,19 +1293,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1336,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126867871</v>
+        <v>126851272</v>
       </c>
       <c r="B8" t="n">
         <v>98442</v>
@@ -1367,17 +1357,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700323</v>
+        <v>700310</v>
       </c>
       <c r="R8" t="n">
-        <v>7114124</v>
+        <v>7114176</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,9 +1394,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,12 +1421,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126864699</v>
+        <v>126867871</v>
       </c>
       <c r="B9" t="n">
         <v>98442</v>
@@ -1465,33 +1465,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700344</v>
+        <v>700323</v>
       </c>
       <c r="R9" t="n">
-        <v>7114307</v>
+        <v>7114124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1516,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1555,7 +1538,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126864701</v>
+        <v>126864699</v>
       </c>
       <c r="B10" t="n">
         <v>98442</v>
@@ -1585,7 +1568,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1593,7 +1576,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1602,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700283</v>
+        <v>700344</v>
       </c>
       <c r="R10" t="n">
-        <v>7114393</v>
+        <v>7114307</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,45 +1656,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864750</v>
+        <v>126864701</v>
       </c>
       <c r="B11" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700151</v>
+        <v>700283</v>
       </c>
       <c r="R11" t="n">
-        <v>7114492</v>
+        <v>7114393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,6 +1747,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1871,45 +1871,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126867869</v>
+        <v>126863311</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>92615</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700339</v>
+        <v>700340</v>
       </c>
       <c r="R13" t="n">
-        <v>7114086</v>
+        <v>7114337</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1972,7 +1972,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126863301</v>
+        <v>126867862</v>
       </c>
       <c r="B14" t="n">
         <v>98442</v>
@@ -2000,17 +2000,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700307</v>
+        <v>700364</v>
       </c>
       <c r="R14" t="n">
-        <v>7114151</v>
+        <v>7114084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,18 +2063,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2073,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126867862</v>
+        <v>126867869</v>
       </c>
       <c r="B15" t="n">
         <v>98442</v>
@@ -2101,29 +2114,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700364</v>
+        <v>700339</v>
       </c>
       <c r="R15" t="n">
-        <v>7114084</v>
+        <v>7114086</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2165,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2187,32 +2187,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126863311</v>
+        <v>126863301</v>
       </c>
       <c r="B16" t="n">
-        <v>92615</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700340</v>
+        <v>700307</v>
       </c>
       <c r="R16" t="n">
-        <v>7114337</v>
+        <v>7114151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2389,32 +2389,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868126</v>
+        <v>126868136</v>
       </c>
       <c r="B18" t="n">
-        <v>80117</v>
+        <v>96568</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700245</v>
+        <v>700114</v>
       </c>
       <c r="R18" t="n">
-        <v>7114154</v>
+        <v>7114614</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,21 +2480,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2515,32 +2500,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126864725</v>
+        <v>126868126</v>
       </c>
       <c r="B19" t="n">
-        <v>79038</v>
+        <v>80117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2550,10 +2535,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700244</v>
+        <v>700245</v>
       </c>
       <c r="R19" t="n">
-        <v>7114210</v>
+        <v>7114154</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,11 +2568,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2596,16 +2591,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2616,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126868136</v>
+        <v>126864725</v>
       </c>
       <c r="B20" t="n">
-        <v>96568</v>
+        <v>79038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,21 +2637,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,13 +2661,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700114</v>
+        <v>700244</v>
       </c>
       <c r="R20" t="n">
-        <v>7114614</v>
+        <v>7114210</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2684,19 +2694,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,12 +2711,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2828,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126863310</v>
+        <v>126862588</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>91325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700290</v>
+        <v>700304</v>
       </c>
       <c r="R22" t="n">
-        <v>7114136</v>
+        <v>7114192</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,12 +2913,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126862588</v>
+        <v>126863310</v>
       </c>
       <c r="B23" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700304</v>
+        <v>700290</v>
       </c>
       <c r="R23" t="n">
-        <v>7114192</v>
+        <v>7114136</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,12 +3014,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3567,32 +3567,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126865559</v>
+        <v>126864748</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700330</v>
+        <v>700220</v>
       </c>
       <c r="R29" t="n">
-        <v>7114328</v>
+        <v>7114448</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3668,7 +3668,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126862653</v>
+        <v>126868151</v>
       </c>
       <c r="B30" t="n">
         <v>98442</v>
@@ -3699,14 +3699,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700319</v>
+        <v>700306</v>
       </c>
       <c r="R30" t="n">
-        <v>7114336</v>
+        <v>7114337</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,9 +3736,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,12 +3763,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3769,7 +3779,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126868151</v>
+        <v>126865559</v>
       </c>
       <c r="B31" t="n">
         <v>98442</v>
@@ -3804,10 +3814,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700306</v>
+        <v>700330</v>
       </c>
       <c r="R31" t="n">
-        <v>7114337</v>
+        <v>7114328</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,19 +3847,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,12 +3864,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3880,45 +3880,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126864748</v>
+        <v>126862653</v>
       </c>
       <c r="B32" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700220</v>
+        <v>700319</v>
       </c>
       <c r="R32" t="n">
-        <v>7114448</v>
+        <v>7114336</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,12 +3965,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3981,45 +3981,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126864698</v>
+        <v>126864703</v>
       </c>
       <c r="B33" t="n">
-        <v>91325</v>
+        <v>98442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700320</v>
+        <v>700315</v>
       </c>
       <c r="R33" t="n">
-        <v>7114182</v>
+        <v>7114347</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,6 +4072,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4082,32 +4095,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126864706</v>
+        <v>126865556</v>
       </c>
       <c r="B34" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4117,10 +4130,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700145</v>
+        <v>700304</v>
       </c>
       <c r="R34" t="n">
-        <v>7114540</v>
+        <v>7114364</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4172,7 +4185,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4183,48 +4196,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126852356</v>
+        <v>126862654</v>
       </c>
       <c r="B35" t="n">
-        <v>92615</v>
+        <v>98442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700344</v>
+        <v>700337</v>
       </c>
       <c r="R35" t="n">
-        <v>7114301</v>
+        <v>7114304</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4251,19 +4264,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,12 +4281,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4294,57 +4297,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126864703</v>
+        <v>126864698</v>
       </c>
       <c r="B36" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700315</v>
+        <v>700320</v>
       </c>
       <c r="R36" t="n">
-        <v>7114347</v>
+        <v>7114182</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,7 +4376,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4408,48 +4398,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126865556</v>
+        <v>126852356</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>92615</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700304</v>
+        <v>700344</v>
       </c>
       <c r="R37" t="n">
-        <v>7114364</v>
+        <v>7114301</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4476,9 +4466,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4493,12 +4493,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4509,45 +4509,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126862654</v>
+        <v>126864706</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700337</v>
+        <v>700145</v>
       </c>
       <c r="R38" t="n">
-        <v>7114304</v>
+        <v>7114540</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,12 +4594,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4610,10 +4610,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126868146</v>
+        <v>126865569</v>
       </c>
       <c r="B39" t="n">
-        <v>41361</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4621,39 +4621,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>215713</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700294</v>
+        <v>700198</v>
       </c>
       <c r="R39" t="n">
-        <v>7114336</v>
+        <v>7114523</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,19 +4678,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4710,12 +4695,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4726,32 +4711,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126865563</v>
+        <v>126867882</v>
       </c>
       <c r="B40" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4761,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700297</v>
+        <v>700181</v>
       </c>
       <c r="R40" t="n">
-        <v>7114112</v>
+        <v>7114498</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,12 +4796,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4827,57 +4812,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126864700</v>
+        <v>126865578</v>
       </c>
       <c r="B41" t="n">
-        <v>98442</v>
+        <v>98359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700265</v>
+        <v>700147</v>
       </c>
       <c r="R41" t="n">
-        <v>7114403</v>
+        <v>7114536</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4891,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4930,7 +4902,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4941,45 +4913,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126865578</v>
+        <v>126868146</v>
       </c>
       <c r="B42" t="n">
-        <v>98359</v>
+        <v>41361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>215713</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700147</v>
+        <v>700294</v>
       </c>
       <c r="R42" t="n">
-        <v>7114536</v>
+        <v>7114336</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5009,9 +4986,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5026,12 +5013,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5042,32 +5029,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126867882</v>
+        <v>126865563</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5077,10 +5064,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700181</v>
+        <v>700297</v>
       </c>
       <c r="R43" t="n">
-        <v>7114498</v>
+        <v>7114112</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,12 +5114,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5143,45 +5130,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126865569</v>
+        <v>126864700</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700198</v>
+        <v>700265</v>
       </c>
       <c r="R44" t="n">
-        <v>7114523</v>
+        <v>7114403</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5222,6 +5221,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5693,45 +5693,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126868129</v>
+        <v>126864734</v>
       </c>
       <c r="B49" t="n">
-        <v>80153</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700245</v>
+        <v>700263</v>
       </c>
       <c r="R49" t="n">
-        <v>7114154</v>
+        <v>7114387</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,21 +5765,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5784,31 +5778,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5819,45 +5798,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126863285</v>
+        <v>126868129</v>
       </c>
       <c r="B50" t="n">
-        <v>57817</v>
+        <v>80153</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700344</v>
+        <v>700245</v>
       </c>
       <c r="R50" t="n">
-        <v>7114335</v>
+        <v>7114154</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5887,11 +5866,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5900,16 +5889,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5920,57 +5924,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126864704</v>
+        <v>126863285</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700273</v>
+        <v>700344</v>
       </c>
       <c r="R51" t="n">
-        <v>7114229</v>
+        <v>7114335</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6017,12 +6009,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6033,7 +6025,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126864734</v>
+        <v>126862656</v>
       </c>
       <c r="B52" t="n">
         <v>98442</v>
@@ -6061,21 +6053,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700263</v>
+        <v>700320</v>
       </c>
       <c r="R52" t="n">
-        <v>7114387</v>
+        <v>7114171</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6122,12 +6110,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6138,7 +6126,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126864738</v>
+        <v>126864704</v>
       </c>
       <c r="B53" t="n">
         <v>98442</v>
@@ -6166,17 +6154,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700299</v>
+        <v>700273</v>
       </c>
       <c r="R53" t="n">
-        <v>7114327</v>
+        <v>7114229</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126865558</v>
+        <v>126864738</v>
       </c>
       <c r="B54" t="n">
         <v>98442</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700326</v>
+        <v>700299</v>
       </c>
       <c r="R54" t="n">
-        <v>7114352</v>
+        <v>7114327</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6340,7 +6340,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126862656</v>
+        <v>126865558</v>
       </c>
       <c r="B55" t="n">
         <v>98442</v>
@@ -6371,14 +6371,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700320</v>
+        <v>700326</v>
       </c>
       <c r="R55" t="n">
-        <v>7114171</v>
+        <v>7114352</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6425,12 +6425,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6441,32 +6441,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126865564</v>
+        <v>126864708</v>
       </c>
       <c r="B56" t="n">
-        <v>98442</v>
+        <v>92615</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6476,10 +6476,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700282</v>
+        <v>700253</v>
       </c>
       <c r="R56" t="n">
-        <v>7114135</v>
+        <v>7114409</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6542,45 +6542,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126865567</v>
+        <v>126864680</v>
       </c>
       <c r="B57" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700281</v>
+        <v>700363</v>
       </c>
       <c r="R57" t="n">
-        <v>7114196</v>
+        <v>7114127</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6627,12 +6627,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6643,7 +6643,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126863304</v>
+        <v>126865567</v>
       </c>
       <c r="B58" t="n">
         <v>98442</v>
@@ -6674,14 +6674,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700323</v>
+        <v>700281</v>
       </c>
       <c r="R58" t="n">
-        <v>7114164</v>
+        <v>7114196</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6728,12 +6728,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6845,32 +6845,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126864680</v>
+        <v>126863304</v>
       </c>
       <c r="B60" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700363</v>
+        <v>700323</v>
       </c>
       <c r="R60" t="n">
-        <v>7114127</v>
+        <v>7114164</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6930,12 +6930,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6946,32 +6946,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126864708</v>
+        <v>126865564</v>
       </c>
       <c r="B61" t="n">
-        <v>92615</v>
+        <v>98442</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6981,10 +6981,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700253</v>
+        <v>700282</v>
       </c>
       <c r="R61" t="n">
-        <v>7114409</v>
+        <v>7114135</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7149,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126864719</v>
+        <v>126864724</v>
       </c>
       <c r="B63" t="n">
-        <v>98463</v>
+        <v>79038</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6434</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700137</v>
+        <v>700243</v>
       </c>
       <c r="R63" t="n">
-        <v>7114498</v>
+        <v>7114142</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7250,10 +7250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126864724</v>
+        <v>126864719</v>
       </c>
       <c r="B64" t="n">
-        <v>79038</v>
+        <v>98463</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7261,21 +7261,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6434</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700243</v>
+        <v>700137</v>
       </c>
       <c r="R64" t="n">
-        <v>7114142</v>
+        <v>7114498</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7351,45 +7351,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126864720</v>
+        <v>126864713</v>
       </c>
       <c r="B65" t="n">
-        <v>80021</v>
+        <v>91683</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700382</v>
+        <v>700335</v>
       </c>
       <c r="R65" t="n">
-        <v>7114108</v>
+        <v>7114031</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7430,6 +7433,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7452,10 +7456,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126864713</v>
+        <v>126864736</v>
       </c>
       <c r="B66" t="n">
-        <v>91683</v>
+        <v>98442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7463,26 +7467,27 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7490,10 +7495,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700335</v>
+        <v>700346</v>
       </c>
       <c r="R66" t="n">
-        <v>7114031</v>
+        <v>7114313</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7546,7 +7551,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7557,7 +7562,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126862630</v>
+        <v>126864702</v>
       </c>
       <c r="B67" t="n">
         <v>98442</v>
@@ -7585,17 +7590,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700326</v>
+        <v>700301</v>
       </c>
       <c r="R67" t="n">
-        <v>7114161</v>
+        <v>7114357</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7643,12 +7660,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7659,7 +7676,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126864702</v>
+        <v>126862630</v>
       </c>
       <c r="B68" t="n">
         <v>98442</v>
@@ -7687,29 +7704,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700301</v>
+        <v>700326</v>
       </c>
       <c r="R68" t="n">
-        <v>7114357</v>
+        <v>7114161</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7757,12 +7762,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7773,48 +7778,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126864683</v>
+        <v>126851658</v>
       </c>
       <c r="B69" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700345</v>
+        <v>700243</v>
       </c>
       <c r="R69" t="n">
-        <v>7114314</v>
+        <v>7114171</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7841,14 +7846,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7863,12 +7873,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7879,49 +7889,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126864736</v>
+        <v>126864720</v>
       </c>
       <c r="B70" t="n">
-        <v>98442</v>
+        <v>80021</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700346</v>
+        <v>700382</v>
       </c>
       <c r="R70" t="n">
-        <v>7114313</v>
+        <v>7114108</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7962,7 +7968,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7974,7 +7979,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7985,48 +7990,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126851658</v>
+        <v>126864683</v>
       </c>
       <c r="B71" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700243</v>
+        <v>700345</v>
       </c>
       <c r="R71" t="n">
-        <v>7114171</v>
+        <v>7114314</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8053,19 +8058,14 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>10:37</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8080,12 +8080,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8096,57 +8096,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126867860</v>
+        <v>126865572</v>
       </c>
       <c r="B72" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700311</v>
+        <v>700229</v>
       </c>
       <c r="R72" t="n">
-        <v>7114124</v>
+        <v>7114231</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8187,19 +8175,18 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8311,45 +8298,57 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126865572</v>
+        <v>126867860</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700229</v>
+        <v>700311</v>
       </c>
       <c r="R74" t="n">
-        <v>7114231</v>
+        <v>7114124</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8390,18 +8389,19 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8523,7 +8523,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126865562</v>
+        <v>126865557</v>
       </c>
       <c r="B76" t="n">
         <v>98442</v>
@@ -8558,10 +8558,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700345</v>
+        <v>700328</v>
       </c>
       <c r="R76" t="n">
-        <v>7114076</v>
+        <v>7114346</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8624,7 +8624,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126865557</v>
+        <v>126865562</v>
       </c>
       <c r="B77" t="n">
         <v>98442</v>
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700328</v>
+        <v>700345</v>
       </c>
       <c r="R77" t="n">
-        <v>7114346</v>
+        <v>7114076</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8725,48 +8725,56 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126856511</v>
+        <v>126864729</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700252</v>
+        <v>700152</v>
       </c>
       <c r="R78" t="n">
-        <v>7114157</v>
+        <v>7114491</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8793,19 +8801,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8820,12 +8818,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8836,53 +8834,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126864729</v>
+        <v>126867872</v>
       </c>
       <c r="B79" t="n">
-        <v>58027</v>
+        <v>98442</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700152</v>
+        <v>700320</v>
       </c>
       <c r="R79" t="n">
-        <v>7114491</v>
+        <v>7114336</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8929,12 +8919,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8945,7 +8935,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126864741</v>
+        <v>126867870</v>
       </c>
       <c r="B80" t="n">
         <v>98442</v>
@@ -8973,21 +8963,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700313</v>
+        <v>700316</v>
       </c>
       <c r="R80" t="n">
-        <v>7114166</v>
+        <v>7114065</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9034,12 +9020,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9050,48 +9036,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126867870</v>
+        <v>126856511</v>
       </c>
       <c r="B81" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700316</v>
+        <v>700252</v>
       </c>
       <c r="R81" t="n">
-        <v>7114065</v>
+        <v>7114157</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9118,9 +9104,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9135,12 +9131,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9252,7 +9248,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126867872</v>
+        <v>126864741</v>
       </c>
       <c r="B83" t="n">
         <v>98442</v>
@@ -9280,17 +9276,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700320</v>
+        <v>700313</v>
       </c>
       <c r="R83" t="n">
-        <v>7114336</v>
+        <v>7114166</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9337,12 +9337,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -776,50 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126868122</v>
+        <v>126864745</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700332</v>
+        <v>700325</v>
       </c>
       <c r="R3" t="n">
-        <v>7114038</v>
+        <v>7114161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -849,21 +844,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,36 +857,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -912,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126868144</v>
+        <v>126868122</v>
       </c>
       <c r="B4" t="n">
-        <v>97320</v>
+        <v>4772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +888,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700167</v>
+        <v>700332</v>
       </c>
       <c r="R4" t="n">
-        <v>7114511</v>
+        <v>7114038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +952,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +962,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,6 +973,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1023,45 +1013,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126862651</v>
+        <v>126868144</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>97320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700266</v>
+        <v>700167</v>
       </c>
       <c r="R5" t="n">
-        <v>7114350</v>
+        <v>7114511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,9 +1081,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,12 +1108,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1124,45 +1124,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126864745</v>
+        <v>126862651</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700325</v>
+        <v>700266</v>
       </c>
       <c r="R6" t="n">
-        <v>7114161</v>
+        <v>7114350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,12 +1209,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -3981,57 +3981,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126864703</v>
+        <v>126864698</v>
       </c>
       <c r="B33" t="n">
-        <v>98442</v>
+        <v>91325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700315</v>
+        <v>700320</v>
       </c>
       <c r="R33" t="n">
-        <v>7114347</v>
+        <v>7114182</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4072,7 +4060,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4095,7 +4082,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126865556</v>
+        <v>126864703</v>
       </c>
       <c r="B34" t="n">
         <v>98442</v>
@@ -4123,17 +4110,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700304</v>
+        <v>700315</v>
       </c>
       <c r="R34" t="n">
-        <v>7114364</v>
+        <v>7114347</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4174,6 +4173,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4196,48 +4196,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126862654</v>
+        <v>126852356</v>
       </c>
       <c r="B35" t="n">
-        <v>98442</v>
+        <v>92615</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700337</v>
+        <v>700344</v>
       </c>
       <c r="R35" t="n">
-        <v>7114304</v>
+        <v>7114301</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4264,9 +4264,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,12 +4291,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4297,32 +4307,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126864698</v>
+        <v>126864706</v>
       </c>
       <c r="B36" t="n">
-        <v>91325</v>
+        <v>98359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4332,10 +4342,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700320</v>
+        <v>700145</v>
       </c>
       <c r="R36" t="n">
-        <v>7114182</v>
+        <v>7114540</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4387,7 +4397,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4398,48 +4408,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126852356</v>
+        <v>126865556</v>
       </c>
       <c r="B37" t="n">
-        <v>92615</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700344</v>
+        <v>700304</v>
       </c>
       <c r="R37" t="n">
-        <v>7114301</v>
+        <v>7114364</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4466,19 +4476,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4493,12 +4493,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4509,45 +4509,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126864706</v>
+        <v>126862654</v>
       </c>
       <c r="B38" t="n">
-        <v>98359</v>
+        <v>98442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700145</v>
+        <v>700337</v>
       </c>
       <c r="R38" t="n">
-        <v>7114540</v>
+        <v>7114304</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,12 +4594,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -5345,48 +5345,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126854059</v>
+        <v>126868134</v>
       </c>
       <c r="B46" t="n">
-        <v>91325</v>
+        <v>4772</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lappmyran, Lappmyran, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700098</v>
+        <v>700186</v>
       </c>
       <c r="R46" t="n">
-        <v>7114648</v>
+        <v>7114499</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5415,7 +5420,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5425,7 +5430,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5436,16 +5441,36 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5456,53 +5481,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126868134</v>
+        <v>126854059</v>
       </c>
       <c r="B47" t="n">
-        <v>4772</v>
+        <v>91325</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lappmyran, Lappmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700186</v>
+        <v>700098</v>
       </c>
       <c r="R47" t="n">
-        <v>7114499</v>
+        <v>7114648</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5531,7 +5551,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5541,7 +5561,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5552,36 +5572,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5693,49 +5693,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126864734</v>
+        <v>126868129</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>80153</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700263</v>
+        <v>700245</v>
       </c>
       <c r="R49" t="n">
-        <v>7114387</v>
+        <v>7114154</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5765,11 +5761,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5778,16 +5784,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5798,45 +5819,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126868129</v>
+        <v>126863285</v>
       </c>
       <c r="B50" t="n">
-        <v>80153</v>
+        <v>57817</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700245</v>
+        <v>700344</v>
       </c>
       <c r="R50" t="n">
-        <v>7114154</v>
+        <v>7114335</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5866,21 +5887,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5889,31 +5900,16 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5924,32 +5920,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126863285</v>
+        <v>126862656</v>
       </c>
       <c r="B51" t="n">
-        <v>57817</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5959,10 +5955,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700344</v>
+        <v>700320</v>
       </c>
       <c r="R51" t="n">
-        <v>7114335</v>
+        <v>7114171</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6009,12 +6005,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6025,7 +6021,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126862656</v>
+        <v>126864704</v>
       </c>
       <c r="B52" t="n">
         <v>98442</v>
@@ -6053,17 +6049,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700320</v>
+        <v>700273</v>
       </c>
       <c r="R52" t="n">
-        <v>7114171</v>
+        <v>7114229</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6110,12 +6118,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6126,7 +6134,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126864704</v>
+        <v>126864738</v>
       </c>
       <c r="B53" t="n">
         <v>98442</v>
@@ -6154,29 +6162,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700273</v>
+        <v>700299</v>
       </c>
       <c r="R53" t="n">
-        <v>7114229</v>
+        <v>7114327</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6228,7 +6224,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6239,7 +6235,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126864738</v>
+        <v>126865558</v>
       </c>
       <c r="B54" t="n">
         <v>98442</v>
@@ -6274,10 +6270,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700299</v>
+        <v>700326</v>
       </c>
       <c r="R54" t="n">
-        <v>7114327</v>
+        <v>7114352</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6329,7 +6325,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6340,7 +6336,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126865558</v>
+        <v>126864734</v>
       </c>
       <c r="B55" t="n">
         <v>98442</v>
@@ -6368,17 +6364,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700326</v>
+        <v>700263</v>
       </c>
       <c r="R55" t="n">
-        <v>7114352</v>
+        <v>7114387</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126864711</v>
+        <v>126862651</v>
       </c>
       <c r="B2" t="n">
-        <v>96695</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700315</v>
+        <v>700266</v>
       </c>
       <c r="R2" t="n">
-        <v>7114081</v>
+        <v>7114350</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -877,50 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126868122</v>
+        <v>126864711</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>96696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700332</v>
+        <v>700315</v>
       </c>
       <c r="R4" t="n">
-        <v>7114038</v>
+        <v>7114081</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,21 +945,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -973,36 +958,16 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1013,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126868144</v>
+        <v>126868122</v>
       </c>
       <c r="B5" t="n">
-        <v>97320</v>
+        <v>4772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +989,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700167</v>
+        <v>700332</v>
       </c>
       <c r="R5" t="n">
-        <v>7114511</v>
+        <v>7114038</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1053,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1093,7 +1063,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,6 +1074,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1124,45 +1114,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126862651</v>
+        <v>126868144</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>97321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700266</v>
+        <v>700167</v>
       </c>
       <c r="R6" t="n">
-        <v>7114350</v>
+        <v>7114511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,9 +1182,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,12 +1209,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1228,7 +1228,7 @@
         <v>126864750</v>
       </c>
       <c r="B7" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,48 +1326,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126851272</v>
+        <v>126862629</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>80077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700310</v>
+        <v>700301</v>
       </c>
       <c r="R8" t="n">
-        <v>7114176</v>
+        <v>7114163</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,19 +1394,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,12 +1411,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1437,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126867871</v>
+        <v>126851272</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,17 +1458,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700323</v>
+        <v>700310</v>
       </c>
       <c r="R9" t="n">
-        <v>7114124</v>
+        <v>7114176</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1505,9 +1495,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,12 +1522,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126864699</v>
+        <v>126867871</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,33 +1566,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700344</v>
+        <v>700323</v>
       </c>
       <c r="R10" t="n">
-        <v>7114307</v>
+        <v>7114124</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,19 +1617,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1656,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864701</v>
+        <v>126864699</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,7 +1669,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1694,7 +1677,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1703,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700283</v>
+        <v>700344</v>
       </c>
       <c r="R11" t="n">
-        <v>7114393</v>
+        <v>7114307</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,45 +1757,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126862629</v>
+        <v>126864701</v>
       </c>
       <c r="B12" t="n">
-        <v>80077</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700301</v>
+        <v>700283</v>
       </c>
       <c r="R12" t="n">
-        <v>7114163</v>
+        <v>7114393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,18 +1848,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126863311</v>
+        <v>126865575</v>
       </c>
       <c r="B13" t="n">
-        <v>92615</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1882,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700340</v>
+        <v>700236</v>
       </c>
       <c r="R13" t="n">
-        <v>7114337</v>
+        <v>7114234</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1975,7 +1975,7 @@
         <v>126867862</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>126867869</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>126863301</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126865575</v>
+        <v>126863311</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>92616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,34 +2299,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700236</v>
+        <v>700340</v>
       </c>
       <c r="R17" t="n">
-        <v>7114234</v>
+        <v>7114337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,12 +2373,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2392,7 +2392,7 @@
         <v>126868136</v>
       </c>
       <c r="B18" t="n">
-        <v>96568</v>
+        <v>96569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>126865568</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126862588</v>
+        <v>126863310</v>
       </c>
       <c r="B22" t="n">
-        <v>91325</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700304</v>
+        <v>700290</v>
       </c>
       <c r="R22" t="n">
-        <v>7114192</v>
+        <v>7114136</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,12 +2913,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126863310</v>
+        <v>126862588</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700290</v>
+        <v>700304</v>
       </c>
       <c r="R23" t="n">
-        <v>7114136</v>
+        <v>7114192</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,12 +3014,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3033,7 +3033,7 @@
         <v>126867858</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>126864710</v>
       </c>
       <c r="B25" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>126864739</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,32 +3567,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126864748</v>
+        <v>126868151</v>
       </c>
       <c r="B29" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700220</v>
+        <v>700306</v>
       </c>
       <c r="R29" t="n">
-        <v>7114448</v>
+        <v>7114337</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,9 +3635,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3652,12 +3662,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3668,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126868151</v>
+        <v>126865559</v>
       </c>
       <c r="B30" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700306</v>
+        <v>700330</v>
       </c>
       <c r="R30" t="n">
-        <v>7114337</v>
+        <v>7114328</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,19 +3746,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,12 +3763,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3779,32 +3779,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126865559</v>
+        <v>126864748</v>
       </c>
       <c r="B31" t="n">
-        <v>98442</v>
+        <v>98360</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700330</v>
+        <v>700220</v>
       </c>
       <c r="R31" t="n">
-        <v>7114328</v>
+        <v>7114448</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3883,7 +3883,7 @@
         <v>126862653</v>
       </c>
       <c r="B32" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3981,32 +3981,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126864698</v>
+        <v>126864706</v>
       </c>
       <c r="B33" t="n">
-        <v>91325</v>
+        <v>98360</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700320</v>
+        <v>700145</v>
       </c>
       <c r="R33" t="n">
-        <v>7114182</v>
+        <v>7114540</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4082,60 +4082,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126864703</v>
+        <v>126852356</v>
       </c>
       <c r="B34" t="n">
-        <v>98442</v>
+        <v>92616</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700315</v>
+        <v>700344</v>
       </c>
       <c r="R34" t="n">
-        <v>7114347</v>
+        <v>7114301</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4162,30 +4150,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4196,48 +4193,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126852356</v>
+        <v>126864698</v>
       </c>
       <c r="B35" t="n">
-        <v>92615</v>
+        <v>91326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700344</v>
+        <v>700320</v>
       </c>
       <c r="R35" t="n">
-        <v>7114301</v>
+        <v>7114182</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4264,19 +4261,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4291,12 +4278,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4307,45 +4294,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126864706</v>
+        <v>126864703</v>
       </c>
       <c r="B36" t="n">
-        <v>98359</v>
+        <v>98443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700145</v>
+        <v>700315</v>
       </c>
       <c r="R36" t="n">
-        <v>7114540</v>
+        <v>7114347</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4386,6 +4385,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4411,7 +4411,7 @@
         <v>126865556</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>126862654</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126867882</v>
+        <v>126868146</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>41361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4722,34 +4722,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>215713</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700181</v>
+        <v>700294</v>
       </c>
       <c r="R40" t="n">
-        <v>7114498</v>
+        <v>7114336</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,9 +4784,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4796,12 +4811,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4812,32 +4827,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126865578</v>
+        <v>126867882</v>
       </c>
       <c r="B41" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4847,10 +4862,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700147</v>
+        <v>700181</v>
       </c>
       <c r="R41" t="n">
-        <v>7114536</v>
+        <v>7114498</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4897,12 +4912,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4913,50 +4928,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126868146</v>
+        <v>126865578</v>
       </c>
       <c r="B42" t="n">
-        <v>41361</v>
+        <v>98360</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>215713</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700294</v>
+        <v>700147</v>
       </c>
       <c r="R42" t="n">
-        <v>7114336</v>
+        <v>7114536</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,19 +4996,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5013,12 +5013,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5032,7 +5032,7 @@
         <v>126865563</v>
       </c>
       <c r="B43" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>126864700</v>
       </c>
       <c r="B44" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>126864733</v>
       </c>
       <c r="B45" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>126854059</v>
       </c>
       <c r="B47" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>126864746</v>
       </c>
       <c r="B48" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5693,45 +5693,57 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126868129</v>
+        <v>126864704</v>
       </c>
       <c r="B49" t="n">
-        <v>80153</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700245</v>
+        <v>700273</v>
       </c>
       <c r="R49" t="n">
-        <v>7114154</v>
+        <v>7114229</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,21 +5773,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5784,31 +5786,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5819,45 +5806,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126863285</v>
+        <v>126864734</v>
       </c>
       <c r="B50" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700344</v>
+        <v>700263</v>
       </c>
       <c r="R50" t="n">
-        <v>7114335</v>
+        <v>7114387</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,12 +5895,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5923,7 +5914,7 @@
         <v>126862656</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6010,7 +6001,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6021,10 +6012,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126864704</v>
+        <v>126864738</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6049,29 +6040,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700273</v>
+        <v>700299</v>
       </c>
       <c r="R52" t="n">
-        <v>7114229</v>
+        <v>7114327</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6123,7 +6102,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6134,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126864738</v>
+        <v>126865558</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6169,10 +6148,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700299</v>
+        <v>700326</v>
       </c>
       <c r="R53" t="n">
-        <v>7114327</v>
+        <v>7114352</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6224,7 +6203,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6235,32 +6214,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126865558</v>
+        <v>126868129</v>
       </c>
       <c r="B54" t="n">
-        <v>98442</v>
+        <v>80153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6270,10 +6249,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700326</v>
+        <v>700245</v>
       </c>
       <c r="R54" t="n">
-        <v>7114352</v>
+        <v>7114154</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6303,11 +6282,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6316,16 +6305,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6336,49 +6340,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126864734</v>
+        <v>126863285</v>
       </c>
       <c r="B55" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700263</v>
+        <v>700344</v>
       </c>
       <c r="R55" t="n">
-        <v>7114387</v>
+        <v>7114335</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6425,12 +6425,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6444,7 +6444,7 @@
         <v>126864708</v>
       </c>
       <c r="B56" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6643,10 +6643,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126865567</v>
+        <v>126865564</v>
       </c>
       <c r="B58" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700281</v>
+        <v>700282</v>
       </c>
       <c r="R58" t="n">
-        <v>7114196</v>
+        <v>7114135</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6747,7 +6747,7 @@
         <v>126862657</v>
       </c>
       <c r="B59" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6848,7 +6848,7 @@
         <v>126863304</v>
       </c>
       <c r="B60" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6946,10 +6946,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126865564</v>
+        <v>126865567</v>
       </c>
       <c r="B61" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700282</v>
+        <v>700281</v>
       </c>
       <c r="R61" t="n">
-        <v>7114135</v>
+        <v>7114196</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126864724</v>
+        <v>126864719</v>
       </c>
       <c r="B63" t="n">
-        <v>79038</v>
+        <v>98464</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700243</v>
+        <v>700137</v>
       </c>
       <c r="R63" t="n">
-        <v>7114142</v>
+        <v>7114498</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7250,10 +7250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126864719</v>
+        <v>126864724</v>
       </c>
       <c r="B64" t="n">
-        <v>98463</v>
+        <v>79038</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7261,21 +7261,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6434</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700137</v>
+        <v>700243</v>
       </c>
       <c r="R64" t="n">
-        <v>7114498</v>
+        <v>7114142</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7354,7 +7354,7 @@
         <v>126864713</v>
       </c>
       <c r="B65" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7456,52 +7456,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126864736</v>
+        <v>126851658</v>
       </c>
       <c r="B66" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700346</v>
+        <v>700243</v>
       </c>
       <c r="R66" t="n">
-        <v>7114313</v>
+        <v>7114171</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7528,30 +7524,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7562,57 +7567,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126864702</v>
+        <v>126864720</v>
       </c>
       <c r="B67" t="n">
-        <v>98442</v>
+        <v>80021</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700301</v>
+        <v>700382</v>
       </c>
       <c r="R67" t="n">
-        <v>7114357</v>
+        <v>7114108</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7653,7 +7646,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7665,7 +7657,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7676,10 +7668,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126862630</v>
+        <v>126864683</v>
       </c>
       <c r="B68" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7711,10 +7703,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700326</v>
+        <v>700345</v>
       </c>
       <c r="R68" t="n">
-        <v>7114161</v>
+        <v>7114314</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7749,25 +7741,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7778,48 +7774,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126851658</v>
+        <v>126862630</v>
       </c>
       <c r="B69" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700243</v>
+        <v>700326</v>
       </c>
       <c r="R69" t="n">
-        <v>7114171</v>
+        <v>7114161</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7846,39 +7842,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7889,45 +7876,49 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126864720</v>
+        <v>126864736</v>
       </c>
       <c r="B70" t="n">
-        <v>80021</v>
+        <v>98443</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700382</v>
+        <v>700346</v>
       </c>
       <c r="R70" t="n">
-        <v>7114108</v>
+        <v>7114313</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7968,6 +7959,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7979,7 +7971,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7990,10 +7982,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126864683</v>
+        <v>126864702</v>
       </c>
       <c r="B71" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8018,17 +8010,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700345</v>
+        <v>700301</v>
       </c>
       <c r="R71" t="n">
-        <v>7114314</v>
+        <v>7114357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8063,29 +8067,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8200,7 +8200,7 @@
         <v>126865566</v>
       </c>
       <c r="B73" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>126867860</v>
       </c>
       <c r="B74" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8412,32 +8412,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126868139</v>
+        <v>126865562</v>
       </c>
       <c r="B75" t="n">
-        <v>96568</v>
+        <v>98443</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700112</v>
+        <v>700345</v>
       </c>
       <c r="R75" t="n">
-        <v>7114619</v>
+        <v>7114076</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8480,19 +8480,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8507,12 +8497,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8523,32 +8513,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126865557</v>
+        <v>126868139</v>
       </c>
       <c r="B76" t="n">
-        <v>98442</v>
+        <v>96569</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8558,10 +8548,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700328</v>
+        <v>700112</v>
       </c>
       <c r="R76" t="n">
-        <v>7114346</v>
+        <v>7114619</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8591,9 +8581,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8608,12 +8608,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8624,10 +8624,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126865562</v>
+        <v>126865557</v>
       </c>
       <c r="B77" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700345</v>
+        <v>700328</v>
       </c>
       <c r="R77" t="n">
-        <v>7114076</v>
+        <v>7114346</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8834,48 +8834,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126867872</v>
+        <v>126856511</v>
       </c>
       <c r="B79" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700320</v>
+        <v>700252</v>
       </c>
       <c r="R79" t="n">
-        <v>7114336</v>
+        <v>7114157</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8902,9 +8902,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8919,12 +8929,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8935,10 +8945,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126867870</v>
+        <v>126867872</v>
       </c>
       <c r="B80" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8970,10 +8980,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700316</v>
+        <v>700320</v>
       </c>
       <c r="R80" t="n">
-        <v>7114065</v>
+        <v>7114336</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9036,48 +9046,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126856511</v>
+        <v>126867870</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700252</v>
+        <v>700316</v>
       </c>
       <c r="R81" t="n">
-        <v>7114157</v>
+        <v>7114065</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9104,19 +9114,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9131,12 +9131,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9147,10 +9147,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126864737</v>
+        <v>126864741</v>
       </c>
       <c r="B82" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9175,17 +9175,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700304</v>
+        <v>700313</v>
       </c>
       <c r="R82" t="n">
-        <v>7114381</v>
+        <v>7114166</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9248,10 +9252,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126864741</v>
+        <v>126864737</v>
       </c>
       <c r="B83" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9276,21 +9280,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700313</v>
+        <v>700304</v>
       </c>
       <c r="R83" t="n">
-        <v>7114166</v>
+        <v>7114381</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9356,7 +9356,7 @@
         <v>126862652</v>
       </c>
       <c r="B84" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126862651</v>
+        <v>126864745</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700266</v>
+        <v>700325</v>
       </c>
       <c r="R2" t="n">
-        <v>7114350</v>
+        <v>7114161</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126864745</v>
+        <v>126864711</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>96696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700325</v>
+        <v>700315</v>
       </c>
       <c r="R3" t="n">
-        <v>7114161</v>
+        <v>7114081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,45 +877,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126864711</v>
+        <v>126868122</v>
       </c>
       <c r="B4" t="n">
-        <v>96696</v>
+        <v>4772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700315</v>
+        <v>700332</v>
       </c>
       <c r="R4" t="n">
-        <v>7114081</v>
+        <v>7114038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -958,16 +973,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126868122</v>
+        <v>126868144</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>97321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,39 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700332</v>
+        <v>700167</v>
       </c>
       <c r="R5" t="n">
-        <v>7114038</v>
+        <v>7114511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1063,7 +1093,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1074,26 +1104,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1114,45 +1124,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868144</v>
+        <v>126862651</v>
       </c>
       <c r="B6" t="n">
-        <v>97321</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700167</v>
+        <v>700266</v>
       </c>
       <c r="R6" t="n">
-        <v>7114511</v>
+        <v>7114350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,19 +1192,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,12 +1209,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1326,48 +1326,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126862629</v>
+        <v>126851272</v>
       </c>
       <c r="B8" t="n">
-        <v>80077</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700301</v>
+        <v>700310</v>
       </c>
       <c r="R8" t="n">
-        <v>7114163</v>
+        <v>7114176</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,9 +1394,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,12 +1421,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1427,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126851272</v>
+        <v>126867871</v>
       </c>
       <c r="B9" t="n">
         <v>98443</v>
@@ -1458,17 +1468,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700310</v>
+        <v>700323</v>
       </c>
       <c r="R9" t="n">
-        <v>7114176</v>
+        <v>7114124</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,19 +1505,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,12 +1522,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1538,7 +1538,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126867871</v>
+        <v>126864699</v>
       </c>
       <c r="B10" t="n">
         <v>98443</v>
@@ -1566,17 +1566,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700323</v>
+        <v>700344</v>
       </c>
       <c r="R10" t="n">
-        <v>7114124</v>
+        <v>7114307</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,18 +1633,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1639,61 +1656,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864699</v>
+        <v>126862629</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>80077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700344</v>
+        <v>700301</v>
       </c>
       <c r="R11" t="n">
-        <v>7114307</v>
+        <v>7114163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,19 +1735,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1871,45 +1871,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126865575</v>
+        <v>126867862</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700236</v>
+        <v>700364</v>
       </c>
       <c r="R13" t="n">
-        <v>7114234</v>
+        <v>7114084</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,18 +1962,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1972,7 +1985,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126867862</v>
+        <v>126867869</v>
       </c>
       <c r="B14" t="n">
         <v>98443</v>
@@ -2000,29 +2013,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700364</v>
+        <v>700339</v>
       </c>
       <c r="R14" t="n">
-        <v>7114084</v>
+        <v>7114086</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,7 +2064,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126867869</v>
+        <v>126863301</v>
       </c>
       <c r="B15" t="n">
         <v>98443</v>
@@ -2117,14 +2117,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700339</v>
+        <v>700307</v>
       </c>
       <c r="R15" t="n">
-        <v>7114086</v>
+        <v>7114151</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,12 +2171,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2187,32 +2187,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126863301</v>
+        <v>126863311</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700307</v>
+        <v>700340</v>
       </c>
       <c r="R16" t="n">
-        <v>7114151</v>
+        <v>7114337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126863311</v>
+        <v>126865575</v>
       </c>
       <c r="B17" t="n">
-        <v>92616</v>
+        <v>98360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,34 +2299,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700340</v>
+        <v>700236</v>
       </c>
       <c r="R17" t="n">
-        <v>7114337</v>
+        <v>7114234</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,12 +2373,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126864710</v>
+        <v>126865571</v>
       </c>
       <c r="B25" t="n">
-        <v>96696</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700302</v>
+        <v>700287</v>
       </c>
       <c r="R25" t="n">
-        <v>7114115</v>
+        <v>7114144</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3245,10 +3245,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126865571</v>
+        <v>126868157</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>40901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,34 +3256,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>102498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Silverfläckspraktmal</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Denisia stroemella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1779)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700287</v>
+        <v>700300</v>
       </c>
       <c r="R26" t="n">
-        <v>7114144</v>
+        <v>7114175</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,9 +3318,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,12 +3345,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3346,38 +3361,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126868157</v>
+        <v>126864739</v>
       </c>
       <c r="B27" t="n">
-        <v>40901</v>
+        <v>98443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102498</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Silverfläckspraktmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Denisia stroemella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1779)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3386,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700300</v>
+        <v>700286</v>
       </c>
       <c r="R27" t="n">
-        <v>7114175</v>
+        <v>7114214</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3419,19 +3433,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3446,12 +3450,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3462,49 +3466,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126864739</v>
+        <v>126864710</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700286</v>
+        <v>700302</v>
       </c>
       <c r="R28" t="n">
-        <v>7114214</v>
+        <v>7114115</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -4610,7 +4610,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126865569</v>
+        <v>126867882</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700198</v>
+        <v>700181</v>
       </c>
       <c r="R39" t="n">
-        <v>7114523</v>
+        <v>7114498</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,12 +4695,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126868146</v>
+        <v>126865569</v>
       </c>
       <c r="B40" t="n">
-        <v>41361</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4722,39 +4722,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>215713</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700294</v>
+        <v>700198</v>
       </c>
       <c r="R40" t="n">
-        <v>7114336</v>
+        <v>7114523</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,19 +4779,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4811,12 +4796,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4827,10 +4812,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126867882</v>
+        <v>126868146</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>41361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4838,34 +4823,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>215713</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700181</v>
+        <v>700294</v>
       </c>
       <c r="R41" t="n">
-        <v>7114498</v>
+        <v>7114336</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4895,9 +4885,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4912,12 +4912,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4928,45 +4928,57 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126865578</v>
+        <v>126864700</v>
       </c>
       <c r="B42" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700147</v>
+        <v>700265</v>
       </c>
       <c r="R42" t="n">
-        <v>7114536</v>
+        <v>7114403</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5007,6 +5019,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5018,7 +5031,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5029,32 +5042,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126865563</v>
+        <v>126865578</v>
       </c>
       <c r="B43" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5064,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700297</v>
+        <v>700147</v>
       </c>
       <c r="R43" t="n">
-        <v>7114112</v>
+        <v>7114536</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5130,7 +5143,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126864700</v>
+        <v>126865563</v>
       </c>
       <c r="B44" t="n">
         <v>98443</v>
@@ -5158,29 +5171,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700265</v>
+        <v>700297</v>
       </c>
       <c r="R44" t="n">
-        <v>7114403</v>
+        <v>7114112</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5221,7 +5222,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -8197,7 +8197,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126865566</v>
+        <v>126867860</v>
       </c>
       <c r="B73" t="n">
         <v>98443</v>
@@ -8225,17 +8225,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700281</v>
+        <v>700311</v>
       </c>
       <c r="R73" t="n">
-        <v>7114184</v>
+        <v>7114124</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8276,18 +8288,19 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8298,7 +8311,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126867860</v>
+        <v>126865566</v>
       </c>
       <c r="B74" t="n">
         <v>98443</v>
@@ -8326,29 +8339,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700311</v>
+        <v>700281</v>
       </c>
       <c r="R74" t="n">
-        <v>7114124</v>
+        <v>7114184</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8389,19 +8390,18 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126864745</v>
+        <v>126864711</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>96696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700325</v>
+        <v>700315</v>
       </c>
       <c r="R2" t="n">
-        <v>7114161</v>
+        <v>7114081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126864711</v>
+        <v>126864745</v>
       </c>
       <c r="B3" t="n">
-        <v>96696</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700315</v>
+        <v>700325</v>
       </c>
       <c r="R3" t="n">
-        <v>7114081</v>
+        <v>7114161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1326,48 +1326,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126851272</v>
+        <v>126862629</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>80077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700310</v>
+        <v>700301</v>
       </c>
       <c r="R8" t="n">
-        <v>7114176</v>
+        <v>7114163</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,19 +1394,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,12 +1411,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1437,7 +1427,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126867871</v>
+        <v>126851272</v>
       </c>
       <c r="B9" t="n">
         <v>98443</v>
@@ -1468,17 +1458,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700323</v>
+        <v>700310</v>
       </c>
       <c r="R9" t="n">
-        <v>7114124</v>
+        <v>7114176</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1505,9 +1495,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,12 +1522,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1538,7 +1538,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126864699</v>
+        <v>126867871</v>
       </c>
       <c r="B10" t="n">
         <v>98443</v>
@@ -1566,33 +1566,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700344</v>
+        <v>700323</v>
       </c>
       <c r="R10" t="n">
-        <v>7114307</v>
+        <v>7114124</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,19 +1617,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1656,45 +1639,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126862629</v>
+        <v>126864701</v>
       </c>
       <c r="B11" t="n">
-        <v>80077</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700301</v>
+        <v>700283</v>
       </c>
       <c r="R11" t="n">
-        <v>7114163</v>
+        <v>7114393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,18 +1730,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1757,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126864701</v>
+        <v>126864699</v>
       </c>
       <c r="B12" t="n">
         <v>98443</v>
@@ -1787,7 +1783,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1795,7 +1791,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700283</v>
+        <v>700344</v>
       </c>
       <c r="R12" t="n">
-        <v>7114393</v>
+        <v>7114307</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,57 +1871,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126867862</v>
+        <v>126863311</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700364</v>
+        <v>700340</v>
       </c>
       <c r="R13" t="n">
-        <v>7114084</v>
+        <v>7114337</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,19 +1950,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1985,7 +1972,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126867869</v>
+        <v>126867862</v>
       </c>
       <c r="B14" t="n">
         <v>98443</v>
@@ -2013,17 +2000,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700339</v>
+        <v>700364</v>
       </c>
       <c r="R14" t="n">
-        <v>7114086</v>
+        <v>7114084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,6 +2063,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,45 +2086,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126863301</v>
+        <v>126865575</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700307</v>
+        <v>700236</v>
       </c>
       <c r="R15" t="n">
-        <v>7114151</v>
+        <v>7114234</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,12 +2171,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2187,45 +2187,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126863311</v>
+        <v>126867869</v>
       </c>
       <c r="B16" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700340</v>
+        <v>700339</v>
       </c>
       <c r="R16" t="n">
-        <v>7114337</v>
+        <v>7114086</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,12 +2272,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2288,45 +2288,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126865575</v>
+        <v>126863301</v>
       </c>
       <c r="B17" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700236</v>
+        <v>700307</v>
       </c>
       <c r="R17" t="n">
-        <v>7114234</v>
+        <v>7114151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,12 +2373,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2389,32 +2389,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868136</v>
+        <v>126868126</v>
       </c>
       <c r="B18" t="n">
-        <v>96569</v>
+        <v>80117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700114</v>
+        <v>700245</v>
       </c>
       <c r="R18" t="n">
-        <v>7114614</v>
+        <v>7114154</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,6 +2480,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2500,32 +2515,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126868126</v>
+        <v>126868136</v>
       </c>
       <c r="B19" t="n">
-        <v>80117</v>
+        <v>96569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2535,13 +2550,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700245</v>
+        <v>700114</v>
       </c>
       <c r="R19" t="n">
-        <v>7114154</v>
+        <v>7114614</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2570,7 +2585,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2580,7 +2595,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,21 +2606,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2828,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126863310</v>
+        <v>126862588</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700290</v>
+        <v>700304</v>
       </c>
       <c r="R22" t="n">
-        <v>7114136</v>
+        <v>7114192</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,12 +2913,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126862588</v>
+        <v>126863310</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700304</v>
+        <v>700290</v>
       </c>
       <c r="R23" t="n">
-        <v>7114192</v>
+        <v>7114136</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,12 +3014,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126865571</v>
+        <v>126864710</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>96696</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700287</v>
+        <v>700302</v>
       </c>
       <c r="R25" t="n">
-        <v>7114144</v>
+        <v>7114115</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3245,10 +3245,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126868157</v>
+        <v>126865571</v>
       </c>
       <c r="B26" t="n">
-        <v>40901</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,39 +3256,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102498</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Silverfläckspraktmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Denisia stroemella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fabricius, 1779)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700300</v>
+        <v>700287</v>
       </c>
       <c r="R26" t="n">
-        <v>7114175</v>
+        <v>7114144</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,19 +3313,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,12 +3330,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3466,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126864710</v>
+        <v>126868157</v>
       </c>
       <c r="B28" t="n">
-        <v>96696</v>
+        <v>40901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,34 +3462,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>102498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Silverfläckspraktmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Denisia stroemella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1779)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700302</v>
+        <v>700300</v>
       </c>
       <c r="R28" t="n">
-        <v>7114115</v>
+        <v>7114175</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,9 +3524,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,12 +3551,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3567,7 +3567,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126868151</v>
+        <v>126865559</v>
       </c>
       <c r="B29" t="n">
         <v>98443</v>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700306</v>
+        <v>700330</v>
       </c>
       <c r="R29" t="n">
-        <v>7114337</v>
+        <v>7114328</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,19 +3635,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3662,12 +3652,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3678,32 +3668,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126865559</v>
+        <v>126864748</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3713,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700330</v>
+        <v>700220</v>
       </c>
       <c r="R30" t="n">
-        <v>7114328</v>
+        <v>7114448</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,7 +3758,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3779,45 +3769,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126864748</v>
+        <v>126862653</v>
       </c>
       <c r="B31" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700220</v>
+        <v>700319</v>
       </c>
       <c r="R31" t="n">
-        <v>7114448</v>
+        <v>7114336</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3864,12 +3854,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3880,7 +3870,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126862653</v>
+        <v>126868151</v>
       </c>
       <c r="B32" t="n">
         <v>98443</v>
@@ -3911,14 +3901,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700319</v>
+        <v>700306</v>
       </c>
       <c r="R32" t="n">
-        <v>7114336</v>
+        <v>7114337</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3948,9 +3938,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3965,12 +3965,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson, Liam Sebestyén</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3981,32 +3981,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126864706</v>
+        <v>126864698</v>
       </c>
       <c r="B33" t="n">
-        <v>98360</v>
+        <v>91326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700145</v>
+        <v>700320</v>
       </c>
       <c r="R33" t="n">
-        <v>7114540</v>
+        <v>7114182</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4193,32 +4193,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126864698</v>
+        <v>126864706</v>
       </c>
       <c r="B35" t="n">
-        <v>91326</v>
+        <v>98360</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700320</v>
+        <v>700145</v>
       </c>
       <c r="R35" t="n">
-        <v>7114182</v>
+        <v>7114540</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4610,10 +4610,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126867882</v>
+        <v>126868146</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>41361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4621,34 +4621,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>215713</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700181</v>
+        <v>700294</v>
       </c>
       <c r="R39" t="n">
-        <v>7114498</v>
+        <v>7114336</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,9 +4683,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4695,12 +4710,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4711,32 +4726,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126865569</v>
+        <v>126865563</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4761,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700198</v>
+        <v>700297</v>
       </c>
       <c r="R40" t="n">
-        <v>7114523</v>
+        <v>7114112</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4812,50 +4827,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126868146</v>
+        <v>126864700</v>
       </c>
       <c r="B41" t="n">
-        <v>41361</v>
+        <v>98443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>215713</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700294</v>
+        <v>700265</v>
       </c>
       <c r="R41" t="n">
-        <v>7114336</v>
+        <v>7114403</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4885,39 +4907,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4928,57 +4941,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126864700</v>
+        <v>126865578</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>98360</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700265</v>
+        <v>700147</v>
       </c>
       <c r="R42" t="n">
-        <v>7114403</v>
+        <v>7114536</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,7 +5020,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5042,32 +5042,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126865578</v>
+        <v>126867882</v>
       </c>
       <c r="B43" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700147</v>
+        <v>700181</v>
       </c>
       <c r="R43" t="n">
-        <v>7114536</v>
+        <v>7114498</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,12 +5127,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5143,32 +5143,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126865563</v>
+        <v>126865569</v>
       </c>
       <c r="B44" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5178,10 +5178,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700297</v>
+        <v>700198</v>
       </c>
       <c r="R44" t="n">
-        <v>7114112</v>
+        <v>7114523</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126868134</v>
+        <v>126864746</v>
       </c>
       <c r="B46" t="n">
-        <v>4772</v>
+        <v>98360</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5356,39 +5356,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700186</v>
+        <v>700240</v>
       </c>
       <c r="R46" t="n">
-        <v>7114499</v>
+        <v>7114242</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5418,21 +5413,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5441,36 +5426,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5592,10 +5557,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126864746</v>
+        <v>126868134</v>
       </c>
       <c r="B48" t="n">
-        <v>98360</v>
+        <v>4772</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,34 +5568,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700240</v>
+        <v>700186</v>
       </c>
       <c r="R48" t="n">
-        <v>7114242</v>
+        <v>7114499</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,11 +5630,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5673,16 +5653,36 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5693,57 +5693,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126864704</v>
+        <v>126863285</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700273</v>
+        <v>700344</v>
       </c>
       <c r="R49" t="n">
-        <v>7114229</v>
+        <v>7114335</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,12 +5778,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5806,49 +5794,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126864734</v>
+        <v>126868129</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>80153</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700263</v>
+        <v>700245</v>
       </c>
       <c r="R50" t="n">
-        <v>7114387</v>
+        <v>7114154</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5878,11 +5862,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5891,16 +5885,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5911,7 +5920,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126862656</v>
+        <v>126864734</v>
       </c>
       <c r="B51" t="n">
         <v>98443</v>
@@ -5939,17 +5948,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700320</v>
+        <v>700263</v>
       </c>
       <c r="R51" t="n">
-        <v>7114171</v>
+        <v>7114387</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,12 +6009,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad, Liam Sebestyén</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6012,7 +6025,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126864738</v>
+        <v>126862656</v>
       </c>
       <c r="B52" t="n">
         <v>98443</v>
@@ -6043,14 +6056,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700299</v>
+        <v>700320</v>
       </c>
       <c r="R52" t="n">
-        <v>7114327</v>
+        <v>7114171</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6097,12 +6110,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6113,7 +6126,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126865558</v>
+        <v>126864704</v>
       </c>
       <c r="B53" t="n">
         <v>98443</v>
@@ -6141,17 +6154,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700326</v>
+        <v>700273</v>
       </c>
       <c r="R53" t="n">
-        <v>7114352</v>
+        <v>7114229</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6203,7 +6228,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6214,32 +6239,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126868129</v>
+        <v>126864738</v>
       </c>
       <c r="B54" t="n">
-        <v>80153</v>
+        <v>98443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6249,10 +6274,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700245</v>
+        <v>700299</v>
       </c>
       <c r="R54" t="n">
-        <v>7114154</v>
+        <v>7114327</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6282,21 +6307,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6305,31 +6320,16 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6340,45 +6340,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126863285</v>
+        <v>126865558</v>
       </c>
       <c r="B55" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700344</v>
+        <v>700326</v>
       </c>
       <c r="R55" t="n">
-        <v>7114335</v>
+        <v>7114352</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6425,12 +6425,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6441,45 +6441,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126864708</v>
+        <v>126864680</v>
       </c>
       <c r="B56" t="n">
-        <v>92616</v>
+        <v>80117</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700253</v>
+        <v>700363</v>
       </c>
       <c r="R56" t="n">
-        <v>7114409</v>
+        <v>7114127</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6526,12 +6526,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6542,45 +6542,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126864680</v>
+        <v>126864708</v>
       </c>
       <c r="B57" t="n">
-        <v>80117</v>
+        <v>92616</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700363</v>
+        <v>700253</v>
       </c>
       <c r="R57" t="n">
-        <v>7114127</v>
+        <v>7114409</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6627,12 +6627,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6643,7 +6643,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126865564</v>
+        <v>126862657</v>
       </c>
       <c r="B58" t="n">
         <v>98443</v>
@@ -6674,14 +6674,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700282</v>
+        <v>700359</v>
       </c>
       <c r="R58" t="n">
-        <v>7114135</v>
+        <v>7114097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6728,12 +6728,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6744,7 +6744,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126862657</v>
+        <v>126863304</v>
       </c>
       <c r="B59" t="n">
         <v>98443</v>
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700359</v>
+        <v>700323</v>
       </c>
       <c r="R59" t="n">
-        <v>7114097</v>
+        <v>7114164</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6829,12 +6829,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson, Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6845,7 +6845,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126863304</v>
+        <v>126865567</v>
       </c>
       <c r="B60" t="n">
         <v>98443</v>
@@ -6876,14 +6876,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700323</v>
+        <v>700281</v>
       </c>
       <c r="R60" t="n">
-        <v>7114164</v>
+        <v>7114196</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6930,12 +6930,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6946,7 +6946,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126865567</v>
+        <v>126865564</v>
       </c>
       <c r="B61" t="n">
         <v>98443</v>
@@ -6981,10 +6981,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700281</v>
+        <v>700282</v>
       </c>
       <c r="R61" t="n">
-        <v>7114196</v>
+        <v>7114135</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126864719</v>
+        <v>126864724</v>
       </c>
       <c r="B63" t="n">
-        <v>98464</v>
+        <v>79038</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7160,21 +7160,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6434</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700137</v>
+        <v>700243</v>
       </c>
       <c r="R63" t="n">
-        <v>7114498</v>
+        <v>7114142</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7250,10 +7250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126864724</v>
+        <v>126864719</v>
       </c>
       <c r="B64" t="n">
-        <v>79038</v>
+        <v>98464</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7261,21 +7261,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6434</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700243</v>
+        <v>700137</v>
       </c>
       <c r="R64" t="n">
-        <v>7114142</v>
+        <v>7114498</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7351,48 +7351,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126864713</v>
+        <v>126864720</v>
       </c>
       <c r="B65" t="n">
-        <v>91684</v>
+        <v>80021</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700335</v>
+        <v>700382</v>
       </c>
       <c r="R65" t="n">
-        <v>7114031</v>
+        <v>7114108</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7433,7 +7430,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7567,45 +7563,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126864720</v>
+        <v>126864683</v>
       </c>
       <c r="B67" t="n">
-        <v>80021</v>
+        <v>98443</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700382</v>
+        <v>700345</v>
       </c>
       <c r="R67" t="n">
-        <v>7114108</v>
+        <v>7114314</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7640,6 +7636,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7652,12 +7653,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7668,7 +7669,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126864683</v>
+        <v>126862630</v>
       </c>
       <c r="B68" t="n">
         <v>98443</v>
@@ -7703,10 +7704,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700345</v>
+        <v>700326</v>
       </c>
       <c r="R68" t="n">
-        <v>7114314</v>
+        <v>7114161</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7741,29 +7742,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7774,10 +7771,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126862630</v>
+        <v>126864713</v>
       </c>
       <c r="B69" t="n">
-        <v>98443</v>
+        <v>91684</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7785,34 +7782,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700326</v>
+        <v>700335</v>
       </c>
       <c r="R69" t="n">
-        <v>7114161</v>
+        <v>7114031</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7860,12 +7860,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8197,7 +8197,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126867860</v>
+        <v>126865566</v>
       </c>
       <c r="B73" t="n">
         <v>98443</v>
@@ -8225,29 +8225,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700311</v>
+        <v>700281</v>
       </c>
       <c r="R73" t="n">
-        <v>7114124</v>
+        <v>7114184</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8288,19 +8276,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8311,7 +8298,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126865566</v>
+        <v>126867860</v>
       </c>
       <c r="B74" t="n">
         <v>98443</v>
@@ -8339,17 +8326,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700281</v>
+        <v>700311</v>
       </c>
       <c r="R74" t="n">
-        <v>7114184</v>
+        <v>7114124</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8390,18 +8389,19 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8412,32 +8412,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126865562</v>
+        <v>126868139</v>
       </c>
       <c r="B75" t="n">
-        <v>98443</v>
+        <v>96569</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700345</v>
+        <v>700112</v>
       </c>
       <c r="R75" t="n">
-        <v>7114076</v>
+        <v>7114619</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8480,9 +8480,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8497,12 +8507,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8513,32 +8523,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126868139</v>
+        <v>126865557</v>
       </c>
       <c r="B76" t="n">
-        <v>96569</v>
+        <v>98443</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8548,10 +8558,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700112</v>
+        <v>700328</v>
       </c>
       <c r="R76" t="n">
-        <v>7114619</v>
+        <v>7114346</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8581,19 +8591,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8608,12 +8608,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8624,7 +8624,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126865557</v>
+        <v>126865562</v>
       </c>
       <c r="B77" t="n">
         <v>98443</v>
@@ -8659,10 +8659,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700328</v>
+        <v>700345</v>
       </c>
       <c r="R77" t="n">
-        <v>7114346</v>
+        <v>7114076</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8834,48 +8834,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126856511</v>
+        <v>126864737</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700252</v>
+        <v>700304</v>
       </c>
       <c r="R79" t="n">
-        <v>7114157</v>
+        <v>7114381</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8902,19 +8902,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8929,12 +8919,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -9252,48 +9242,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126864737</v>
+        <v>126856511</v>
       </c>
       <c r="B83" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700304</v>
+        <v>700252</v>
       </c>
       <c r="R83" t="n">
-        <v>7114381</v>
+        <v>7114157</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9320,9 +9310,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9337,12 +9337,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126864711</v>
+        <v>126864745</v>
       </c>
       <c r="B2" t="n">
-        <v>96696</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700315</v>
+        <v>700325</v>
       </c>
       <c r="R2" t="n">
-        <v>7114081</v>
+        <v>7114161</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126864745</v>
+        <v>126864711</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>96696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700325</v>
+        <v>700315</v>
       </c>
       <c r="R3" t="n">
-        <v>7114161</v>
+        <v>7114081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1013,45 +1013,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126868144</v>
+        <v>126862651</v>
       </c>
       <c r="B5" t="n">
-        <v>97321</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700167</v>
+        <v>700266</v>
       </c>
       <c r="R5" t="n">
-        <v>7114511</v>
+        <v>7114350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,19 +1081,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,12 +1098,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1124,45 +1114,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126862651</v>
+        <v>126868144</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>97321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700266</v>
+        <v>700167</v>
       </c>
       <c r="R6" t="n">
-        <v>7114350</v>
+        <v>7114511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,9 +1182,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,12 +1209,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2389,32 +2389,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868126</v>
+        <v>126865568</v>
       </c>
       <c r="B18" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700245</v>
+        <v>700363</v>
       </c>
       <c r="R18" t="n">
-        <v>7114154</v>
+        <v>7114098</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,21 +2457,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2480,31 +2470,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2626,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126864725</v>
+        <v>126868126</v>
       </c>
       <c r="B20" t="n">
-        <v>79038</v>
+        <v>80117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2661,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700244</v>
+        <v>700245</v>
       </c>
       <c r="R20" t="n">
-        <v>7114210</v>
+        <v>7114154</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,11 +2669,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2707,16 +2692,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2727,32 +2727,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126865568</v>
+        <v>126864725</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>79038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700363</v>
+        <v>700244</v>
       </c>
       <c r="R21" t="n">
-        <v>7114098</v>
+        <v>7114210</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2828,45 +2828,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126862588</v>
+        <v>126867858</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700304</v>
+        <v>700318</v>
       </c>
       <c r="R22" t="n">
-        <v>7114192</v>
+        <v>7114179</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,18 +2919,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2929,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126863310</v>
+        <v>126862588</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2964,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700290</v>
+        <v>700304</v>
       </c>
       <c r="R23" t="n">
-        <v>7114136</v>
+        <v>7114192</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,12 +3027,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3030,57 +3043,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126867858</v>
+        <v>126863310</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700318</v>
+        <v>700290</v>
       </c>
       <c r="R24" t="n">
-        <v>7114179</v>
+        <v>7114136</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,19 +3122,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3981,32 +3981,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126864698</v>
+        <v>126864706</v>
       </c>
       <c r="B33" t="n">
-        <v>91326</v>
+        <v>98360</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700320</v>
+        <v>700145</v>
       </c>
       <c r="R33" t="n">
-        <v>7114182</v>
+        <v>7114540</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4082,48 +4082,60 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126852356</v>
+        <v>126864703</v>
       </c>
       <c r="B34" t="n">
-        <v>92616</v>
+        <v>98443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700344</v>
+        <v>700315</v>
       </c>
       <c r="R34" t="n">
-        <v>7114301</v>
+        <v>7114347</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4150,39 +4162,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4193,32 +4196,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126864706</v>
+        <v>126865556</v>
       </c>
       <c r="B35" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700145</v>
+        <v>700304</v>
       </c>
       <c r="R35" t="n">
-        <v>7114540</v>
+        <v>7114364</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,7 +4286,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4294,7 +4297,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126864703</v>
+        <v>126862654</v>
       </c>
       <c r="B36" t="n">
         <v>98443</v>
@@ -4322,29 +4325,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700315</v>
+        <v>700337</v>
       </c>
       <c r="R36" t="n">
-        <v>7114347</v>
+        <v>7114304</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,19 +4376,18 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4408,32 +4398,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126865556</v>
+        <v>126864698</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>91326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4443,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700304</v>
+        <v>700320</v>
       </c>
       <c r="R37" t="n">
-        <v>7114364</v>
+        <v>7114182</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4498,7 +4488,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4509,48 +4499,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126862654</v>
+        <v>126852356</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700337</v>
+        <v>700344</v>
       </c>
       <c r="R38" t="n">
-        <v>7114304</v>
+        <v>7114301</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4577,9 +4567,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4594,12 +4594,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4726,32 +4726,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126865563</v>
+        <v>126867882</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700297</v>
+        <v>700181</v>
       </c>
       <c r="R40" t="n">
-        <v>7114112</v>
+        <v>7114498</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,12 +4811,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4827,7 +4827,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126864700</v>
+        <v>126865563</v>
       </c>
       <c r="B41" t="n">
         <v>98443</v>
@@ -4855,29 +4855,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700265</v>
+        <v>700297</v>
       </c>
       <c r="R41" t="n">
-        <v>7114403</v>
+        <v>7114112</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4906,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4930,7 +4917,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4941,45 +4928,57 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126865578</v>
+        <v>126864700</v>
       </c>
       <c r="B42" t="n">
-        <v>98360</v>
+        <v>98443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700147</v>
+        <v>700265</v>
       </c>
       <c r="R42" t="n">
-        <v>7114536</v>
+        <v>7114403</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5020,6 +5019,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5042,32 +5042,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126867882</v>
+        <v>126865578</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700181</v>
+        <v>700147</v>
       </c>
       <c r="R43" t="n">
-        <v>7114498</v>
+        <v>7114536</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,12 +5127,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5345,48 +5345,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126864746</v>
+        <v>126854059</v>
       </c>
       <c r="B46" t="n">
-        <v>98360</v>
+        <v>91326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lappmyran, Lappmyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700240</v>
+        <v>700098</v>
       </c>
       <c r="R46" t="n">
-        <v>7114242</v>
+        <v>7114648</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5413,9 +5413,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5430,12 +5440,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5446,48 +5456,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126854059</v>
+        <v>126868134</v>
       </c>
       <c r="B47" t="n">
-        <v>91326</v>
+        <v>4772</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lappmyran, Lappmyran, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700098</v>
+        <v>700186</v>
       </c>
       <c r="R47" t="n">
-        <v>7114648</v>
+        <v>7114499</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5516,7 +5531,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5526,7 +5541,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5537,16 +5552,36 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5557,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126868134</v>
+        <v>126864746</v>
       </c>
       <c r="B48" t="n">
-        <v>4772</v>
+        <v>98360</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5568,39 +5603,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700186</v>
+        <v>700240</v>
       </c>
       <c r="R48" t="n">
-        <v>7114499</v>
+        <v>7114242</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5630,21 +5660,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5653,36 +5673,16 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -8725,56 +8725,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126864729</v>
+        <v>126856511</v>
       </c>
       <c r="B78" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700152</v>
+        <v>700252</v>
       </c>
       <c r="R78" t="n">
-        <v>7114491</v>
+        <v>7114157</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8801,9 +8793,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8818,12 +8820,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8834,45 +8836,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126864737</v>
+        <v>126864729</v>
       </c>
       <c r="B79" t="n">
-        <v>98443</v>
+        <v>58027</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700304</v>
+        <v>700152</v>
       </c>
       <c r="R79" t="n">
-        <v>7114381</v>
+        <v>7114491</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8924,7 +8934,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8935,7 +8945,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126867872</v>
+        <v>126864737</v>
       </c>
       <c r="B80" t="n">
         <v>98443</v>
@@ -8970,10 +8980,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700320</v>
+        <v>700304</v>
       </c>
       <c r="R80" t="n">
-        <v>7114336</v>
+        <v>7114381</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9020,12 +9030,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9036,7 +9046,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126867870</v>
+        <v>126867872</v>
       </c>
       <c r="B81" t="n">
         <v>98443</v>
@@ -9071,10 +9081,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700316</v>
+        <v>700320</v>
       </c>
       <c r="R81" t="n">
-        <v>7114065</v>
+        <v>7114336</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9137,7 +9147,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126864741</v>
+        <v>126867870</v>
       </c>
       <c r="B82" t="n">
         <v>98443</v>
@@ -9165,21 +9175,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700313</v>
+        <v>700316</v>
       </c>
       <c r="R82" t="n">
-        <v>7114166</v>
+        <v>7114065</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9226,12 +9232,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9242,48 +9248,52 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126856511</v>
+        <v>126864741</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700252</v>
+        <v>700313</v>
       </c>
       <c r="R83" t="n">
-        <v>7114157</v>
+        <v>7114166</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9310,19 +9320,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9337,12 +9337,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -5345,48 +5345,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126854059</v>
+        <v>126864746</v>
       </c>
       <c r="B46" t="n">
-        <v>91326</v>
+        <v>98360</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lappmyran, Lappmyran, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700098</v>
+        <v>700240</v>
       </c>
       <c r="R46" t="n">
-        <v>7114648</v>
+        <v>7114242</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5413,19 +5413,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5440,12 +5430,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5456,53 +5446,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126868134</v>
+        <v>126854059</v>
       </c>
       <c r="B47" t="n">
-        <v>4772</v>
+        <v>91326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lappmyran, Lappmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700186</v>
+        <v>700098</v>
       </c>
       <c r="R47" t="n">
-        <v>7114499</v>
+        <v>7114648</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5531,7 +5516,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5541,7 +5526,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5552,36 +5537,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5592,10 +5557,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126864746</v>
+        <v>126868134</v>
       </c>
       <c r="B48" t="n">
-        <v>98360</v>
+        <v>4772</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,34 +5568,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700240</v>
+        <v>700186</v>
       </c>
       <c r="R48" t="n">
-        <v>7114242</v>
+        <v>7114499</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,11 +5630,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5673,16 +5653,36 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5693,32 +5693,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126863285</v>
+        <v>126862656</v>
       </c>
       <c r="B49" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700344</v>
+        <v>700320</v>
       </c>
       <c r="R49" t="n">
-        <v>7114335</v>
+        <v>7114171</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5778,12 +5778,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5794,45 +5794,57 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126868129</v>
+        <v>126864704</v>
       </c>
       <c r="B50" t="n">
-        <v>80153</v>
+        <v>98443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700245</v>
+        <v>700273</v>
       </c>
       <c r="R50" t="n">
-        <v>7114154</v>
+        <v>7114229</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5862,21 +5874,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5885,31 +5887,16 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5920,7 +5907,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126864734</v>
+        <v>126864738</v>
       </c>
       <c r="B51" t="n">
         <v>98443</v>
@@ -5948,21 +5935,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700263</v>
+        <v>700299</v>
       </c>
       <c r="R51" t="n">
-        <v>7114387</v>
+        <v>7114327</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6025,7 +6008,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126862656</v>
+        <v>126865558</v>
       </c>
       <c r="B52" t="n">
         <v>98443</v>
@@ -6056,14 +6039,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700320</v>
+        <v>700326</v>
       </c>
       <c r="R52" t="n">
-        <v>7114171</v>
+        <v>7114352</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6110,12 +6093,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6126,7 +6109,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126864704</v>
+        <v>126864734</v>
       </c>
       <c r="B53" t="n">
         <v>98443</v>
@@ -6156,27 +6139,19 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700273</v>
+        <v>700263</v>
       </c>
       <c r="R53" t="n">
-        <v>7114229</v>
+        <v>7114387</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6228,7 +6203,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6239,45 +6214,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126864738</v>
+        <v>126863285</v>
       </c>
       <c r="B54" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700299</v>
+        <v>700344</v>
       </c>
       <c r="R54" t="n">
-        <v>7114327</v>
+        <v>7114335</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6324,12 +6299,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6340,32 +6315,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126865558</v>
+        <v>126868129</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>80153</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6375,10 +6350,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700326</v>
+        <v>700245</v>
       </c>
       <c r="R55" t="n">
-        <v>7114352</v>
+        <v>7114154</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6408,11 +6383,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6421,16 +6406,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -8725,48 +8725,56 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126856511</v>
+        <v>126864729</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700252</v>
+        <v>700152</v>
       </c>
       <c r="R78" t="n">
-        <v>7114157</v>
+        <v>7114491</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8793,19 +8801,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8820,12 +8818,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8836,53 +8834,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126864729</v>
+        <v>126864737</v>
       </c>
       <c r="B79" t="n">
-        <v>58027</v>
+        <v>98443</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700152</v>
+        <v>700304</v>
       </c>
       <c r="R79" t="n">
-        <v>7114491</v>
+        <v>7114381</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8934,7 +8924,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8945,7 +8935,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126864737</v>
+        <v>126867872</v>
       </c>
       <c r="B80" t="n">
         <v>98443</v>
@@ -8980,10 +8970,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700304</v>
+        <v>700320</v>
       </c>
       <c r="R80" t="n">
-        <v>7114381</v>
+        <v>7114336</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9030,12 +9020,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9046,7 +9036,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126867872</v>
+        <v>126867870</v>
       </c>
       <c r="B81" t="n">
         <v>98443</v>
@@ -9081,10 +9071,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700320</v>
+        <v>700316</v>
       </c>
       <c r="R81" t="n">
-        <v>7114336</v>
+        <v>7114065</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9147,7 +9137,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126867870</v>
+        <v>126864741</v>
       </c>
       <c r="B82" t="n">
         <v>98443</v>
@@ -9175,17 +9165,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700316</v>
+        <v>700313</v>
       </c>
       <c r="R82" t="n">
-        <v>7114065</v>
+        <v>7114166</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9232,12 +9226,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9248,52 +9242,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126864741</v>
+        <v>126856511</v>
       </c>
       <c r="B83" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700313</v>
+        <v>700252</v>
       </c>
       <c r="R83" t="n">
-        <v>7114166</v>
+        <v>7114157</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9320,9 +9310,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9337,12 +9337,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126864745</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126864711</v>
+        <v>126862651</v>
       </c>
       <c r="B3" t="n">
-        <v>96696</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700315</v>
+        <v>700266</v>
       </c>
       <c r="R3" t="n">
-        <v>7114081</v>
+        <v>7114350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126868122</v>
+        <v>126868144</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>97325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,39 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700332</v>
+        <v>700167</v>
       </c>
       <c r="R4" t="n">
-        <v>7114038</v>
+        <v>7114511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +947,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -962,7 +957,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,26 +968,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1013,45 +988,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126862651</v>
+        <v>126864711</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>96700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700266</v>
+        <v>700315</v>
       </c>
       <c r="R5" t="n">
-        <v>7114350</v>
+        <v>7114081</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,12 +1073,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1114,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868144</v>
+        <v>126868122</v>
       </c>
       <c r="B6" t="n">
-        <v>97321</v>
+        <v>4773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,34 +1100,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700167</v>
+        <v>700332</v>
       </c>
       <c r="R6" t="n">
-        <v>7114511</v>
+        <v>7114038</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1164,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,7 +1174,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,6 +1185,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1228,7 +1228,7 @@
         <v>126864750</v>
       </c>
       <c r="B7" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,48 +1326,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126862629</v>
+        <v>126851272</v>
       </c>
       <c r="B8" t="n">
-        <v>80077</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700301</v>
+        <v>700310</v>
       </c>
       <c r="R8" t="n">
-        <v>7114163</v>
+        <v>7114176</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,9 +1394,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,12 +1421,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1427,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126851272</v>
+        <v>126867871</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,17 +1468,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700310</v>
+        <v>700323</v>
       </c>
       <c r="R9" t="n">
-        <v>7114176</v>
+        <v>7114124</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,19 +1505,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,12 +1522,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126867871</v>
+        <v>126864701</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,17 +1566,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700323</v>
+        <v>700283</v>
       </c>
       <c r="R10" t="n">
-        <v>7114124</v>
+        <v>7114393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,18 +1629,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1639,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864701</v>
+        <v>126864699</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,7 +1682,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1677,7 +1690,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1686,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700283</v>
+        <v>700344</v>
       </c>
       <c r="R11" t="n">
-        <v>7114393</v>
+        <v>7114307</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,61 +1770,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126864699</v>
+        <v>126862629</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>80081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700344</v>
+        <v>700301</v>
       </c>
       <c r="R12" t="n">
-        <v>7114307</v>
+        <v>7114163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,19 +1849,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1874,7 +1874,7 @@
         <v>126863311</v>
       </c>
       <c r="B13" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,57 +1972,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126867862</v>
+        <v>126865575</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700364</v>
+        <v>700236</v>
       </c>
       <c r="R14" t="n">
-        <v>7114084</v>
+        <v>7114234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,19 +2051,18 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2086,45 +2073,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126865575</v>
+        <v>126867862</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700236</v>
+        <v>700364</v>
       </c>
       <c r="R15" t="n">
-        <v>7114234</v>
+        <v>7114084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,18 +2164,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2190,7 +2190,7 @@
         <v>126867869</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>126863301</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>126865568</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>126868136</v>
       </c>
       <c r="B19" t="n">
-        <v>96569</v>
+        <v>96573</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>126868126</v>
       </c>
       <c r="B20" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>126864725</v>
       </c>
       <c r="B21" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>126867858</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>126862588</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>126863310</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>126864710</v>
       </c>
       <c r="B25" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>126865571</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3346,37 +3346,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126864739</v>
+        <v>126868157</v>
       </c>
       <c r="B27" t="n">
-        <v>98443</v>
+        <v>40905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Silverfläckspraktmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Denisia stroemella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Fabricius, 1779)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3385,10 +3386,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700286</v>
+        <v>700300</v>
       </c>
       <c r="R27" t="n">
-        <v>7114214</v>
+        <v>7114175</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,9 +3419,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,12 +3446,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3451,38 +3462,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126868157</v>
+        <v>126864739</v>
       </c>
       <c r="B28" t="n">
-        <v>40901</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silverfläckspraktmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Denisia stroemella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1779)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3491,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700300</v>
+        <v>700286</v>
       </c>
       <c r="R28" t="n">
-        <v>7114175</v>
+        <v>7114214</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,19 +3534,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,12 +3551,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3567,32 +3567,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126865559</v>
+        <v>126864748</v>
       </c>
       <c r="B29" t="n">
-        <v>98443</v>
+        <v>98364</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700330</v>
+        <v>700220</v>
       </c>
       <c r="R29" t="n">
-        <v>7114328</v>
+        <v>7114448</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3668,45 +3668,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126864748</v>
+        <v>126862653</v>
       </c>
       <c r="B30" t="n">
-        <v>98360</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700220</v>
+        <v>700319</v>
       </c>
       <c r="R30" t="n">
-        <v>7114448</v>
+        <v>7114336</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,12 +3753,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3769,10 +3769,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126862653</v>
+        <v>126868151</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,14 +3800,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700319</v>
+        <v>700306</v>
       </c>
       <c r="R31" t="n">
-        <v>7114336</v>
+        <v>7114337</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,9 +3837,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3854,12 +3864,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3870,10 +3880,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126868151</v>
+        <v>126865559</v>
       </c>
       <c r="B32" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3905,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700306</v>
+        <v>700330</v>
       </c>
       <c r="R32" t="n">
-        <v>7114337</v>
+        <v>7114328</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3938,19 +3948,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3965,12 +3965,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3981,32 +3981,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126864706</v>
+        <v>126864698</v>
       </c>
       <c r="B33" t="n">
-        <v>98360</v>
+        <v>91330</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700145</v>
+        <v>700320</v>
       </c>
       <c r="R33" t="n">
-        <v>7114540</v>
+        <v>7114182</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4082,60 +4082,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126864703</v>
+        <v>126852356</v>
       </c>
       <c r="B34" t="n">
-        <v>98443</v>
+        <v>92620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700315</v>
+        <v>700344</v>
       </c>
       <c r="R34" t="n">
-        <v>7114347</v>
+        <v>7114301</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4162,30 +4150,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4196,32 +4193,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126865556</v>
+        <v>126864706</v>
       </c>
       <c r="B35" t="n">
-        <v>98443</v>
+        <v>98364</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700304</v>
+        <v>700145</v>
       </c>
       <c r="R35" t="n">
-        <v>7114364</v>
+        <v>7114540</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4286,7 +4283,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4297,10 +4294,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126862654</v>
+        <v>126864703</v>
       </c>
       <c r="B36" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4325,17 +4322,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700337</v>
+        <v>700315</v>
       </c>
       <c r="R36" t="n">
-        <v>7114304</v>
+        <v>7114347</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4376,18 +4385,19 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4398,32 +4408,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126864698</v>
+        <v>126865556</v>
       </c>
       <c r="B37" t="n">
-        <v>91326</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4433,10 +4443,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700320</v>
+        <v>700304</v>
       </c>
       <c r="R37" t="n">
-        <v>7114182</v>
+        <v>7114364</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4488,7 +4498,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4499,48 +4509,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126852356</v>
+        <v>126862654</v>
       </c>
       <c r="B38" t="n">
-        <v>92616</v>
+        <v>98447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700344</v>
+        <v>700337</v>
       </c>
       <c r="R38" t="n">
-        <v>7114301</v>
+        <v>7114304</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4567,19 +4577,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4594,12 +4594,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4610,10 +4610,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126868146</v>
+        <v>126867882</v>
       </c>
       <c r="B39" t="n">
-        <v>41361</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4621,39 +4621,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>215713</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700294</v>
+        <v>700181</v>
       </c>
       <c r="R39" t="n">
-        <v>7114336</v>
+        <v>7114498</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4683,19 +4678,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4710,12 +4695,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4726,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126867882</v>
+        <v>126865569</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4761,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700181</v>
+        <v>700198</v>
       </c>
       <c r="R40" t="n">
-        <v>7114498</v>
+        <v>7114523</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,12 +4796,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4827,45 +4812,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126865563</v>
+        <v>126868146</v>
       </c>
       <c r="B41" t="n">
-        <v>98443</v>
+        <v>41365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>215713</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700297</v>
+        <v>700294</v>
       </c>
       <c r="R41" t="n">
-        <v>7114112</v>
+        <v>7114336</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4895,9 +4885,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4912,12 +4912,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4928,57 +4928,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126864700</v>
+        <v>126865578</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>98364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700265</v>
+        <v>700147</v>
       </c>
       <c r="R42" t="n">
-        <v>7114403</v>
+        <v>7114536</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,7 +5007,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5031,7 +5018,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5042,32 +5029,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126865578</v>
+        <v>126865563</v>
       </c>
       <c r="B43" t="n">
-        <v>98360</v>
+        <v>98447</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5077,10 +5064,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700147</v>
+        <v>700297</v>
       </c>
       <c r="R43" t="n">
-        <v>7114536</v>
+        <v>7114112</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5143,45 +5130,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126865569</v>
+        <v>126864700</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700198</v>
+        <v>700265</v>
       </c>
       <c r="R44" t="n">
-        <v>7114523</v>
+        <v>7114403</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5222,6 +5221,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5247,7 +5247,7 @@
         <v>126864733</v>
       </c>
       <c r="B45" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5345,48 +5345,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126864746</v>
+        <v>126854059</v>
       </c>
       <c r="B46" t="n">
-        <v>98360</v>
+        <v>91330</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lappmyran, Lappmyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700240</v>
+        <v>700098</v>
       </c>
       <c r="R46" t="n">
-        <v>7114242</v>
+        <v>7114648</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5413,9 +5413,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5430,12 +5440,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5446,48 +5456,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126854059</v>
+        <v>126868134</v>
       </c>
       <c r="B47" t="n">
-        <v>91326</v>
+        <v>4773</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lappmyran, Lappmyran, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700098</v>
+        <v>700186</v>
       </c>
       <c r="R47" t="n">
-        <v>7114648</v>
+        <v>7114499</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5516,7 +5531,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5526,7 +5541,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5537,16 +5552,36 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5557,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126868134</v>
+        <v>126864746</v>
       </c>
       <c r="B48" t="n">
-        <v>4772</v>
+        <v>98364</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5568,39 +5603,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700186</v>
+        <v>700240</v>
       </c>
       <c r="R48" t="n">
-        <v>7114499</v>
+        <v>7114242</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5630,21 +5660,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5653,36 +5673,16 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5696,7 +5696,7 @@
         <v>126862656</v>
       </c>
       <c r="B49" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>126864704</v>
       </c>
       <c r="B50" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>126864738</v>
       </c>
       <c r="B51" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6008,10 +6008,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126865558</v>
+        <v>126864734</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6036,17 +6036,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700326</v>
+        <v>700263</v>
       </c>
       <c r="R52" t="n">
-        <v>7114352</v>
+        <v>7114387</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6098,7 +6102,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6109,10 +6113,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126864734</v>
+        <v>126865558</v>
       </c>
       <c r="B53" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6137,21 +6141,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700263</v>
+        <v>700326</v>
       </c>
       <c r="R53" t="n">
-        <v>7114387</v>
+        <v>7114352</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6214,45 +6214,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126863285</v>
+        <v>126868129</v>
       </c>
       <c r="B54" t="n">
-        <v>57817</v>
+        <v>80157</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700344</v>
+        <v>700245</v>
       </c>
       <c r="R54" t="n">
-        <v>7114335</v>
+        <v>7114154</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6282,11 +6282,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6295,16 +6305,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6315,45 +6340,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126868129</v>
+        <v>126863285</v>
       </c>
       <c r="B55" t="n">
-        <v>80153</v>
+        <v>57821</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700245</v>
+        <v>700344</v>
       </c>
       <c r="R55" t="n">
-        <v>7114154</v>
+        <v>7114335</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6383,21 +6408,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6406,31 +6421,16 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6441,45 +6441,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126864680</v>
+        <v>126864708</v>
       </c>
       <c r="B56" t="n">
-        <v>80117</v>
+        <v>92620</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700363</v>
+        <v>700253</v>
       </c>
       <c r="R56" t="n">
-        <v>7114127</v>
+        <v>7114409</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6526,12 +6526,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6542,45 +6542,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126864708</v>
+        <v>126864680</v>
       </c>
       <c r="B57" t="n">
-        <v>92616</v>
+        <v>80121</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700253</v>
+        <v>700363</v>
       </c>
       <c r="R57" t="n">
-        <v>7114409</v>
+        <v>7114127</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6627,12 +6627,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6643,10 +6643,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126862657</v>
+        <v>126865567</v>
       </c>
       <c r="B58" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6674,14 +6674,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700359</v>
+        <v>700281</v>
       </c>
       <c r="R58" t="n">
-        <v>7114097</v>
+        <v>7114196</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6728,12 +6728,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6744,10 +6744,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126863304</v>
+        <v>126865564</v>
       </c>
       <c r="B59" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6775,14 +6775,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700323</v>
+        <v>700282</v>
       </c>
       <c r="R59" t="n">
-        <v>7114164</v>
+        <v>7114135</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6829,12 +6829,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6845,10 +6845,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126865567</v>
+        <v>126862657</v>
       </c>
       <c r="B60" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6876,14 +6876,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700281</v>
+        <v>700359</v>
       </c>
       <c r="R60" t="n">
-        <v>7114196</v>
+        <v>7114097</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6930,12 +6930,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6946,10 +6946,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126865564</v>
+        <v>126863304</v>
       </c>
       <c r="B61" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6977,14 +6977,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700282</v>
+        <v>700323</v>
       </c>
       <c r="R61" t="n">
-        <v>7114135</v>
+        <v>7114164</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7031,12 +7031,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7050,7 +7050,7 @@
         <v>126864687</v>
       </c>
       <c r="B62" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>126864724</v>
       </c>
       <c r="B63" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>126864719</v>
       </c>
       <c r="B64" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7351,45 +7351,49 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126864720</v>
+        <v>126864736</v>
       </c>
       <c r="B65" t="n">
-        <v>80021</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700382</v>
+        <v>700346</v>
       </c>
       <c r="R65" t="n">
-        <v>7114108</v>
+        <v>7114313</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7430,6 +7434,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7441,7 +7446,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7452,48 +7457,60 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126851658</v>
+        <v>126864702</v>
       </c>
       <c r="B66" t="n">
-        <v>80117</v>
+        <v>98447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700243</v>
+        <v>700301</v>
       </c>
       <c r="R66" t="n">
-        <v>7114171</v>
+        <v>7114357</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7520,39 +7537,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7566,7 +7574,7 @@
         <v>126864683</v>
       </c>
       <c r="B67" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7672,7 +7680,7 @@
         <v>126862630</v>
       </c>
       <c r="B68" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7771,51 +7779,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126864713</v>
+        <v>126851658</v>
       </c>
       <c r="B69" t="n">
-        <v>91684</v>
+        <v>80121</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700335</v>
+        <v>700243</v>
       </c>
       <c r="R69" t="n">
-        <v>7114031</v>
+        <v>7114171</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7842,30 +7847,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7876,49 +7890,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126864736</v>
+        <v>126864720</v>
       </c>
       <c r="B70" t="n">
-        <v>98443</v>
+        <v>80025</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700346</v>
+        <v>700382</v>
       </c>
       <c r="R70" t="n">
-        <v>7114313</v>
+        <v>7114108</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7959,7 +7969,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7971,7 +7980,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7982,10 +7991,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126864702</v>
+        <v>126864713</v>
       </c>
       <c r="B71" t="n">
-        <v>98443</v>
+        <v>91688</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7993,35 +8002,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700301</v>
+        <v>700335</v>
       </c>
       <c r="R71" t="n">
-        <v>7114357</v>
+        <v>7114031</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8096,32 +8096,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126865572</v>
+        <v>126865566</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700229</v>
+        <v>700281</v>
       </c>
       <c r="R72" t="n">
-        <v>7114231</v>
+        <v>7114184</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8197,10 +8197,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126865566</v>
+        <v>126867860</v>
       </c>
       <c r="B73" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8225,17 +8225,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700281</v>
+        <v>700311</v>
       </c>
       <c r="R73" t="n">
-        <v>7114184</v>
+        <v>7114124</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8276,18 +8288,19 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8298,57 +8311,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126867860</v>
+        <v>126865572</v>
       </c>
       <c r="B74" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700311</v>
+        <v>700229</v>
       </c>
       <c r="R74" t="n">
-        <v>7114124</v>
+        <v>7114231</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8389,19 +8390,18 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8412,32 +8412,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126868139</v>
+        <v>126865557</v>
       </c>
       <c r="B75" t="n">
-        <v>96569</v>
+        <v>98447</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700112</v>
+        <v>700328</v>
       </c>
       <c r="R75" t="n">
-        <v>7114619</v>
+        <v>7114346</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8480,19 +8480,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8507,12 +8497,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8523,32 +8513,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126865557</v>
+        <v>126868139</v>
       </c>
       <c r="B76" t="n">
-        <v>98443</v>
+        <v>96573</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8558,10 +8548,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700328</v>
+        <v>700112</v>
       </c>
       <c r="R76" t="n">
-        <v>7114346</v>
+        <v>7114619</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8591,9 +8581,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8608,12 +8608,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8627,7 +8627,7 @@
         <v>126865562</v>
       </c>
       <c r="B77" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8725,56 +8725,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126864729</v>
+        <v>126856511</v>
       </c>
       <c r="B78" t="n">
-        <v>58027</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700152</v>
+        <v>700252</v>
       </c>
       <c r="R78" t="n">
-        <v>7114491</v>
+        <v>7114157</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8801,9 +8793,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8818,12 +8820,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8837,7 +8839,7 @@
         <v>126864737</v>
       </c>
       <c r="B79" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8938,7 +8940,7 @@
         <v>126867872</v>
       </c>
       <c r="B80" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9039,7 +9041,7 @@
         <v>126867870</v>
       </c>
       <c r="B81" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9140,7 +9142,7 @@
         <v>126864741</v>
       </c>
       <c r="B82" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9242,48 +9244,56 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126856511</v>
+        <v>126864729</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>58031</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700252</v>
+        <v>700152</v>
       </c>
       <c r="R83" t="n">
-        <v>7114157</v>
+        <v>7114491</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9310,19 +9320,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9337,12 +9337,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9356,7 +9356,7 @@
         <v>126862652</v>
       </c>
       <c r="B84" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126864745</v>
+        <v>126864711</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>96700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700325</v>
+        <v>700315</v>
       </c>
       <c r="R2" t="n">
-        <v>7114161</v>
+        <v>7114081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126862651</v>
+        <v>126864745</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700266</v>
+        <v>700325</v>
       </c>
       <c r="R3" t="n">
-        <v>7114350</v>
+        <v>7114161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126868144</v>
+        <v>126868122</v>
       </c>
       <c r="B4" t="n">
-        <v>97325</v>
+        <v>4773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +888,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700167</v>
+        <v>700332</v>
       </c>
       <c r="R4" t="n">
-        <v>7114511</v>
+        <v>7114038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,7 +952,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -957,7 +962,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -968,6 +973,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -988,45 +1013,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126864711</v>
+        <v>126862651</v>
       </c>
       <c r="B5" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700315</v>
+        <v>700266</v>
       </c>
       <c r="R5" t="n">
-        <v>7114081</v>
+        <v>7114350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,12 +1098,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1089,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868122</v>
+        <v>126868144</v>
       </c>
       <c r="B6" t="n">
-        <v>4773</v>
+        <v>97325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,39 +1125,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700332</v>
+        <v>700167</v>
       </c>
       <c r="R6" t="n">
-        <v>7114038</v>
+        <v>7114511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1174,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,26 +1205,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126864750</v>
+        <v>126862629</v>
       </c>
       <c r="B7" t="n">
-        <v>98364</v>
+        <v>80081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,34 +1236,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700151</v>
+        <v>700301</v>
       </c>
       <c r="R7" t="n">
-        <v>7114492</v>
+        <v>7114163</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1326,48 +1326,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126851272</v>
+        <v>126864750</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700310</v>
+        <v>700151</v>
       </c>
       <c r="R8" t="n">
-        <v>7114176</v>
+        <v>7114492</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,19 +1394,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,12 +1411,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1437,7 +1427,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126867871</v>
+        <v>126851272</v>
       </c>
       <c r="B9" t="n">
         <v>98447</v>
@@ -1468,17 +1458,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700323</v>
+        <v>700310</v>
       </c>
       <c r="R9" t="n">
-        <v>7114124</v>
+        <v>7114176</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1505,9 +1495,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,12 +1522,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1538,7 +1538,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126864701</v>
+        <v>126867871</v>
       </c>
       <c r="B10" t="n">
         <v>98447</v>
@@ -1566,29 +1566,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700283</v>
+        <v>700323</v>
       </c>
       <c r="R10" t="n">
-        <v>7114393</v>
+        <v>7114124</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,19 +1617,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1652,7 +1639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864699</v>
+        <v>126864701</v>
       </c>
       <c r="B11" t="n">
         <v>98447</v>
@@ -1682,7 +1669,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1690,11 +1677,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1703,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700344</v>
+        <v>700283</v>
       </c>
       <c r="R11" t="n">
-        <v>7114307</v>
+        <v>7114393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,45 +1753,61 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126862629</v>
+        <v>126864699</v>
       </c>
       <c r="B12" t="n">
-        <v>80081</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700301</v>
+        <v>700344</v>
       </c>
       <c r="R12" t="n">
-        <v>7114163</v>
+        <v>7114307</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,18 +1848,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1972,45 +1972,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126865575</v>
+        <v>126867862</v>
       </c>
       <c r="B14" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700236</v>
+        <v>700364</v>
       </c>
       <c r="R14" t="n">
-        <v>7114234</v>
+        <v>7114084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,18 +2063,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2073,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126867862</v>
+        <v>126867869</v>
       </c>
       <c r="B15" t="n">
         <v>98447</v>
@@ -2101,29 +2114,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700364</v>
+        <v>700339</v>
       </c>
       <c r="R15" t="n">
-        <v>7114084</v>
+        <v>7114086</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2165,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126867869</v>
+        <v>126863301</v>
       </c>
       <c r="B16" t="n">
         <v>98447</v>
@@ -2218,14 +2218,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700339</v>
+        <v>700307</v>
       </c>
       <c r="R16" t="n">
-        <v>7114086</v>
+        <v>7114151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,12 +2272,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2288,45 +2288,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126863301</v>
+        <v>126865575</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700307</v>
+        <v>700236</v>
       </c>
       <c r="R17" t="n">
-        <v>7114151</v>
+        <v>7114234</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,12 +2373,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2389,32 +2389,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126865568</v>
+        <v>126864725</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>79042</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700363</v>
+        <v>700244</v>
       </c>
       <c r="R18" t="n">
-        <v>7114098</v>
+        <v>7114210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2490,32 +2490,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126868136</v>
+        <v>126865568</v>
       </c>
       <c r="B19" t="n">
-        <v>96573</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700114</v>
+        <v>700363</v>
       </c>
       <c r="R19" t="n">
-        <v>7114614</v>
+        <v>7114098</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2558,19 +2558,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2585,12 +2575,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2601,32 +2591,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126868126</v>
+        <v>126868136</v>
       </c>
       <c r="B20" t="n">
-        <v>80121</v>
+        <v>96573</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,13 +2626,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700245</v>
+        <v>700114</v>
       </c>
       <c r="R20" t="n">
-        <v>7114154</v>
+        <v>7114614</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2692,21 +2682,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2727,32 +2702,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126864725</v>
+        <v>126868126</v>
       </c>
       <c r="B21" t="n">
-        <v>79042</v>
+        <v>80121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2762,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700244</v>
+        <v>700245</v>
       </c>
       <c r="R21" t="n">
-        <v>7114210</v>
+        <v>7114154</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,11 +2770,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2808,16 +2793,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2828,57 +2828,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126867858</v>
+        <v>126863310</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700318</v>
+        <v>700290</v>
       </c>
       <c r="R22" t="n">
-        <v>7114179</v>
+        <v>7114136</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,19 +2907,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2942,45 +2929,57 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126862588</v>
+        <v>126867858</v>
       </c>
       <c r="B23" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700304</v>
+        <v>700318</v>
       </c>
       <c r="R23" t="n">
-        <v>7114192</v>
+        <v>7114179</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3021,18 +3020,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3043,10 +3043,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126863310</v>
+        <v>126862588</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3054,21 +3054,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700290</v>
+        <v>700304</v>
       </c>
       <c r="R24" t="n">
-        <v>7114136</v>
+        <v>7114192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3128,12 +3128,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126864710</v>
+        <v>126865571</v>
       </c>
       <c r="B25" t="n">
-        <v>96700</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700302</v>
+        <v>700287</v>
       </c>
       <c r="R25" t="n">
-        <v>7114115</v>
+        <v>7114144</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3245,45 +3245,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126865571</v>
+        <v>126864739</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700287</v>
+        <v>700286</v>
       </c>
       <c r="R26" t="n">
-        <v>7114144</v>
+        <v>7114214</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,7 +3339,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3346,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126868157</v>
+        <v>126864710</v>
       </c>
       <c r="B27" t="n">
-        <v>40905</v>
+        <v>96700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3357,39 +3361,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102498</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Silverfläckspraktmal</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Denisia stroemella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1779)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700300</v>
+        <v>700302</v>
       </c>
       <c r="R27" t="n">
-        <v>7114175</v>
+        <v>7114115</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3419,19 +3418,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3446,12 +3435,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3462,37 +3451,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126864739</v>
+        <v>126868157</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>40905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Silverfläckspraktmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Denisia stroemella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Fabricius, 1779)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3501,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700286</v>
+        <v>700300</v>
       </c>
       <c r="R28" t="n">
-        <v>7114214</v>
+        <v>7114175</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,9 +3524,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,12 +3551,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -4610,32 +4610,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126867882</v>
+        <v>126865563</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700181</v>
+        <v>700297</v>
       </c>
       <c r="R39" t="n">
-        <v>7114498</v>
+        <v>7114112</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,12 +4695,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4711,45 +4711,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126865569</v>
+        <v>126864700</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700198</v>
+        <v>700265</v>
       </c>
       <c r="R40" t="n">
-        <v>7114523</v>
+        <v>7114403</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4790,6 +4802,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4801,7 +4814,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4928,32 +4941,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126865578</v>
+        <v>126867882</v>
       </c>
       <c r="B42" t="n">
-        <v>98364</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4963,10 +4976,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700147</v>
+        <v>700181</v>
       </c>
       <c r="R42" t="n">
-        <v>7114536</v>
+        <v>7114498</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5013,12 +5026,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5029,32 +5042,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126865563</v>
+        <v>126865569</v>
       </c>
       <c r="B43" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5064,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700297</v>
+        <v>700198</v>
       </c>
       <c r="R43" t="n">
-        <v>7114112</v>
+        <v>7114523</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5130,57 +5143,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126864700</v>
+        <v>126865578</v>
       </c>
       <c r="B44" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700265</v>
+        <v>700147</v>
       </c>
       <c r="R44" t="n">
-        <v>7114403</v>
+        <v>7114536</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5221,7 +5222,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126868134</v>
+        <v>126864746</v>
       </c>
       <c r="B47" t="n">
-        <v>4773</v>
+        <v>98364</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5467,39 +5467,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700186</v>
+        <v>700240</v>
       </c>
       <c r="R47" t="n">
-        <v>7114499</v>
+        <v>7114242</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5529,21 +5524,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5552,36 +5537,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5592,10 +5557,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126864746</v>
+        <v>126868134</v>
       </c>
       <c r="B48" t="n">
-        <v>98364</v>
+        <v>4773</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,34 +5568,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700240</v>
+        <v>700186</v>
       </c>
       <c r="R48" t="n">
-        <v>7114242</v>
+        <v>7114499</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,11 +5630,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5673,16 +5653,36 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6214,45 +6214,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126868129</v>
+        <v>126863285</v>
       </c>
       <c r="B54" t="n">
-        <v>80157</v>
+        <v>57821</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700245</v>
+        <v>700344</v>
       </c>
       <c r="R54" t="n">
-        <v>7114154</v>
+        <v>7114335</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6282,21 +6282,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6305,31 +6295,16 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6340,45 +6315,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126863285</v>
+        <v>126868129</v>
       </c>
       <c r="B55" t="n">
-        <v>57821</v>
+        <v>80157</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700344</v>
+        <v>700245</v>
       </c>
       <c r="R55" t="n">
-        <v>7114335</v>
+        <v>7114154</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6408,11 +6383,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6421,16 +6406,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -7047,45 +7047,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126864687</v>
+        <v>126864719</v>
       </c>
       <c r="B62" t="n">
-        <v>82859</v>
+        <v>98468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700348</v>
+        <v>700137</v>
       </c>
       <c r="R62" t="n">
-        <v>7114044</v>
+        <v>7114498</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7126,19 +7126,18 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7149,45 +7148,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126864724</v>
+        <v>126864687</v>
       </c>
       <c r="B63" t="n">
-        <v>79042</v>
+        <v>82859</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700243</v>
+        <v>700348</v>
       </c>
       <c r="R63" t="n">
-        <v>7114142</v>
+        <v>7114044</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7228,18 +7227,19 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7250,10 +7250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126864719</v>
+        <v>126864724</v>
       </c>
       <c r="B64" t="n">
-        <v>98468</v>
+        <v>79042</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7261,21 +7261,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6434</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700137</v>
+        <v>700243</v>
       </c>
       <c r="R64" t="n">
-        <v>7114498</v>
+        <v>7114142</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7351,52 +7351,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126864736</v>
+        <v>126851658</v>
       </c>
       <c r="B65" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700346</v>
+        <v>700243</v>
       </c>
       <c r="R65" t="n">
-        <v>7114313</v>
+        <v>7114171</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7423,30 +7419,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7457,57 +7462,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126864702</v>
+        <v>126864720</v>
       </c>
       <c r="B66" t="n">
-        <v>98447</v>
+        <v>80025</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700301</v>
+        <v>700382</v>
       </c>
       <c r="R66" t="n">
-        <v>7114357</v>
+        <v>7114108</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7548,7 +7541,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7560,7 +7552,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7571,7 +7563,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126864683</v>
+        <v>126864736</v>
       </c>
       <c r="B67" t="n">
         <v>98447</v>
@@ -7600,16 +7592,20 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700345</v>
+        <v>700346</v>
       </c>
       <c r="R67" t="n">
-        <v>7114314</v>
+        <v>7114313</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7644,29 +7640,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7677,7 +7669,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126862630</v>
+        <v>126864702</v>
       </c>
       <c r="B68" t="n">
         <v>98447</v>
@@ -7705,17 +7697,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700326</v>
+        <v>700301</v>
       </c>
       <c r="R68" t="n">
-        <v>7114161</v>
+        <v>7114357</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7763,12 +7767,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7779,48 +7783,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126851658</v>
+        <v>126864683</v>
       </c>
       <c r="B69" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700243</v>
+        <v>700345</v>
       </c>
       <c r="R69" t="n">
-        <v>7114171</v>
+        <v>7114314</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7847,19 +7851,14 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:37</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7874,12 +7873,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7890,45 +7889,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126864720</v>
+        <v>126862630</v>
       </c>
       <c r="B70" t="n">
-        <v>80025</v>
+        <v>98447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700382</v>
+        <v>700326</v>
       </c>
       <c r="R70" t="n">
-        <v>7114108</v>
+        <v>7114161</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7969,18 +7968,19 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8096,32 +8096,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126865566</v>
+        <v>126865572</v>
       </c>
       <c r="B72" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700281</v>
+        <v>700229</v>
       </c>
       <c r="R72" t="n">
-        <v>7114184</v>
+        <v>7114231</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8197,7 +8197,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126867860</v>
+        <v>126865566</v>
       </c>
       <c r="B73" t="n">
         <v>98447</v>
@@ -8225,29 +8225,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700311</v>
+        <v>700281</v>
       </c>
       <c r="R73" t="n">
-        <v>7114124</v>
+        <v>7114184</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8288,19 +8276,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8311,45 +8298,57 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126865572</v>
+        <v>126867860</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700229</v>
+        <v>700311</v>
       </c>
       <c r="R74" t="n">
-        <v>7114231</v>
+        <v>7114124</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8390,18 +8389,19 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8412,32 +8412,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126865557</v>
+        <v>126868139</v>
       </c>
       <c r="B75" t="n">
-        <v>98447</v>
+        <v>96573</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700328</v>
+        <v>700112</v>
       </c>
       <c r="R75" t="n">
-        <v>7114346</v>
+        <v>7114619</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8480,9 +8480,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8497,12 +8507,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8513,32 +8523,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126868139</v>
+        <v>126865557</v>
       </c>
       <c r="B76" t="n">
-        <v>96573</v>
+        <v>98447</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8548,10 +8558,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700112</v>
+        <v>700328</v>
       </c>
       <c r="R76" t="n">
-        <v>7114619</v>
+        <v>7114346</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8581,19 +8591,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8608,12 +8608,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8836,45 +8836,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126864737</v>
+        <v>126864729</v>
       </c>
       <c r="B79" t="n">
-        <v>98447</v>
+        <v>58031</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700304</v>
+        <v>700152</v>
       </c>
       <c r="R79" t="n">
-        <v>7114381</v>
+        <v>7114491</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8926,7 +8934,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8937,7 +8945,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126867872</v>
+        <v>126864737</v>
       </c>
       <c r="B80" t="n">
         <v>98447</v>
@@ -8972,10 +8980,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700320</v>
+        <v>700304</v>
       </c>
       <c r="R80" t="n">
-        <v>7114336</v>
+        <v>7114381</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9022,12 +9030,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9038,7 +9046,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126867870</v>
+        <v>126867872</v>
       </c>
       <c r="B81" t="n">
         <v>98447</v>
@@ -9073,10 +9081,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700316</v>
+        <v>700320</v>
       </c>
       <c r="R81" t="n">
-        <v>7114065</v>
+        <v>7114336</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9139,7 +9147,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126864741</v>
+        <v>126867870</v>
       </c>
       <c r="B82" t="n">
         <v>98447</v>
@@ -9167,21 +9175,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700313</v>
+        <v>700316</v>
       </c>
       <c r="R82" t="n">
-        <v>7114166</v>
+        <v>7114065</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9228,12 +9232,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9244,53 +9248,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126864729</v>
+        <v>126864741</v>
       </c>
       <c r="B83" t="n">
-        <v>58031</v>
+        <v>98447</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700152</v>
+        <v>700313</v>
       </c>
       <c r="R83" t="n">
-        <v>7114491</v>
+        <v>7114166</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -1972,57 +1972,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126867862</v>
+        <v>126865575</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700364</v>
+        <v>700236</v>
       </c>
       <c r="R14" t="n">
-        <v>7114084</v>
+        <v>7114234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2063,19 +2051,18 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2086,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126867869</v>
+        <v>126867862</v>
       </c>
       <c r="B15" t="n">
         <v>98447</v>
@@ -2114,17 +2101,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700339</v>
+        <v>700364</v>
       </c>
       <c r="R15" t="n">
-        <v>7114086</v>
+        <v>7114084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,6 +2164,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126863301</v>
+        <v>126867869</v>
       </c>
       <c r="B16" t="n">
         <v>98447</v>
@@ -2218,14 +2218,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700307</v>
+        <v>700339</v>
       </c>
       <c r="R16" t="n">
-        <v>7114151</v>
+        <v>7114086</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,12 +2272,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2288,45 +2288,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126865575</v>
+        <v>126863301</v>
       </c>
       <c r="B17" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700236</v>
+        <v>700307</v>
       </c>
       <c r="R17" t="n">
-        <v>7114234</v>
+        <v>7114151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,12 +2373,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2389,32 +2389,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126864725</v>
+        <v>126868126</v>
       </c>
       <c r="B18" t="n">
-        <v>79042</v>
+        <v>80121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700244</v>
+        <v>700245</v>
       </c>
       <c r="R18" t="n">
-        <v>7114210</v>
+        <v>7114154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,11 +2457,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2470,16 +2480,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2490,32 +2515,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126865568</v>
+        <v>126868136</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>96573</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2525,13 +2550,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700363</v>
+        <v>700114</v>
       </c>
       <c r="R19" t="n">
-        <v>7114098</v>
+        <v>7114614</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2558,9 +2583,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2575,12 +2610,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2591,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126868136</v>
+        <v>126864725</v>
       </c>
       <c r="B20" t="n">
-        <v>96573</v>
+        <v>79042</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,21 +2637,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,13 +2661,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700114</v>
+        <v>700244</v>
       </c>
       <c r="R20" t="n">
-        <v>7114614</v>
+        <v>7114210</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2659,19 +2694,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,12 +2711,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2702,32 +2727,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126868126</v>
+        <v>126865568</v>
       </c>
       <c r="B21" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700245</v>
+        <v>700363</v>
       </c>
       <c r="R21" t="n">
-        <v>7114154</v>
+        <v>7114098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,21 +2795,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2793,31 +2808,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2828,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126863310</v>
+        <v>126862588</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700290</v>
+        <v>700304</v>
       </c>
       <c r="R22" t="n">
-        <v>7114136</v>
+        <v>7114192</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,12 +2913,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2929,57 +2929,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126867858</v>
+        <v>126863310</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700318</v>
+        <v>700290</v>
       </c>
       <c r="R23" t="n">
-        <v>7114179</v>
+        <v>7114136</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,19 +3008,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3043,45 +3030,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126862588</v>
+        <v>126867858</v>
       </c>
       <c r="B24" t="n">
-        <v>91330</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700304</v>
+        <v>700318</v>
       </c>
       <c r="R24" t="n">
-        <v>7114192</v>
+        <v>7114179</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,18 +3121,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126864745</v>
+        <v>126862651</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700325</v>
+        <v>700266</v>
       </c>
       <c r="R3" t="n">
-        <v>7114161</v>
+        <v>7114350</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126868122</v>
+        <v>126868144</v>
       </c>
       <c r="B4" t="n">
-        <v>4773</v>
+        <v>97325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,39 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700332</v>
+        <v>700167</v>
       </c>
       <c r="R4" t="n">
-        <v>7114038</v>
+        <v>7114511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,7 +947,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -962,7 +957,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,26 +968,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1013,45 +988,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126862651</v>
+        <v>126864745</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700266</v>
+        <v>700325</v>
       </c>
       <c r="R5" t="n">
-        <v>7114350</v>
+        <v>7114161</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,12 +1073,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1114,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868144</v>
+        <v>126868122</v>
       </c>
       <c r="B6" t="n">
-        <v>97325</v>
+        <v>4773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,34 +1100,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700167</v>
+        <v>700332</v>
       </c>
       <c r="R6" t="n">
-        <v>7114511</v>
+        <v>7114038</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1164,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1194,7 +1174,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,6 +1185,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126863311</v>
+        <v>126865575</v>
       </c>
       <c r="B13" t="n">
-        <v>92620</v>
+        <v>98364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1882,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700340</v>
+        <v>700236</v>
       </c>
       <c r="R13" t="n">
-        <v>7114337</v>
+        <v>7114234</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1972,45 +1972,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126865575</v>
+        <v>126867862</v>
       </c>
       <c r="B14" t="n">
-        <v>98364</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700236</v>
+        <v>700364</v>
       </c>
       <c r="R14" t="n">
-        <v>7114234</v>
+        <v>7114084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,18 +2063,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2073,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126867862</v>
+        <v>126867869</v>
       </c>
       <c r="B15" t="n">
         <v>98447</v>
@@ -2101,29 +2114,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700364</v>
+        <v>700339</v>
       </c>
       <c r="R15" t="n">
-        <v>7114084</v>
+        <v>7114086</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2165,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126867869</v>
+        <v>126863301</v>
       </c>
       <c r="B16" t="n">
         <v>98447</v>
@@ -2218,14 +2218,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700339</v>
+        <v>700307</v>
       </c>
       <c r="R16" t="n">
-        <v>7114086</v>
+        <v>7114151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,12 +2272,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2288,32 +2288,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126863301</v>
+        <v>126863311</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>92620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700307</v>
+        <v>700340</v>
       </c>
       <c r="R17" t="n">
-        <v>7114151</v>
+        <v>7114337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,32 +2389,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868126</v>
+        <v>126864725</v>
       </c>
       <c r="B18" t="n">
-        <v>80121</v>
+        <v>79042</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700245</v>
+        <v>700244</v>
       </c>
       <c r="R18" t="n">
-        <v>7114154</v>
+        <v>7114210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,21 +2457,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2480,31 +2470,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2515,32 +2490,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126868136</v>
+        <v>126865568</v>
       </c>
       <c r="B19" t="n">
-        <v>96573</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2550,13 +2525,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700114</v>
+        <v>700363</v>
       </c>
       <c r="R19" t="n">
-        <v>7114614</v>
+        <v>7114098</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2583,19 +2558,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2610,12 +2575,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2626,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126864725</v>
+        <v>126868136</v>
       </c>
       <c r="B20" t="n">
-        <v>79042</v>
+        <v>96573</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2661,13 +2626,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700244</v>
+        <v>700114</v>
       </c>
       <c r="R20" t="n">
-        <v>7114210</v>
+        <v>7114614</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2694,9 +2659,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,12 +2686,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2727,32 +2702,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126865568</v>
+        <v>126868126</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2762,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700363</v>
+        <v>700245</v>
       </c>
       <c r="R21" t="n">
-        <v>7114098</v>
+        <v>7114154</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,11 +2770,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2808,16 +2793,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126865571</v>
+        <v>126864710</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>96700</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700287</v>
+        <v>700302</v>
       </c>
       <c r="R25" t="n">
-        <v>7114144</v>
+        <v>7114115</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3245,49 +3245,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126864739</v>
+        <v>126865571</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700286</v>
+        <v>700287</v>
       </c>
       <c r="R26" t="n">
-        <v>7114214</v>
+        <v>7114144</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,7 +3335,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3350,10 +3346,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126864710</v>
+        <v>126868157</v>
       </c>
       <c r="B27" t="n">
-        <v>96700</v>
+        <v>40905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,34 +3357,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>102498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Silverfläckspraktmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Denisia stroemella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1779)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700302</v>
+        <v>700300</v>
       </c>
       <c r="R27" t="n">
-        <v>7114115</v>
+        <v>7114175</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,9 +3419,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,12 +3446,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3451,38 +3462,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126868157</v>
+        <v>126864739</v>
       </c>
       <c r="B28" t="n">
-        <v>40905</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silverfläckspraktmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Denisia stroemella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1779)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3491,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700300</v>
+        <v>700286</v>
       </c>
       <c r="R28" t="n">
-        <v>7114175</v>
+        <v>7114214</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,19 +3534,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,12 +3551,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3981,48 +3981,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126864698</v>
+        <v>126852356</v>
       </c>
       <c r="B33" t="n">
-        <v>91330</v>
+        <v>92620</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700320</v>
+        <v>700344</v>
       </c>
       <c r="R33" t="n">
-        <v>7114182</v>
+        <v>7114301</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4049,9 +4049,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,12 +4076,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4082,48 +4092,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126852356</v>
+        <v>126864698</v>
       </c>
       <c r="B34" t="n">
-        <v>92620</v>
+        <v>91330</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700344</v>
+        <v>700320</v>
       </c>
       <c r="R34" t="n">
-        <v>7114301</v>
+        <v>7114182</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4150,19 +4160,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4177,12 +4177,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4825,10 +4825,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126868146</v>
+        <v>126867882</v>
       </c>
       <c r="B41" t="n">
-        <v>41365</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4836,39 +4836,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>215713</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700294</v>
+        <v>700181</v>
       </c>
       <c r="R41" t="n">
-        <v>7114336</v>
+        <v>7114498</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4898,19 +4893,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4925,12 +4910,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4941,7 +4926,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126867882</v>
+        <v>126865569</v>
       </c>
       <c r="B42" t="n">
         <v>79018</v>
@@ -4976,10 +4961,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700181</v>
+        <v>700198</v>
       </c>
       <c r="R42" t="n">
-        <v>7114498</v>
+        <v>7114523</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5026,12 +5011,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5042,10 +5027,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126865569</v>
+        <v>126868146</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>41365</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5053,34 +5038,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>215713</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700198</v>
+        <v>700294</v>
       </c>
       <c r="R43" t="n">
-        <v>7114523</v>
+        <v>7114336</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5110,9 +5100,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5127,12 +5127,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5456,10 +5456,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126864746</v>
+        <v>126868134</v>
       </c>
       <c r="B47" t="n">
-        <v>98364</v>
+        <v>4773</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5467,34 +5467,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700240</v>
+        <v>700186</v>
       </c>
       <c r="R47" t="n">
-        <v>7114242</v>
+        <v>7114499</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5524,11 +5529,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5537,16 +5552,36 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5557,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126868134</v>
+        <v>126864746</v>
       </c>
       <c r="B48" t="n">
-        <v>4773</v>
+        <v>98364</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5568,39 +5603,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700186</v>
+        <v>700240</v>
       </c>
       <c r="R48" t="n">
-        <v>7114499</v>
+        <v>7114242</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5630,21 +5660,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5653,36 +5673,16 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -7351,48 +7351,52 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126851658</v>
+        <v>126864736</v>
       </c>
       <c r="B65" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700243</v>
+        <v>700346</v>
       </c>
       <c r="R65" t="n">
-        <v>7114171</v>
+        <v>7114313</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7419,39 +7423,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7462,45 +7457,57 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126864720</v>
+        <v>126864702</v>
       </c>
       <c r="B66" t="n">
-        <v>80025</v>
+        <v>98447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700382</v>
+        <v>700301</v>
       </c>
       <c r="R66" t="n">
-        <v>7114108</v>
+        <v>7114357</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7541,6 +7548,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7552,7 +7560,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7563,7 +7571,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126864736</v>
+        <v>126864683</v>
       </c>
       <c r="B67" t="n">
         <v>98447</v>
@@ -7592,20 +7600,16 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700346</v>
+        <v>700345</v>
       </c>
       <c r="R67" t="n">
-        <v>7114313</v>
+        <v>7114314</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7640,25 +7644,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7669,7 +7677,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126864702</v>
+        <v>126862630</v>
       </c>
       <c r="B68" t="n">
         <v>98447</v>
@@ -7697,29 +7705,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700301</v>
+        <v>700326</v>
       </c>
       <c r="R68" t="n">
-        <v>7114357</v>
+        <v>7114161</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7767,12 +7763,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7783,10 +7779,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126864683</v>
+        <v>126864713</v>
       </c>
       <c r="B69" t="n">
-        <v>98447</v>
+        <v>91688</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7794,34 +7790,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700345</v>
+        <v>700335</v>
       </c>
       <c r="R69" t="n">
-        <v>7114314</v>
+        <v>7114031</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7856,29 +7855,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7889,48 +7884,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126862630</v>
+        <v>126851658</v>
       </c>
       <c r="B70" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700326</v>
+        <v>700243</v>
       </c>
       <c r="R70" t="n">
-        <v>7114161</v>
+        <v>7114171</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7957,30 +7952,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7991,48 +7995,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126864713</v>
+        <v>126864720</v>
       </c>
       <c r="B71" t="n">
-        <v>91688</v>
+        <v>80025</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700335</v>
+        <v>700382</v>
       </c>
       <c r="R71" t="n">
-        <v>7114031</v>
+        <v>7114108</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8073,7 +8074,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126862651</v>
+        <v>126864745</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700266</v>
+        <v>700325</v>
       </c>
       <c r="R3" t="n">
-        <v>7114350</v>
+        <v>7114161</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,45 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126868144</v>
+        <v>126862651</v>
       </c>
       <c r="B4" t="n">
-        <v>97325</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700167</v>
+        <v>700266</v>
       </c>
       <c r="R4" t="n">
-        <v>7114511</v>
+        <v>7114350</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,19 +945,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -988,45 +978,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126864745</v>
+        <v>126868122</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>4773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700325</v>
+        <v>700332</v>
       </c>
       <c r="R5" t="n">
-        <v>7114161</v>
+        <v>7114038</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,11 +1051,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1069,16 +1074,36 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1089,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868122</v>
+        <v>126868144</v>
       </c>
       <c r="B6" t="n">
-        <v>4773</v>
+        <v>97325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,39 +1125,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700332</v>
+        <v>700167</v>
       </c>
       <c r="R6" t="n">
-        <v>7114038</v>
+        <v>7114511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1174,7 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,26 +1205,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1225,48 +1225,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126862629</v>
+        <v>126851272</v>
       </c>
       <c r="B7" t="n">
-        <v>80081</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700301</v>
+        <v>700310</v>
       </c>
       <c r="R7" t="n">
-        <v>7114163</v>
+        <v>7114176</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,9 +1293,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,12 +1320,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1326,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126864750</v>
+        <v>126867871</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700151</v>
+        <v>700323</v>
       </c>
       <c r="R8" t="n">
-        <v>7114492</v>
+        <v>7114124</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,12 +1421,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1427,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126851272</v>
+        <v>126864699</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,20 +1465,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700310</v>
+        <v>700344</v>
       </c>
       <c r="R9" t="n">
-        <v>7114176</v>
+        <v>7114307</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,39 +1521,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1538,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126867871</v>
+        <v>126864701</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,17 +1583,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700323</v>
+        <v>700283</v>
       </c>
       <c r="R10" t="n">
-        <v>7114124</v>
+        <v>7114393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,18 +1646,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1639,57 +1669,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864701</v>
+        <v>126864750</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700283</v>
+        <v>700151</v>
       </c>
       <c r="R11" t="n">
-        <v>7114393</v>
+        <v>7114492</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1748,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1742,7 +1759,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1753,61 +1770,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126864699</v>
+        <v>126862629</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>80081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700344</v>
+        <v>700301</v>
       </c>
       <c r="R12" t="n">
-        <v>7114307</v>
+        <v>7114163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,19 +1849,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126865575</v>
+        <v>126863311</v>
       </c>
       <c r="B13" t="n">
-        <v>98364</v>
+        <v>92620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1882,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700236</v>
+        <v>700340</v>
       </c>
       <c r="R13" t="n">
-        <v>7114234</v>
+        <v>7114337</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1975,7 +1975,7 @@
         <v>126867862</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,32 +2086,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126867869</v>
+        <v>126865575</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700339</v>
+        <v>700236</v>
       </c>
       <c r="R15" t="n">
-        <v>7114086</v>
+        <v>7114234</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,12 +2171,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126863301</v>
+        <v>126867869</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,14 +2218,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700307</v>
+        <v>700339</v>
       </c>
       <c r="R16" t="n">
-        <v>7114151</v>
+        <v>7114086</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,12 +2272,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2288,32 +2288,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126863311</v>
+        <v>126863301</v>
       </c>
       <c r="B17" t="n">
-        <v>92620</v>
+        <v>98448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700340</v>
+        <v>700307</v>
       </c>
       <c r="R17" t="n">
-        <v>7114337</v>
+        <v>7114151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126864725</v>
+        <v>126868136</v>
       </c>
       <c r="B18" t="n">
-        <v>79042</v>
+        <v>96573</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,21 +2400,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700244</v>
+        <v>700114</v>
       </c>
       <c r="R18" t="n">
-        <v>7114210</v>
+        <v>7114614</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2457,9 +2457,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,12 +2484,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2490,32 +2500,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126865568</v>
+        <v>126868126</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2525,10 +2535,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700363</v>
+        <v>700245</v>
       </c>
       <c r="R19" t="n">
-        <v>7114098</v>
+        <v>7114154</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,11 +2568,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2571,16 +2591,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2591,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126868136</v>
+        <v>126864725</v>
       </c>
       <c r="B20" t="n">
-        <v>96573</v>
+        <v>79042</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,21 +2637,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,13 +2661,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700114</v>
+        <v>700244</v>
       </c>
       <c r="R20" t="n">
-        <v>7114614</v>
+        <v>7114210</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2659,19 +2694,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,12 +2711,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2702,32 +2727,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126868126</v>
+        <v>126865568</v>
       </c>
       <c r="B21" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700245</v>
+        <v>700363</v>
       </c>
       <c r="R21" t="n">
-        <v>7114154</v>
+        <v>7114098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,21 +2795,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2793,31 +2808,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3033,7 +3033,7 @@
         <v>126867858</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,45 +3245,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126865571</v>
+        <v>126864739</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700287</v>
+        <v>700286</v>
       </c>
       <c r="R26" t="n">
-        <v>7114144</v>
+        <v>7114214</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,7 +3339,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3346,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126868157</v>
+        <v>126865571</v>
       </c>
       <c r="B27" t="n">
-        <v>40905</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3357,39 +3361,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102498</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Silverfläckspraktmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Denisia stroemella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1779)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700300</v>
+        <v>700287</v>
       </c>
       <c r="R27" t="n">
-        <v>7114175</v>
+        <v>7114144</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3419,19 +3418,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3446,12 +3435,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum, Alva Danielsson, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3462,37 +3451,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126864739</v>
+        <v>126868157</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>40905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>102498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Silverfläckspraktmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Denisia stroemella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Fabricius, 1779)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3501,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700286</v>
+        <v>700300</v>
       </c>
       <c r="R28" t="n">
-        <v>7114214</v>
+        <v>7114175</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,9 +3524,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,12 +3551,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3570,7 +3570,7 @@
         <v>126864748</v>
       </c>
       <c r="B29" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>126862653</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3772,7 +3772,7 @@
         <v>126868151</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3883,7 +3883,7 @@
         <v>126865559</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4092,32 +4092,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126864698</v>
+        <v>126864706</v>
       </c>
       <c r="B34" t="n">
-        <v>91330</v>
+        <v>98365</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700320</v>
+        <v>700145</v>
       </c>
       <c r="R34" t="n">
-        <v>7114182</v>
+        <v>7114540</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4193,32 +4193,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126864706</v>
+        <v>126865556</v>
       </c>
       <c r="B35" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700145</v>
+        <v>700304</v>
       </c>
       <c r="R35" t="n">
-        <v>7114540</v>
+        <v>7114364</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4294,10 +4294,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126864703</v>
+        <v>126862654</v>
       </c>
       <c r="B36" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4322,29 +4322,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700315</v>
+        <v>700337</v>
       </c>
       <c r="R36" t="n">
-        <v>7114347</v>
+        <v>7114304</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,19 +4373,18 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4408,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126865556</v>
+        <v>126864703</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4436,17 +4423,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700304</v>
+        <v>700315</v>
       </c>
       <c r="R37" t="n">
-        <v>7114364</v>
+        <v>7114347</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4487,6 +4486,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4509,45 +4509,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126862654</v>
+        <v>126864698</v>
       </c>
       <c r="B38" t="n">
-        <v>98447</v>
+        <v>91330</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700337</v>
+        <v>700320</v>
       </c>
       <c r="R38" t="n">
-        <v>7114304</v>
+        <v>7114182</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,12 +4594,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4610,32 +4610,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126865563</v>
+        <v>126867882</v>
       </c>
       <c r="B39" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700297</v>
+        <v>700181</v>
       </c>
       <c r="R39" t="n">
-        <v>7114112</v>
+        <v>7114498</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,12 +4695,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4711,57 +4711,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126864700</v>
+        <v>126865569</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700265</v>
+        <v>700198</v>
       </c>
       <c r="R40" t="n">
-        <v>7114403</v>
+        <v>7114523</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4802,7 +4790,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4814,7 +4801,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4825,10 +4812,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126867882</v>
+        <v>126868146</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>41365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4836,34 +4823,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>215713</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700181</v>
+        <v>700294</v>
       </c>
       <c r="R41" t="n">
-        <v>7114498</v>
+        <v>7114336</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4893,9 +4885,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4910,12 +4912,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4926,32 +4928,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126865569</v>
+        <v>126865578</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>98365</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4961,10 +4963,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700198</v>
+        <v>700147</v>
       </c>
       <c r="R42" t="n">
-        <v>7114523</v>
+        <v>7114536</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5027,50 +5029,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126868146</v>
+        <v>126865563</v>
       </c>
       <c r="B43" t="n">
-        <v>41365</v>
+        <v>98448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>215713</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700294</v>
+        <v>700297</v>
       </c>
       <c r="R43" t="n">
-        <v>7114336</v>
+        <v>7114112</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,19 +5097,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5127,12 +5114,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5143,45 +5130,57 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126865578</v>
+        <v>126864700</v>
       </c>
       <c r="B44" t="n">
-        <v>98364</v>
+        <v>98448</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700147</v>
+        <v>700265</v>
       </c>
       <c r="R44" t="n">
-        <v>7114536</v>
+        <v>7114403</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5222,6 +5221,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5247,7 +5247,7 @@
         <v>126864733</v>
       </c>
       <c r="B45" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5345,48 +5345,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126854059</v>
+        <v>126868134</v>
       </c>
       <c r="B46" t="n">
-        <v>91330</v>
+        <v>4773</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lappmyran, Lappmyran, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700098</v>
+        <v>700186</v>
       </c>
       <c r="R46" t="n">
-        <v>7114648</v>
+        <v>7114499</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5415,7 +5420,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5425,7 +5430,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5436,16 +5441,36 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5456,10 +5481,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126868134</v>
+        <v>126864746</v>
       </c>
       <c r="B47" t="n">
-        <v>4773</v>
+        <v>98365</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5467,39 +5492,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700186</v>
+        <v>700240</v>
       </c>
       <c r="R47" t="n">
-        <v>7114499</v>
+        <v>7114242</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5529,21 +5549,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5552,36 +5562,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5592,48 +5582,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126864746</v>
+        <v>126854059</v>
       </c>
       <c r="B48" t="n">
-        <v>98364</v>
+        <v>91330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lappmyran, Lappmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700240</v>
+        <v>700098</v>
       </c>
       <c r="R48" t="n">
-        <v>7114242</v>
+        <v>7114648</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5660,9 +5650,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5677,12 +5677,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5693,32 +5693,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126862656</v>
+        <v>126863285</v>
       </c>
       <c r="B49" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700320</v>
+        <v>700344</v>
       </c>
       <c r="R49" t="n">
-        <v>7114171</v>
+        <v>7114335</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5778,12 +5778,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5794,10 +5794,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126864704</v>
+        <v>126862656</v>
       </c>
       <c r="B50" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5822,29 +5822,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700273</v>
+        <v>700320</v>
       </c>
       <c r="R50" t="n">
-        <v>7114229</v>
+        <v>7114171</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5891,12 +5879,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5907,10 +5895,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126864738</v>
+        <v>126864704</v>
       </c>
       <c r="B51" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5935,17 +5923,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700299</v>
+        <v>700273</v>
       </c>
       <c r="R51" t="n">
-        <v>7114327</v>
+        <v>7114229</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6011,7 +6011,7 @@
         <v>126864734</v>
       </c>
       <c r="B52" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6113,32 +6113,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126865558</v>
+        <v>126868129</v>
       </c>
       <c r="B53" t="n">
-        <v>98447</v>
+        <v>80157</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700326</v>
+        <v>700245</v>
       </c>
       <c r="R53" t="n">
-        <v>7114352</v>
+        <v>7114154</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6181,11 +6181,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6194,16 +6204,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6214,45 +6239,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126863285</v>
+        <v>126864738</v>
       </c>
       <c r="B54" t="n">
-        <v>57821</v>
+        <v>98448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700344</v>
+        <v>700299</v>
       </c>
       <c r="R54" t="n">
-        <v>7114335</v>
+        <v>7114327</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6299,12 +6324,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6315,32 +6340,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126868129</v>
+        <v>126865558</v>
       </c>
       <c r="B55" t="n">
-        <v>80157</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6350,10 +6375,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700245</v>
+        <v>700326</v>
       </c>
       <c r="R55" t="n">
-        <v>7114154</v>
+        <v>7114352</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6383,21 +6408,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6406,31 +6421,16 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6441,32 +6441,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126864708</v>
+        <v>126865564</v>
       </c>
       <c r="B56" t="n">
-        <v>92620</v>
+        <v>98448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6476,10 +6476,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700253</v>
+        <v>700282</v>
       </c>
       <c r="R56" t="n">
-        <v>7114409</v>
+        <v>7114135</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6542,45 +6542,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126864680</v>
+        <v>126864708</v>
       </c>
       <c r="B57" t="n">
-        <v>80121</v>
+        <v>92620</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700363</v>
+        <v>700253</v>
       </c>
       <c r="R57" t="n">
-        <v>7114127</v>
+        <v>7114409</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6627,12 +6627,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6643,45 +6643,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126865567</v>
+        <v>126864680</v>
       </c>
       <c r="B58" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700281</v>
+        <v>700363</v>
       </c>
       <c r="R58" t="n">
-        <v>7114196</v>
+        <v>7114127</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6728,12 +6728,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6744,10 +6744,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126865564</v>
+        <v>126865567</v>
       </c>
       <c r="B59" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700282</v>
+        <v>700281</v>
       </c>
       <c r="R59" t="n">
-        <v>7114135</v>
+        <v>7114196</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6848,7 +6848,7 @@
         <v>126862657</v>
       </c>
       <c r="B60" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>126863304</v>
       </c>
       <c r="B61" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7047,45 +7047,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126864719</v>
+        <v>126864687</v>
       </c>
       <c r="B62" t="n">
-        <v>98468</v>
+        <v>82859</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700137</v>
+        <v>700348</v>
       </c>
       <c r="R62" t="n">
-        <v>7114498</v>
+        <v>7114044</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7126,18 +7126,19 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7148,45 +7149,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126864687</v>
+        <v>126864724</v>
       </c>
       <c r="B63" t="n">
-        <v>82859</v>
+        <v>79042</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700348</v>
+        <v>700243</v>
       </c>
       <c r="R63" t="n">
-        <v>7114044</v>
+        <v>7114142</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7227,19 +7228,18 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7250,10 +7250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126864724</v>
+        <v>126864719</v>
       </c>
       <c r="B64" t="n">
-        <v>79042</v>
+        <v>98469</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7261,21 +7261,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6434</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700243</v>
+        <v>700137</v>
       </c>
       <c r="R64" t="n">
-        <v>7114142</v>
+        <v>7114498</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7351,52 +7351,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126864736</v>
+        <v>126851658</v>
       </c>
       <c r="B65" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700346</v>
+        <v>700243</v>
       </c>
       <c r="R65" t="n">
-        <v>7114313</v>
+        <v>7114171</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7423,30 +7419,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7460,7 +7465,7 @@
         <v>126864702</v>
       </c>
       <c r="B66" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7574,7 +7579,7 @@
         <v>126864683</v>
       </c>
       <c r="B67" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7680,7 +7685,7 @@
         <v>126862630</v>
       </c>
       <c r="B68" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7768,7 +7773,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7779,10 +7784,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126864713</v>
+        <v>126864736</v>
       </c>
       <c r="B69" t="n">
-        <v>91688</v>
+        <v>98448</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7790,26 +7795,27 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7817,10 +7823,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700335</v>
+        <v>700346</v>
       </c>
       <c r="R69" t="n">
-        <v>7114031</v>
+        <v>7114313</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7873,7 +7879,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7884,48 +7890,51 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126851658</v>
+        <v>126864713</v>
       </c>
       <c r="B70" t="n">
-        <v>80121</v>
+        <v>91688</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700243</v>
+        <v>700335</v>
       </c>
       <c r="R70" t="n">
-        <v>7114171</v>
+        <v>7114031</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7952,39 +7961,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8197,10 +8197,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126865566</v>
+        <v>126867860</v>
       </c>
       <c r="B73" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8225,17 +8225,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700281</v>
+        <v>700311</v>
       </c>
       <c r="R73" t="n">
-        <v>7114184</v>
+        <v>7114124</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8276,18 +8288,19 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8298,10 +8311,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126867860</v>
+        <v>126865566</v>
       </c>
       <c r="B74" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8326,29 +8339,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700311</v>
+        <v>700281</v>
       </c>
       <c r="R74" t="n">
-        <v>7114124</v>
+        <v>7114184</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8389,19 +8390,18 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8412,32 +8412,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126868139</v>
+        <v>126865557</v>
       </c>
       <c r="B75" t="n">
-        <v>96573</v>
+        <v>98448</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700112</v>
+        <v>700328</v>
       </c>
       <c r="R75" t="n">
-        <v>7114619</v>
+        <v>7114346</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8480,19 +8480,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8507,12 +8497,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8523,10 +8513,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126865557</v>
+        <v>126865562</v>
       </c>
       <c r="B76" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8558,10 +8548,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700328</v>
+        <v>700345</v>
       </c>
       <c r="R76" t="n">
-        <v>7114346</v>
+        <v>7114076</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8624,32 +8614,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126865562</v>
+        <v>126868139</v>
       </c>
       <c r="B77" t="n">
-        <v>98447</v>
+        <v>96573</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8659,10 +8649,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700345</v>
+        <v>700112</v>
       </c>
       <c r="R77" t="n">
-        <v>7114076</v>
+        <v>7114619</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8692,9 +8682,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8709,12 +8709,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8725,48 +8725,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126856511</v>
+        <v>126864737</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700252</v>
+        <v>700304</v>
       </c>
       <c r="R78" t="n">
-        <v>7114157</v>
+        <v>7114381</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8793,19 +8793,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8820,12 +8810,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8836,53 +8826,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126864729</v>
+        <v>126867872</v>
       </c>
       <c r="B79" t="n">
-        <v>58031</v>
+        <v>98448</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700152</v>
+        <v>700320</v>
       </c>
       <c r="R79" t="n">
-        <v>7114491</v>
+        <v>7114336</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8929,12 +8911,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8945,10 +8927,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126864737</v>
+        <v>126864741</v>
       </c>
       <c r="B80" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8973,17 +8955,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700304</v>
+        <v>700313</v>
       </c>
       <c r="R80" t="n">
-        <v>7114381</v>
+        <v>7114166</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9046,48 +9032,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126867872</v>
+        <v>126856511</v>
       </c>
       <c r="B81" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700320</v>
+        <v>700252</v>
       </c>
       <c r="R81" t="n">
-        <v>7114336</v>
+        <v>7114157</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9114,9 +9100,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9131,12 +9127,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9147,45 +9143,53 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126867870</v>
+        <v>126864729</v>
       </c>
       <c r="B82" t="n">
-        <v>98447</v>
+        <v>58031</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700316</v>
+        <v>700152</v>
       </c>
       <c r="R82" t="n">
-        <v>7114065</v>
+        <v>7114491</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9232,12 +9236,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9248,10 +9252,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126864741</v>
+        <v>126867870</v>
       </c>
       <c r="B83" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9276,21 +9280,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700313</v>
+        <v>700316</v>
       </c>
       <c r="R83" t="n">
-        <v>7114166</v>
+        <v>7114065</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9337,12 +9337,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9356,7 +9356,7 @@
         <v>126862652</v>
       </c>
       <c r="B84" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126864711</v>
+        <v>126868122</v>
       </c>
       <c r="B2" t="n">
-        <v>96700</v>
+        <v>4773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700315</v>
+        <v>700332</v>
       </c>
       <c r="R2" t="n">
-        <v>7114081</v>
+        <v>7114038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,11 +748,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -756,16 +771,36 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126864745</v>
+        <v>126864711</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>96700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +822,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700325</v>
+        <v>700315</v>
       </c>
       <c r="R3" t="n">
-        <v>7114161</v>
+        <v>7114081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +901,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,45 +912,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126862651</v>
+        <v>126864745</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700266</v>
+        <v>700325</v>
       </c>
       <c r="R4" t="n">
-        <v>7114350</v>
+        <v>7114161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +997,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,50 +1013,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126868122</v>
+        <v>126862651</v>
       </c>
       <c r="B5" t="n">
-        <v>4773</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700332</v>
+        <v>700266</v>
       </c>
       <c r="R5" t="n">
-        <v>7114038</v>
+        <v>7114350</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,21 +1081,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1074,36 +1094,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1225,48 +1225,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126851272</v>
+        <v>126864750</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700310</v>
+        <v>700151</v>
       </c>
       <c r="R7" t="n">
-        <v>7114176</v>
+        <v>7114492</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,19 +1293,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1336,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126867871</v>
+        <v>126851272</v>
       </c>
       <c r="B8" t="n">
         <v>98448</v>
@@ -1367,17 +1357,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700323</v>
+        <v>700310</v>
       </c>
       <c r="R8" t="n">
-        <v>7114124</v>
+        <v>7114176</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,9 +1394,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,12 +1421,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126864699</v>
+        <v>126867871</v>
       </c>
       <c r="B9" t="n">
         <v>98448</v>
@@ -1465,33 +1465,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700344</v>
+        <v>700323</v>
       </c>
       <c r="R9" t="n">
-        <v>7114307</v>
+        <v>7114124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1516,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1555,7 +1538,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126864701</v>
+        <v>126864699</v>
       </c>
       <c r="B10" t="n">
         <v>98448</v>
@@ -1585,7 +1568,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1593,7 +1576,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1602,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700283</v>
+        <v>700344</v>
       </c>
       <c r="R10" t="n">
-        <v>7114393</v>
+        <v>7114307</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,45 +1656,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864750</v>
+        <v>126864701</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700151</v>
+        <v>700283</v>
       </c>
       <c r="R11" t="n">
-        <v>7114492</v>
+        <v>7114393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,6 +1747,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -4610,32 +4610,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126867882</v>
+        <v>126865578</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>98365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700181</v>
+        <v>700147</v>
       </c>
       <c r="R39" t="n">
-        <v>7114498</v>
+        <v>7114536</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4695,12 +4695,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4711,32 +4711,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126865569</v>
+        <v>126865563</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700198</v>
+        <v>700297</v>
       </c>
       <c r="R40" t="n">
-        <v>7114523</v>
+        <v>7114112</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4812,50 +4812,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126868146</v>
+        <v>126864700</v>
       </c>
       <c r="B41" t="n">
-        <v>41365</v>
+        <v>98448</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>215713</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700294</v>
+        <v>700265</v>
       </c>
       <c r="R41" t="n">
-        <v>7114336</v>
+        <v>7114403</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4885,39 +4892,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4928,45 +4926,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126865578</v>
+        <v>126868146</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>41365</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>215713</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700147</v>
+        <v>700294</v>
       </c>
       <c r="R42" t="n">
-        <v>7114536</v>
+        <v>7114336</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4996,9 +4999,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5013,12 +5026,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5029,32 +5042,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126865563</v>
+        <v>126867882</v>
       </c>
       <c r="B43" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5064,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700297</v>
+        <v>700181</v>
       </c>
       <c r="R43" t="n">
-        <v>7114112</v>
+        <v>7114498</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5114,12 +5127,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5130,57 +5143,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126864700</v>
+        <v>126865569</v>
       </c>
       <c r="B44" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700265</v>
+        <v>700198</v>
       </c>
       <c r="R44" t="n">
-        <v>7114403</v>
+        <v>7114523</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5221,7 +5222,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5481,48 +5481,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126864746</v>
+        <v>126854059</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>91330</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lappmyran, Lappmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700240</v>
+        <v>700098</v>
       </c>
       <c r="R47" t="n">
-        <v>7114242</v>
+        <v>7114648</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5549,9 +5549,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5566,12 +5576,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5582,48 +5592,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126854059</v>
+        <v>126864746</v>
       </c>
       <c r="B48" t="n">
-        <v>91330</v>
+        <v>98365</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lappmyran, Lappmyran, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700098</v>
+        <v>700240</v>
       </c>
       <c r="R48" t="n">
-        <v>7114648</v>
+        <v>7114242</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5650,19 +5660,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5677,12 +5677,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5693,45 +5693,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126863285</v>
+        <v>126868129</v>
       </c>
       <c r="B49" t="n">
-        <v>57821</v>
+        <v>80157</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700344</v>
+        <v>700245</v>
       </c>
       <c r="R49" t="n">
-        <v>7114335</v>
+        <v>7114154</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,11 +5761,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5774,16 +5784,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5794,32 +5819,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126862656</v>
+        <v>126863285</v>
       </c>
       <c r="B50" t="n">
-        <v>98448</v>
+        <v>57821</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5829,10 +5854,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700320</v>
+        <v>700344</v>
       </c>
       <c r="R50" t="n">
-        <v>7114171</v>
+        <v>7114335</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5879,12 +5904,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5895,7 +5920,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126864704</v>
+        <v>126864738</v>
       </c>
       <c r="B51" t="n">
         <v>98448</v>
@@ -5923,29 +5948,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700273</v>
+        <v>700299</v>
       </c>
       <c r="R51" t="n">
-        <v>7114229</v>
+        <v>7114327</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5997,7 +6010,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6008,7 +6021,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126864734</v>
+        <v>126865558</v>
       </c>
       <c r="B52" t="n">
         <v>98448</v>
@@ -6036,21 +6049,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700263</v>
+        <v>700326</v>
       </c>
       <c r="R52" t="n">
-        <v>7114387</v>
+        <v>7114352</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6102,7 +6111,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6113,45 +6122,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126868129</v>
+        <v>126862656</v>
       </c>
       <c r="B53" t="n">
-        <v>80157</v>
+        <v>98448</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700245</v>
+        <v>700320</v>
       </c>
       <c r="R53" t="n">
-        <v>7114154</v>
+        <v>7114171</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6181,21 +6190,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6204,31 +6203,16 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6239,7 +6223,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126864738</v>
+        <v>126864704</v>
       </c>
       <c r="B54" t="n">
         <v>98448</v>
@@ -6267,17 +6251,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700299</v>
+        <v>700273</v>
       </c>
       <c r="R54" t="n">
-        <v>7114327</v>
+        <v>7114229</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6329,7 +6325,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6340,7 +6336,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126865558</v>
+        <v>126864734</v>
       </c>
       <c r="B55" t="n">
         <v>98448</v>
@@ -6368,17 +6364,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700326</v>
+        <v>700263</v>
       </c>
       <c r="R55" t="n">
-        <v>7114352</v>
+        <v>7114387</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6441,32 +6441,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126865564</v>
+        <v>126864708</v>
       </c>
       <c r="B56" t="n">
-        <v>98448</v>
+        <v>92620</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6476,10 +6476,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700282</v>
+        <v>700253</v>
       </c>
       <c r="R56" t="n">
-        <v>7114135</v>
+        <v>7114409</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6542,45 +6542,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126864708</v>
+        <v>126864680</v>
       </c>
       <c r="B57" t="n">
-        <v>92620</v>
+        <v>80121</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700253</v>
+        <v>700363</v>
       </c>
       <c r="R57" t="n">
-        <v>7114409</v>
+        <v>7114127</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6627,12 +6627,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6643,45 +6643,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126864680</v>
+        <v>126865564</v>
       </c>
       <c r="B58" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700363</v>
+        <v>700282</v>
       </c>
       <c r="R58" t="n">
-        <v>7114127</v>
+        <v>7114135</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6728,12 +6728,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7351,48 +7351,51 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126851658</v>
+        <v>126864713</v>
       </c>
       <c r="B65" t="n">
-        <v>80121</v>
+        <v>91688</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700243</v>
+        <v>700335</v>
       </c>
       <c r="R65" t="n">
-        <v>7114171</v>
+        <v>7114031</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7419,39 +7422,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7462,60 +7456,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126864702</v>
+        <v>126851658</v>
       </c>
       <c r="B66" t="n">
-        <v>98448</v>
+        <v>80121</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700301</v>
+        <v>700243</v>
       </c>
       <c r="R66" t="n">
-        <v>7114357</v>
+        <v>7114171</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7542,30 +7524,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7576,45 +7567,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126864683</v>
+        <v>126864720</v>
       </c>
       <c r="B67" t="n">
-        <v>98448</v>
+        <v>80025</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700345</v>
+        <v>700382</v>
       </c>
       <c r="R67" t="n">
-        <v>7114314</v>
+        <v>7114108</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7649,11 +7640,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7666,12 +7652,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7682,7 +7668,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126862630</v>
+        <v>126864702</v>
       </c>
       <c r="B68" t="n">
         <v>98448</v>
@@ -7710,17 +7696,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700326</v>
+        <v>700301</v>
       </c>
       <c r="R68" t="n">
-        <v>7114161</v>
+        <v>7114357</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7768,12 +7766,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7784,7 +7782,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126864736</v>
+        <v>126864683</v>
       </c>
       <c r="B69" t="n">
         <v>98448</v>
@@ -7813,20 +7811,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700346</v>
+        <v>700345</v>
       </c>
       <c r="R69" t="n">
-        <v>7114313</v>
+        <v>7114314</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7861,25 +7855,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7890,10 +7888,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126864713</v>
+        <v>126862630</v>
       </c>
       <c r="B70" t="n">
-        <v>91688</v>
+        <v>98448</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7901,37 +7899,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700335</v>
+        <v>700326</v>
       </c>
       <c r="R70" t="n">
-        <v>7114031</v>
+        <v>7114161</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7979,12 +7974,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7995,45 +7990,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126864720</v>
+        <v>126864736</v>
       </c>
       <c r="B71" t="n">
-        <v>80025</v>
+        <v>98448</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700382</v>
+        <v>700346</v>
       </c>
       <c r="R71" t="n">
-        <v>7114108</v>
+        <v>7114313</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8074,6 +8073,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8725,48 +8725,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126864737</v>
+        <v>126856511</v>
       </c>
       <c r="B78" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700304</v>
+        <v>700252</v>
       </c>
       <c r="R78" t="n">
-        <v>7114381</v>
+        <v>7114157</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8793,9 +8793,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8810,12 +8820,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8826,45 +8836,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126867872</v>
+        <v>126864729</v>
       </c>
       <c r="B79" t="n">
-        <v>98448</v>
+        <v>58031</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700320</v>
+        <v>700152</v>
       </c>
       <c r="R79" t="n">
-        <v>7114336</v>
+        <v>7114491</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8911,12 +8929,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8927,7 +8945,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126864741</v>
+        <v>126867870</v>
       </c>
       <c r="B80" t="n">
         <v>98448</v>
@@ -8955,21 +8973,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700313</v>
+        <v>700316</v>
       </c>
       <c r="R80" t="n">
-        <v>7114166</v>
+        <v>7114065</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9016,12 +9030,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9032,48 +9046,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126856511</v>
+        <v>126864737</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700252</v>
+        <v>700304</v>
       </c>
       <c r="R81" t="n">
-        <v>7114157</v>
+        <v>7114381</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9100,19 +9114,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9127,12 +9131,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9143,53 +9147,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126864729</v>
+        <v>126867872</v>
       </c>
       <c r="B82" t="n">
-        <v>58031</v>
+        <v>98448</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700152</v>
+        <v>700320</v>
       </c>
       <c r="R82" t="n">
-        <v>7114491</v>
+        <v>7114336</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9236,12 +9232,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9252,7 +9248,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126867870</v>
+        <v>126864741</v>
       </c>
       <c r="B83" t="n">
         <v>98448</v>
@@ -9280,17 +9276,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700316</v>
+        <v>700313</v>
       </c>
       <c r="R83" t="n">
-        <v>7114065</v>
+        <v>7114166</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9337,12 +9337,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126868122</v>
+        <v>126864745</v>
       </c>
       <c r="B2" t="n">
-        <v>4773</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700332</v>
+        <v>700325</v>
       </c>
       <c r="R2" t="n">
-        <v>7114038</v>
+        <v>7114161</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,36 +756,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -811,45 +776,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126864711</v>
+        <v>126868122</v>
       </c>
       <c r="B3" t="n">
-        <v>96700</v>
+        <v>4772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>700315</v>
+        <v>700332</v>
       </c>
       <c r="R3" t="n">
-        <v>7114081</v>
+        <v>7114038</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,11 +849,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,16 +872,36 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126864745</v>
+        <v>126864711</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>96689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700325</v>
+        <v>700315</v>
       </c>
       <c r="R4" t="n">
-        <v>7114161</v>
+        <v>7114081</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1016,7 +1016,7 @@
         <v>126862651</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1117,7 +1117,7 @@
         <v>126868144</v>
       </c>
       <c r="B6" t="n">
-        <v>97325</v>
+        <v>97314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126864750</v>
+        <v>126862629</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>80074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,34 +1236,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700151</v>
+        <v>700301</v>
       </c>
       <c r="R7" t="n">
-        <v>7114492</v>
+        <v>7114163</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1326,48 +1326,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126851272</v>
+        <v>126864750</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700310</v>
+        <v>700151</v>
       </c>
       <c r="R8" t="n">
-        <v>7114176</v>
+        <v>7114492</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,19 +1394,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,12 +1411,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1440,7 +1430,7 @@
         <v>126867871</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126864699</v>
+        <v>126864701</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,7 +1558,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1576,11 +1566,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1589,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700344</v>
+        <v>700283</v>
       </c>
       <c r="R10" t="n">
-        <v>7114307</v>
+        <v>7114393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864701</v>
+        <v>126864699</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,7 +1672,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1694,7 +1680,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1703,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700283</v>
+        <v>700344</v>
       </c>
       <c r="R11" t="n">
-        <v>7114393</v>
+        <v>7114307</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,48 +1760,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126862629</v>
+        <v>126851272</v>
       </c>
       <c r="B12" t="n">
-        <v>80081</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700301</v>
+        <v>700310</v>
       </c>
       <c r="R12" t="n">
-        <v>7114163</v>
+        <v>7114176</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,9 +1828,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,12 +1855,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1874,7 +1874,7 @@
         <v>126863311</v>
       </c>
       <c r="B13" t="n">
-        <v>92620</v>
+        <v>92609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>126867862</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,32 +2086,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126865575</v>
+        <v>126867869</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700236</v>
+        <v>700339</v>
       </c>
       <c r="R15" t="n">
-        <v>7114234</v>
+        <v>7114086</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,12 +2171,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126867869</v>
+        <v>126863301</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,14 +2218,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700339</v>
+        <v>700307</v>
       </c>
       <c r="R16" t="n">
-        <v>7114086</v>
+        <v>7114151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,12 +2272,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2288,45 +2288,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126863301</v>
+        <v>126865575</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>98353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700307</v>
+        <v>700236</v>
       </c>
       <c r="R17" t="n">
-        <v>7114151</v>
+        <v>7114234</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,12 +2373,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2392,7 +2392,7 @@
         <v>126868136</v>
       </c>
       <c r="B18" t="n">
-        <v>96573</v>
+        <v>96562</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2500,32 +2500,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126868126</v>
+        <v>126864725</v>
       </c>
       <c r="B19" t="n">
-        <v>80121</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700245</v>
+        <v>700244</v>
       </c>
       <c r="R19" t="n">
-        <v>7114154</v>
+        <v>7114210</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,21 +2568,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2591,31 +2581,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2626,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126864725</v>
+        <v>126865568</v>
       </c>
       <c r="B20" t="n">
-        <v>79042</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2661,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700244</v>
+        <v>700363</v>
       </c>
       <c r="R20" t="n">
-        <v>7114210</v>
+        <v>7114098</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2716,7 +2691,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2727,32 +2702,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126865568</v>
+        <v>126868126</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>80114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2762,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700363</v>
+        <v>700245</v>
       </c>
       <c r="R21" t="n">
-        <v>7114098</v>
+        <v>7114154</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,11 +2770,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2808,16 +2793,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2831,7 +2831,7 @@
         <v>126862588</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2932,7 +2932,7 @@
         <v>126863310</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>126867858</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>126864710</v>
       </c>
       <c r="B25" t="n">
-        <v>96700</v>
+        <v>96689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,49 +3245,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126864739</v>
+        <v>126865571</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700286</v>
+        <v>700287</v>
       </c>
       <c r="R26" t="n">
-        <v>7114214</v>
+        <v>7114144</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,7 +3335,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3350,10 +3346,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126865571</v>
+        <v>126868157</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>40901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,34 +3357,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>102498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Silverfläckspraktmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Denisia stroemella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1779)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700287</v>
+        <v>700300</v>
       </c>
       <c r="R27" t="n">
-        <v>7114144</v>
+        <v>7114175</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,9 +3419,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,12 +3446,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum, Alva Danielsson, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3451,38 +3462,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126868157</v>
+        <v>126864739</v>
       </c>
       <c r="B28" t="n">
-        <v>40905</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silverfläckspraktmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Denisia stroemella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1779)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3491,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700300</v>
+        <v>700286</v>
       </c>
       <c r="R28" t="n">
-        <v>7114175</v>
+        <v>7114214</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,19 +3534,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,12 +3551,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3567,45 +3567,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126864748</v>
+        <v>126862653</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>98436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700220</v>
+        <v>700319</v>
       </c>
       <c r="R29" t="n">
-        <v>7114448</v>
+        <v>7114336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,12 +3652,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3668,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126862653</v>
+        <v>126868151</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,14 +3699,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700319</v>
+        <v>700306</v>
       </c>
       <c r="R30" t="n">
-        <v>7114336</v>
+        <v>7114337</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,9 +3736,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3753,12 +3763,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3769,10 +3779,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126868151</v>
+        <v>126865559</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3804,10 +3814,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700306</v>
+        <v>700330</v>
       </c>
       <c r="R31" t="n">
-        <v>7114337</v>
+        <v>7114328</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,19 +3847,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,12 +3864,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3880,32 +3880,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126865559</v>
+        <v>126864748</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>98353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700330</v>
+        <v>700220</v>
       </c>
       <c r="R32" t="n">
-        <v>7114328</v>
+        <v>7114448</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3981,48 +3981,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126852356</v>
+        <v>126864698</v>
       </c>
       <c r="B33" t="n">
-        <v>92620</v>
+        <v>91319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700344</v>
+        <v>700320</v>
       </c>
       <c r="R33" t="n">
-        <v>7114301</v>
+        <v>7114182</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4049,19 +4049,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4076,12 +4066,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4092,10 +4082,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126864706</v>
+        <v>126852356</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>92609</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4103,37 +4093,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700145</v>
+        <v>700344</v>
       </c>
       <c r="R34" t="n">
-        <v>7114540</v>
+        <v>7114301</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4160,9 +4150,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4177,12 +4177,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4193,32 +4193,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126865556</v>
+        <v>126864706</v>
       </c>
       <c r="B35" t="n">
-        <v>98448</v>
+        <v>98353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700304</v>
+        <v>700145</v>
       </c>
       <c r="R35" t="n">
-        <v>7114364</v>
+        <v>7114540</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4294,10 +4294,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126862654</v>
+        <v>126864703</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4322,17 +4322,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700337</v>
+        <v>700315</v>
       </c>
       <c r="R36" t="n">
-        <v>7114304</v>
+        <v>7114347</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,18 +4385,19 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4395,10 +4408,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126864703</v>
+        <v>126865556</v>
       </c>
       <c r="B37" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4423,29 +4436,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700315</v>
+        <v>700304</v>
       </c>
       <c r="R37" t="n">
-        <v>7114347</v>
+        <v>7114364</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4486,7 +4487,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4509,45 +4509,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126864698</v>
+        <v>126862654</v>
       </c>
       <c r="B38" t="n">
-        <v>91330</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700320</v>
+        <v>700337</v>
       </c>
       <c r="R38" t="n">
-        <v>7114182</v>
+        <v>7114304</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,12 +4594,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4610,32 +4610,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126865578</v>
+        <v>126865563</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>98436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700147</v>
+        <v>700297</v>
       </c>
       <c r="R39" t="n">
-        <v>7114536</v>
+        <v>7114112</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126865563</v>
+        <v>126864700</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4739,17 +4739,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700297</v>
+        <v>700265</v>
       </c>
       <c r="R40" t="n">
-        <v>7114112</v>
+        <v>7114403</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4790,6 +4802,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4801,7 +4814,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4812,57 +4825,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126864700</v>
+        <v>126868146</v>
       </c>
       <c r="B41" t="n">
-        <v>98448</v>
+        <v>41361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>215713</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700265</v>
+        <v>700294</v>
       </c>
       <c r="R41" t="n">
-        <v>7114403</v>
+        <v>7114336</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4892,30 +4898,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4926,50 +4941,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126868146</v>
+        <v>126865578</v>
       </c>
       <c r="B42" t="n">
-        <v>41365</v>
+        <v>98353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>215713</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700294</v>
+        <v>700147</v>
       </c>
       <c r="R42" t="n">
-        <v>7114336</v>
+        <v>7114536</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4999,19 +5009,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5026,12 +5026,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5042,10 +5042,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126867882</v>
+        <v>126865569</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700181</v>
+        <v>700198</v>
       </c>
       <c r="R43" t="n">
-        <v>7114498</v>
+        <v>7114523</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5127,12 +5127,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5143,10 +5143,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126865569</v>
+        <v>126867882</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,10 +5178,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700198</v>
+        <v>700181</v>
       </c>
       <c r="R44" t="n">
-        <v>7114523</v>
+        <v>7114498</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5228,12 +5228,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5247,7 +5247,7 @@
         <v>126864733</v>
       </c>
       <c r="B45" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5345,53 +5345,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126868134</v>
+        <v>126854059</v>
       </c>
       <c r="B46" t="n">
-        <v>4773</v>
+        <v>91319</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lappmyran, Lappmyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700186</v>
+        <v>700098</v>
       </c>
       <c r="R46" t="n">
-        <v>7114499</v>
+        <v>7114648</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5420,7 +5415,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5430,7 +5425,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5441,36 +5436,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5481,48 +5456,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126854059</v>
+        <v>126868134</v>
       </c>
       <c r="B47" t="n">
-        <v>91330</v>
+        <v>4772</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lappmyran, Lappmyran, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700098</v>
+        <v>700186</v>
       </c>
       <c r="R47" t="n">
-        <v>7114648</v>
+        <v>7114499</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5551,7 +5531,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5561,7 +5541,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5572,16 +5552,36 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5595,7 +5595,7 @@
         <v>126864746</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>98353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5693,45 +5693,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126868129</v>
+        <v>126863285</v>
       </c>
       <c r="B49" t="n">
-        <v>80157</v>
+        <v>57817</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700245</v>
+        <v>700344</v>
       </c>
       <c r="R49" t="n">
-        <v>7114154</v>
+        <v>7114335</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,21 +5761,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5784,31 +5774,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5819,45 +5794,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126863285</v>
+        <v>126868129</v>
       </c>
       <c r="B50" t="n">
-        <v>57821</v>
+        <v>80150</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700344</v>
+        <v>700245</v>
       </c>
       <c r="R50" t="n">
-        <v>7114335</v>
+        <v>7114154</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5887,11 +5862,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5900,16 +5885,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5920,10 +5920,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126864738</v>
+        <v>126864704</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5948,17 +5948,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700299</v>
+        <v>700273</v>
       </c>
       <c r="R51" t="n">
-        <v>7114327</v>
+        <v>7114229</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6010,7 +6022,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6021,10 +6033,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126865558</v>
+        <v>126864738</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6056,10 +6068,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700326</v>
+        <v>700299</v>
       </c>
       <c r="R52" t="n">
-        <v>7114352</v>
+        <v>7114327</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,7 +6123,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6122,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126862656</v>
+        <v>126864734</v>
       </c>
       <c r="B53" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6150,17 +6162,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700320</v>
+        <v>700263</v>
       </c>
       <c r="R53" t="n">
-        <v>7114171</v>
+        <v>7114387</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6207,12 +6223,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6223,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126864704</v>
+        <v>126865558</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6251,29 +6267,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700273</v>
+        <v>700326</v>
       </c>
       <c r="R54" t="n">
-        <v>7114229</v>
+        <v>7114352</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6325,7 +6329,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6336,10 +6340,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126864734</v>
+        <v>126862656</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,21 +6368,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700263</v>
+        <v>700320</v>
       </c>
       <c r="R55" t="n">
-        <v>7114387</v>
+        <v>7114171</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6425,12 +6425,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6441,45 +6441,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126864708</v>
+        <v>126864680</v>
       </c>
       <c r="B56" t="n">
-        <v>92620</v>
+        <v>80114</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700253</v>
+        <v>700363</v>
       </c>
       <c r="R56" t="n">
-        <v>7114409</v>
+        <v>7114127</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6526,12 +6526,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6542,45 +6542,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126864680</v>
+        <v>126864708</v>
       </c>
       <c r="B57" t="n">
-        <v>80121</v>
+        <v>92609</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700363</v>
+        <v>700253</v>
       </c>
       <c r="R57" t="n">
-        <v>7114127</v>
+        <v>7114409</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6627,12 +6627,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6643,10 +6643,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126865564</v>
+        <v>126865567</v>
       </c>
       <c r="B58" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700282</v>
+        <v>700281</v>
       </c>
       <c r="R58" t="n">
-        <v>7114135</v>
+        <v>7114196</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6744,10 +6744,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126865567</v>
+        <v>126865564</v>
       </c>
       <c r="B59" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700281</v>
+        <v>700282</v>
       </c>
       <c r="R59" t="n">
-        <v>7114196</v>
+        <v>7114135</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6845,10 +6845,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126862657</v>
+        <v>126863304</v>
       </c>
       <c r="B60" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700359</v>
+        <v>700323</v>
       </c>
       <c r="R60" t="n">
-        <v>7114097</v>
+        <v>7114164</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6930,12 +6930,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6946,10 +6946,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126863304</v>
+        <v>126862657</v>
       </c>
       <c r="B61" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700323</v>
+        <v>700359</v>
       </c>
       <c r="R61" t="n">
-        <v>7114164</v>
+        <v>7114097</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7031,12 +7031,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7047,45 +7047,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126864687</v>
+        <v>126864719</v>
       </c>
       <c r="B62" t="n">
-        <v>82859</v>
+        <v>98457</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700348</v>
+        <v>700137</v>
       </c>
       <c r="R62" t="n">
-        <v>7114044</v>
+        <v>7114498</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7126,19 +7126,18 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7149,45 +7148,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126864724</v>
+        <v>126864687</v>
       </c>
       <c r="B63" t="n">
-        <v>79042</v>
+        <v>82852</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700243</v>
+        <v>700348</v>
       </c>
       <c r="R63" t="n">
-        <v>7114142</v>
+        <v>7114044</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7228,18 +7227,19 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7250,10 +7250,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126864719</v>
+        <v>126864724</v>
       </c>
       <c r="B64" t="n">
-        <v>98469</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7261,21 +7261,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6434</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700137</v>
+        <v>700243</v>
       </c>
       <c r="R64" t="n">
-        <v>7114498</v>
+        <v>7114142</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7354,7 +7354,7 @@
         <v>126864713</v>
       </c>
       <c r="B65" t="n">
-        <v>91688</v>
+        <v>91677</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7456,48 +7456,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126851658</v>
+        <v>126864720</v>
       </c>
       <c r="B66" t="n">
-        <v>80121</v>
+        <v>80018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700243</v>
+        <v>700382</v>
       </c>
       <c r="R66" t="n">
-        <v>7114171</v>
+        <v>7114108</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7524,19 +7524,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7551,12 +7541,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7567,48 +7557,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126864720</v>
+        <v>126851658</v>
       </c>
       <c r="B67" t="n">
-        <v>80025</v>
+        <v>80114</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700382</v>
+        <v>700243</v>
       </c>
       <c r="R67" t="n">
-        <v>7114108</v>
+        <v>7114171</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7635,9 +7625,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7652,12 +7652,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7668,10 +7668,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126864702</v>
+        <v>126864683</v>
       </c>
       <c r="B68" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7696,29 +7696,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700301</v>
+        <v>700345</v>
       </c>
       <c r="R68" t="n">
-        <v>7114357</v>
+        <v>7114314</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7753,25 +7741,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7782,10 +7774,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126864683</v>
+        <v>126864736</v>
       </c>
       <c r="B69" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7811,16 +7803,20 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700345</v>
+        <v>700346</v>
       </c>
       <c r="R69" t="n">
-        <v>7114314</v>
+        <v>7114313</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7855,29 +7851,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7888,10 +7880,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126862630</v>
+        <v>126864702</v>
       </c>
       <c r="B70" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7916,17 +7908,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700326</v>
+        <v>700301</v>
       </c>
       <c r="R70" t="n">
-        <v>7114161</v>
+        <v>7114357</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7974,12 +7978,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7990,10 +7994,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126864736</v>
+        <v>126862630</v>
       </c>
       <c r="B71" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8019,20 +8023,16 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700346</v>
+        <v>700326</v>
       </c>
       <c r="R71" t="n">
-        <v>7114313</v>
+        <v>7114161</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8080,12 +8080,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8099,7 +8099,7 @@
         <v>126865572</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, Elke Blöhbaum, Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8197,10 +8197,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126867860</v>
+        <v>126865566</v>
       </c>
       <c r="B73" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8225,29 +8225,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700311</v>
+        <v>700281</v>
       </c>
       <c r="R73" t="n">
-        <v>7114124</v>
+        <v>7114184</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8288,19 +8276,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8311,10 +8298,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126865566</v>
+        <v>126867860</v>
       </c>
       <c r="B74" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8339,17 +8326,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700281</v>
+        <v>700311</v>
       </c>
       <c r="R74" t="n">
-        <v>7114184</v>
+        <v>7114124</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8390,18 +8389,19 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8412,32 +8412,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126865557</v>
+        <v>126868139</v>
       </c>
       <c r="B75" t="n">
-        <v>98448</v>
+        <v>96562</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700328</v>
+        <v>700112</v>
       </c>
       <c r="R75" t="n">
-        <v>7114346</v>
+        <v>7114619</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8480,9 +8480,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8497,12 +8507,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8513,10 +8523,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126865562</v>
+        <v>126865557</v>
       </c>
       <c r="B76" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8548,10 +8558,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700345</v>
+        <v>700328</v>
       </c>
       <c r="R76" t="n">
-        <v>7114076</v>
+        <v>7114346</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8614,32 +8624,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126868139</v>
+        <v>126865562</v>
       </c>
       <c r="B77" t="n">
-        <v>96573</v>
+        <v>98436</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8649,10 +8659,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700112</v>
+        <v>700345</v>
       </c>
       <c r="R77" t="n">
-        <v>7114619</v>
+        <v>7114076</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8682,19 +8692,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8709,12 +8709,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8728,7 +8728,7 @@
         <v>126856511</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>126864729</v>
       </c>
       <c r="B79" t="n">
-        <v>58031</v>
+        <v>58027</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8945,10 +8945,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126867870</v>
+        <v>126864737</v>
       </c>
       <c r="B80" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700316</v>
+        <v>700304</v>
       </c>
       <c r="R80" t="n">
-        <v>7114065</v>
+        <v>7114381</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9030,12 +9030,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9046,10 +9046,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126864737</v>
+        <v>126867872</v>
       </c>
       <c r="B81" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9081,10 +9081,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700304</v>
+        <v>700320</v>
       </c>
       <c r="R81" t="n">
-        <v>7114381</v>
+        <v>7114336</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9131,12 +9131,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9147,10 +9147,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126867872</v>
+        <v>126867870</v>
       </c>
       <c r="B82" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9182,10 +9182,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700320</v>
+        <v>700316</v>
       </c>
       <c r="R82" t="n">
-        <v>7114336</v>
+        <v>7114065</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9251,7 +9251,7 @@
         <v>126864741</v>
       </c>
       <c r="B83" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>126862652</v>
       </c>
       <c r="B84" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>126868157</v>
       </c>
       <c r="B28" t="n">
-        <v>41044</v>
+        <v>41070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>126868157</v>
       </c>
       <c r="B28" t="n">
-        <v>41070</v>
+        <v>41072</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>126868157</v>
       </c>
       <c r="B28" t="n">
-        <v>41072</v>
+        <v>41080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -3454,7 +3454,7 @@
         <v>126868157</v>
       </c>
       <c r="B28" t="n">
-        <v>41080</v>
+        <v>41081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126868122</v>
+        <v>126864710</v>
       </c>
       <c r="B2" t="n">
-        <v>4773</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>700332</v>
+        <v>700302</v>
       </c>
       <c r="R2" t="n">
-        <v>7114038</v>
+        <v>7114115</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,36 +756,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -814,7 +779,7 @@
         <v>126864711</v>
       </c>
       <c r="B3" t="n">
-        <v>96700</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126864745</v>
+        <v>126868149</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>700325</v>
+        <v>700285</v>
       </c>
       <c r="R4" t="n">
-        <v>7114161</v>
+        <v>7114325</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,11 +945,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -993,16 +968,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Högstubbe i sankmark.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Högstubbe i sankmark.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1013,48 +1008,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126862651</v>
+        <v>126854059</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lappmyran, Lappmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>700266</v>
+        <v>700098</v>
       </c>
       <c r="R5" t="n">
-        <v>7114350</v>
+        <v>7114648</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,9 +1076,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,12 +1103,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1114,45 +1119,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868144</v>
+        <v>126862588</v>
       </c>
       <c r="B6" t="n">
-        <v>97325</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>700167</v>
+        <v>700304</v>
       </c>
       <c r="R6" t="n">
-        <v>7114511</v>
+        <v>7114192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,19 +1187,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,12 +1204,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1225,32 +1220,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126864750</v>
+        <v>126864698</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>700151</v>
+        <v>700320</v>
       </c>
       <c r="R7" t="n">
-        <v>7114492</v>
+        <v>7114182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1326,48 +1321,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126851272</v>
+        <v>126864714</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>700310</v>
+        <v>700352</v>
       </c>
       <c r="R8" t="n">
-        <v>7114176</v>
+        <v>7114034</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,19 +1389,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,12 +1406,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1437,45 +1422,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126867871</v>
+        <v>126864687</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700323</v>
+        <v>700348</v>
       </c>
       <c r="R9" t="n">
-        <v>7114124</v>
+        <v>7114044</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,18 +1501,19 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1538,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126864699</v>
+        <v>126864713</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>92281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,39 +1535,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>700344</v>
+        <v>700335</v>
       </c>
       <c r="R10" t="n">
-        <v>7114307</v>
+        <v>7114031</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1656,44 +1629,36 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126864701</v>
+        <v>126868132</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>95962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1703,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700283</v>
+        <v>700209</v>
       </c>
       <c r="R11" t="n">
-        <v>7114393</v>
+        <v>7114261</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,9 +1701,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,12 +1729,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1770,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126862629</v>
+        <v>126868136</v>
       </c>
       <c r="B12" t="n">
-        <v>80081</v>
+        <v>97231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,37 +1756,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700301</v>
+        <v>700114</v>
       </c>
       <c r="R12" t="n">
-        <v>7114163</v>
+        <v>7114614</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,9 +1813,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,12 +1840,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1871,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126863311</v>
+        <v>126868139</v>
       </c>
       <c r="B13" t="n">
-        <v>92620</v>
+        <v>97231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1867,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>700340</v>
+        <v>700112</v>
       </c>
       <c r="R13" t="n">
-        <v>7114337</v>
+        <v>7114619</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,9 +1924,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,12 +1951,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1972,60 +1967,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126867862</v>
+        <v>126852356</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700364</v>
+        <v>700344</v>
       </c>
       <c r="R14" t="n">
-        <v>7114084</v>
+        <v>7114301</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,30 +2035,39 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2086,45 +2078,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126865575</v>
+        <v>126863311</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700236</v>
+        <v>700340</v>
       </c>
       <c r="R15" t="n">
-        <v>7114234</v>
+        <v>7114337</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,12 +2163,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2187,45 +2179,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126867869</v>
+        <v>126864691</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700339</v>
+        <v>700317</v>
       </c>
       <c r="R16" t="n">
-        <v>7114086</v>
+        <v>7114297</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,12 +2264,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2288,45 +2280,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126863301</v>
+        <v>126864708</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700307</v>
+        <v>700253</v>
       </c>
       <c r="R17" t="n">
-        <v>7114151</v>
+        <v>7114409</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,12 +2365,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2389,48 +2381,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126868136</v>
+        <v>126856511</v>
       </c>
       <c r="B18" t="n">
-        <v>96573</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>700114</v>
+        <v>700252</v>
       </c>
       <c r="R18" t="n">
-        <v>7114614</v>
+        <v>7114157</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2459,7 +2451,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2469,7 +2461,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,12 +2476,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2500,45 +2492,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126868126</v>
+        <v>126863310</v>
       </c>
       <c r="B19" t="n">
-        <v>80121</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>700245</v>
+        <v>700290</v>
       </c>
       <c r="R19" t="n">
-        <v>7114154</v>
+        <v>7114136</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,21 +2560,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2591,31 +2573,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2626,45 +2593,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126864725</v>
+        <v>126864686</v>
       </c>
       <c r="B20" t="n">
-        <v>79042</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700244</v>
+        <v>700326</v>
       </c>
       <c r="R20" t="n">
-        <v>7114210</v>
+        <v>7114187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2711,12 +2678,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2727,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126865568</v>
+        <v>126864705</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2762,10 +2729,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700363</v>
+        <v>700319</v>
       </c>
       <c r="R21" t="n">
-        <v>7114098</v>
+        <v>7114202</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2817,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2828,45 +2795,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126862588</v>
+        <v>126864744</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>700304</v>
+        <v>700226</v>
       </c>
       <c r="R22" t="n">
-        <v>7114192</v>
+        <v>7114226</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,12 +2880,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2929,14 +2896,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126863310</v>
+        <v>126864745</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2960,14 +2927,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>700290</v>
+        <v>700325</v>
       </c>
       <c r="R23" t="n">
-        <v>7114136</v>
+        <v>7114161</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,12 +2981,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3030,10 +2997,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126867858</v>
+        <v>126865569</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3041,46 +3008,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>700318</v>
+        <v>700198</v>
       </c>
       <c r="R24" t="n">
-        <v>7114179</v>
+        <v>7114523</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,19 +3076,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3144,32 +3098,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126864710</v>
+        <v>126865570</v>
       </c>
       <c r="B25" t="n">
-        <v>96700</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3179,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>700302</v>
+        <v>700321</v>
       </c>
       <c r="R25" t="n">
-        <v>7114115</v>
+        <v>7114184</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,7 +3188,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3245,10 +3199,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126864739</v>
+        <v>126865571</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3256,38 +3210,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>700286</v>
+        <v>700287</v>
       </c>
       <c r="R26" t="n">
-        <v>7114214</v>
+        <v>7114144</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,7 +3289,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3350,14 +3300,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126865571</v>
+        <v>126865572</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3385,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>700287</v>
+        <v>700229</v>
       </c>
       <c r="R27" t="n">
-        <v>7114144</v>
+        <v>7114231</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,7 +3390,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum, Alva Danielsson, Jennica Andersson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3451,50 +3401,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126868157</v>
+        <v>126867880</v>
       </c>
       <c r="B28" t="n">
-        <v>41081</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102498</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silverfläckspraktmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Denisia stroemella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1779)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>700300</v>
+        <v>700369</v>
       </c>
       <c r="R28" t="n">
-        <v>7114175</v>
+        <v>7114060</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,19 +3469,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3551,12 +3486,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3567,32 +3502,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126864748</v>
+        <v>126867881</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3602,10 +3537,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>700220</v>
+        <v>700230</v>
       </c>
       <c r="R29" t="n">
-        <v>7114448</v>
+        <v>7114216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3652,12 +3587,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3668,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126862653</v>
+        <v>126867882</v>
       </c>
       <c r="B30" t="n">
-        <v>98448</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,34 +3614,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>700319</v>
+        <v>700181</v>
       </c>
       <c r="R30" t="n">
-        <v>7114336</v>
+        <v>7114498</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,12 +3688,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3769,32 +3704,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126868151</v>
+        <v>126864724</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>79351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3804,10 +3739,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>700306</v>
+        <v>700243</v>
       </c>
       <c r="R31" t="n">
-        <v>7114337</v>
+        <v>7114142</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,19 +3772,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,12 +3789,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3880,32 +3805,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126865559</v>
+        <v>126864725</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>79351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3915,10 +3840,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>700330</v>
+        <v>700244</v>
       </c>
       <c r="R32" t="n">
-        <v>7114328</v>
+        <v>7114210</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3970,7 +3895,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3981,32 +3906,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126852356</v>
+        <v>126851584</v>
       </c>
       <c r="B33" t="n">
-        <v>92620</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4016,10 +3941,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>700344</v>
+        <v>700243</v>
       </c>
       <c r="R33" t="n">
-        <v>7114301</v>
+        <v>7114171</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4051,7 +3976,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4061,7 +3986,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4092,45 +4017,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126864706</v>
+        <v>126864680</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>700145</v>
+        <v>700363</v>
       </c>
       <c r="R34" t="n">
-        <v>7114540</v>
+        <v>7114127</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4177,12 +4102,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4193,32 +4118,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126865556</v>
+        <v>126868126</v>
       </c>
       <c r="B35" t="n">
-        <v>98448</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4228,10 +4153,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>700304</v>
+        <v>700245</v>
       </c>
       <c r="R35" t="n">
-        <v>7114364</v>
+        <v>7114154</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4261,11 +4186,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4274,16 +4209,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4294,45 +4244,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126862654</v>
+        <v>126868129</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>80468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>700337</v>
+        <v>700245</v>
       </c>
       <c r="R36" t="n">
-        <v>7114304</v>
+        <v>7114154</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4362,11 +4312,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4375,16 +4335,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4395,57 +4370,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126864703</v>
+        <v>126868122</v>
       </c>
       <c r="B37" t="n">
-        <v>98448</v>
+        <v>4775</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>700315</v>
+        <v>700332</v>
       </c>
       <c r="R37" t="n">
-        <v>7114347</v>
+        <v>7114038</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4475,30 +4443,59 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4509,45 +4506,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126864698</v>
+        <v>126868134</v>
       </c>
       <c r="B38" t="n">
-        <v>91330</v>
+        <v>4775</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>700320</v>
+        <v>700186</v>
       </c>
       <c r="R38" t="n">
-        <v>7114182</v>
+        <v>7114499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4577,11 +4579,21 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4590,16 +4602,36 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4610,45 +4642,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126865578</v>
+        <v>126868157</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>41138</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>102498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Silverfläckspraktmal</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Denisia stroemella</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fabricius, 1779)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>700147</v>
+        <v>700300</v>
       </c>
       <c r="R39" t="n">
-        <v>7114536</v>
+        <v>7114175</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,9 +4715,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4695,12 +4742,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4711,45 +4758,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126865563</v>
+        <v>126864729</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>58327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700297</v>
+        <v>700152</v>
       </c>
       <c r="R40" t="n">
-        <v>7114112</v>
+        <v>7114491</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,7 +4856,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4812,57 +4867,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126864700</v>
+        <v>126863285</v>
       </c>
       <c r="B41" t="n">
-        <v>98448</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>700265</v>
+        <v>700344</v>
       </c>
       <c r="R41" t="n">
-        <v>7114403</v>
+        <v>7114335</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,19 +4946,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4929,7 +4971,7 @@
         <v>126868146</v>
       </c>
       <c r="B42" t="n">
-        <v>41365</v>
+        <v>41601</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5031,7 +5073,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5042,48 +5084,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126867882</v>
+        <v>126856078</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>99035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700181</v>
+        <v>700180</v>
       </c>
       <c r="R43" t="n">
-        <v>7114498</v>
+        <v>7114405</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5110,9 +5152,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5127,12 +5179,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5143,32 +5195,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126865569</v>
+        <v>126864706</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>99035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5178,10 +5230,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>700198</v>
+        <v>700145</v>
       </c>
       <c r="R44" t="n">
-        <v>7114523</v>
+        <v>7114540</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5233,7 +5285,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5244,32 +5296,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126864733</v>
+        <v>126864707</v>
       </c>
       <c r="B45" t="n">
-        <v>98448</v>
+        <v>99035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5279,10 +5331,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>700324</v>
+        <v>700183</v>
       </c>
       <c r="R45" t="n">
-        <v>7114108</v>
+        <v>7114417</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5334,7 +5386,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5345,10 +5397,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126868134</v>
+        <v>126864746</v>
       </c>
       <c r="B46" t="n">
-        <v>4773</v>
+        <v>99035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5356,39 +5408,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700186</v>
+        <v>700240</v>
       </c>
       <c r="R46" t="n">
-        <v>7114499</v>
+        <v>7114242</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5418,21 +5465,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5441,36 +5478,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5481,48 +5498,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126854059</v>
+        <v>126864747</v>
       </c>
       <c r="B47" t="n">
-        <v>91330</v>
+        <v>99035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lappmyran, Lappmyran, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700098</v>
+        <v>700218</v>
       </c>
       <c r="R47" t="n">
-        <v>7114648</v>
+        <v>7114260</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5549,19 +5566,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,12 +5583,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5592,10 +5599,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126864746</v>
+        <v>126864748</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>99035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5627,10 +5634,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>700240</v>
+        <v>700220</v>
       </c>
       <c r="R48" t="n">
-        <v>7114242</v>
+        <v>7114448</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5693,10 +5700,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126868129</v>
+        <v>126864750</v>
       </c>
       <c r="B49" t="n">
-        <v>80157</v>
+        <v>99035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5704,21 +5711,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5728,10 +5735,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700245</v>
+        <v>700151</v>
       </c>
       <c r="R49" t="n">
-        <v>7114154</v>
+        <v>7114492</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,21 +5768,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5784,31 +5781,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5819,45 +5801,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126863285</v>
+        <v>126864751</v>
       </c>
       <c r="B50" t="n">
-        <v>57821</v>
+        <v>99035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>700344</v>
+        <v>700307</v>
       </c>
       <c r="R50" t="n">
-        <v>7114335</v>
+        <v>7114295</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,12 +5886,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5920,32 +5902,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126864738</v>
+        <v>126865575</v>
       </c>
       <c r="B51" t="n">
-        <v>98448</v>
+        <v>99035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5955,10 +5937,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>700299</v>
+        <v>700236</v>
       </c>
       <c r="R51" t="n">
-        <v>7114327</v>
+        <v>7114234</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6010,7 +5992,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6021,32 +6003,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126865558</v>
+        <v>126865578</v>
       </c>
       <c r="B52" t="n">
-        <v>98448</v>
+        <v>99035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6056,10 +6038,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>700326</v>
+        <v>700147</v>
       </c>
       <c r="R52" t="n">
-        <v>7114352</v>
+        <v>7114536</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,7 +6093,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6122,45 +6104,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126862656</v>
+        <v>126865555</v>
       </c>
       <c r="B53" t="n">
-        <v>98448</v>
+        <v>99022</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>700320</v>
+        <v>700217</v>
       </c>
       <c r="R53" t="n">
-        <v>7114171</v>
+        <v>7114256</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6207,12 +6189,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6223,57 +6205,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126864704</v>
+        <v>126867856</v>
       </c>
       <c r="B54" t="n">
-        <v>98448</v>
+        <v>99022</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>700273</v>
+        <v>700211</v>
       </c>
       <c r="R54" t="n">
-        <v>7114229</v>
+        <v>7114265</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6320,12 +6290,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6336,10 +6306,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126864734</v>
+        <v>126851272</v>
       </c>
       <c r="B55" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6364,24 +6334,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>700263</v>
+        <v>700310</v>
       </c>
       <c r="R55" t="n">
-        <v>7114387</v>
+        <v>7114176</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6408,9 +6374,19 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6425,12 +6401,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>kristina stenmarck</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6441,45 +6417,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126864708</v>
+        <v>126862630</v>
       </c>
       <c r="B56" t="n">
-        <v>92620</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>700253</v>
+        <v>700326</v>
       </c>
       <c r="R56" t="n">
-        <v>7114409</v>
+        <v>7114161</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6520,18 +6496,19 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6542,32 +6519,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126864680</v>
+        <v>126862651</v>
       </c>
       <c r="B57" t="n">
-        <v>80121</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6577,10 +6554,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>700363</v>
+        <v>700266</v>
       </c>
       <c r="R57" t="n">
-        <v>7114127</v>
+        <v>7114350</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6627,12 +6604,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6643,10 +6620,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126865564</v>
+        <v>126862652</v>
       </c>
       <c r="B58" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6674,14 +6651,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>700282</v>
+        <v>700336</v>
       </c>
       <c r="R58" t="n">
-        <v>7114135</v>
+        <v>7114339</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6728,12 +6705,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6744,10 +6721,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126865567</v>
+        <v>126862653</v>
       </c>
       <c r="B59" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6775,14 +6752,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>700281</v>
+        <v>700319</v>
       </c>
       <c r="R59" t="n">
-        <v>7114196</v>
+        <v>7114336</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6829,12 +6806,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6845,10 +6822,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126862657</v>
+        <v>126862654</v>
       </c>
       <c r="B60" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6880,10 +6857,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>700359</v>
+        <v>700337</v>
       </c>
       <c r="R60" t="n">
-        <v>7114097</v>
+        <v>7114304</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6946,10 +6923,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126863304</v>
+        <v>126862656</v>
       </c>
       <c r="B61" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6981,10 +6958,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>700323</v>
+        <v>700320</v>
       </c>
       <c r="R61" t="n">
-        <v>7114164</v>
+        <v>7114171</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7031,12 +7008,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7047,32 +7024,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126864687</v>
+        <v>126862657</v>
       </c>
       <c r="B62" t="n">
-        <v>82859</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7082,10 +7059,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>700348</v>
+        <v>700359</v>
       </c>
       <c r="R62" t="n">
-        <v>7114044</v>
+        <v>7114097</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7126,19 +7103,18 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7149,45 +7125,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126864724</v>
+        <v>126863301</v>
       </c>
       <c r="B63" t="n">
-        <v>79042</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>700243</v>
+        <v>700307</v>
       </c>
       <c r="R63" t="n">
-        <v>7114142</v>
+        <v>7114151</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7234,12 +7210,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7250,45 +7226,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126864719</v>
+        <v>126863302</v>
       </c>
       <c r="B64" t="n">
-        <v>98469</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>700137</v>
+        <v>700313</v>
       </c>
       <c r="R64" t="n">
-        <v>7114498</v>
+        <v>7114199</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7335,12 +7311,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7351,10 +7327,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126864713</v>
+        <v>126863303</v>
       </c>
       <c r="B65" t="n">
-        <v>91688</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7362,37 +7338,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>700335</v>
+        <v>700301</v>
       </c>
       <c r="R65" t="n">
-        <v>7114031</v>
+        <v>7114212</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7433,19 +7406,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7456,48 +7428,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126851658</v>
+        <v>126863304</v>
       </c>
       <c r="B66" t="n">
-        <v>80121</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>700243</v>
+        <v>700323</v>
       </c>
       <c r="R66" t="n">
-        <v>7114171</v>
+        <v>7114164</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7524,19 +7496,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:37</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7551,12 +7513,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7567,45 +7529,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126864720</v>
+        <v>126864683</v>
       </c>
       <c r="B67" t="n">
-        <v>80025</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lillgodberget, Vb</t>
+          <t>Lillgoberget, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>700382</v>
+        <v>700345</v>
       </c>
       <c r="R67" t="n">
-        <v>7114108</v>
+        <v>7114314</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7640,6 +7602,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7652,12 +7619,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alexandra Astafourova</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7668,10 +7635,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126864702</v>
+        <v>126864699</v>
       </c>
       <c r="B68" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7706,7 +7673,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -7715,10 +7686,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>700301</v>
+        <v>700344</v>
       </c>
       <c r="R68" t="n">
-        <v>7114357</v>
+        <v>7114307</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7782,10 +7753,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126864683</v>
+        <v>126864700</v>
       </c>
       <c r="B69" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7810,17 +7781,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>700345</v>
+        <v>700265</v>
       </c>
       <c r="R69" t="n">
-        <v>7114314</v>
+        <v>7114403</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7855,29 +7838,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Alexandra Astafourova</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7888,10 +7867,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126862630</v>
+        <v>126864701</v>
       </c>
       <c r="B70" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7916,17 +7895,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>700326</v>
+        <v>700283</v>
       </c>
       <c r="R70" t="n">
-        <v>7114161</v>
+        <v>7114393</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7974,12 +7965,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Heggestad, Torbjörn Söderquist, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7990,10 +7981,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126864736</v>
+        <v>126864702</v>
       </c>
       <c r="B71" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8018,8 +8009,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -8029,10 +8028,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>700346</v>
+        <v>700301</v>
       </c>
       <c r="R71" t="n">
-        <v>7114313</v>
+        <v>7114357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8085,7 +8084,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8096,45 +8095,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126865572</v>
+        <v>126864703</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700229</v>
+        <v>700315</v>
       </c>
       <c r="R72" t="n">
-        <v>7114231</v>
+        <v>7114347</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8175,6 +8186,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8186,7 +8198,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Anders Heggestad, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8197,10 +8209,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126867860</v>
+        <v>126864704</v>
       </c>
       <c r="B73" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8227,7 +8239,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8244,10 +8256,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700311</v>
+        <v>700273</v>
       </c>
       <c r="R73" t="n">
-        <v>7114124</v>
+        <v>7114229</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8288,19 +8300,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8311,10 +8322,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126865566</v>
+        <v>126864733</v>
       </c>
       <c r="B74" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8346,10 +8357,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700281</v>
+        <v>700324</v>
       </c>
       <c r="R74" t="n">
-        <v>7114184</v>
+        <v>7114108</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8401,7 +8412,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8412,10 +8423,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126865557</v>
+        <v>126864734</v>
       </c>
       <c r="B75" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8440,17 +8451,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700328</v>
+        <v>700263</v>
       </c>
       <c r="R75" t="n">
-        <v>7114346</v>
+        <v>7114387</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8502,7 +8517,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Klas Magnusson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Jennica Andersson, Alva Danielsson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8513,10 +8528,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126865562</v>
+        <v>126864735</v>
       </c>
       <c r="B76" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8548,10 +8563,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700345</v>
+        <v>700291</v>
       </c>
       <c r="R76" t="n">
-        <v>7114076</v>
+        <v>7114325</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8603,7 +8618,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8614,45 +8629,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126868139</v>
+        <v>126864736</v>
       </c>
       <c r="B77" t="n">
-        <v>96573</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700112</v>
+        <v>700346</v>
       </c>
       <c r="R77" t="n">
-        <v>7114619</v>
+        <v>7114313</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8682,39 +8701,30 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Elke Blöhbaum, Alva Danielsson, Jennica Andersson, kristina stenmarck, Klas Magnusson</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8725,48 +8735,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126856511</v>
+        <v>126864737</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stor-Sandsjön, Stor-Sandsjön, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700252</v>
+        <v>700304</v>
       </c>
       <c r="R78" t="n">
-        <v>7114157</v>
+        <v>7114381</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8793,19 +8803,9 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8820,12 +8820,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>kristina stenmarck</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8836,53 +8836,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126864729</v>
+        <v>126864738</v>
       </c>
       <c r="B79" t="n">
-        <v>58031</v>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700152</v>
+        <v>700299</v>
       </c>
       <c r="R79" t="n">
-        <v>7114491</v>
+        <v>7114327</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8934,7 +8926,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8945,10 +8937,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126867870</v>
+        <v>126864739</v>
       </c>
       <c r="B80" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8973,17 +8965,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700316</v>
+        <v>700286</v>
       </c>
       <c r="R80" t="n">
-        <v>7114065</v>
+        <v>7114214</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9030,12 +9026,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9046,10 +9042,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126864737</v>
+        <v>126864740</v>
       </c>
       <c r="B81" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9081,10 +9077,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700304</v>
+        <v>700290</v>
       </c>
       <c r="R81" t="n">
-        <v>7114381</v>
+        <v>7114228</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9147,10 +9143,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126867872</v>
+        <v>126864741</v>
       </c>
       <c r="B82" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9175,17 +9171,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700320</v>
+        <v>700313</v>
       </c>
       <c r="R82" t="n">
-        <v>7114336</v>
+        <v>7114166</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9232,12 +9232,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9248,10 +9248,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126864741</v>
+        <v>126865556</v>
       </c>
       <c r="B83" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9276,21 +9276,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700313</v>
+        <v>700304</v>
       </c>
       <c r="R83" t="n">
-        <v>7114166</v>
+        <v>7114364</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9342,7 +9338,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Klas Magnusson, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum, kristina stenmarck, Jennica Andersson</t>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9353,10 +9349,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126862652</v>
+        <v>126865557</v>
       </c>
       <c r="B84" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9384,14 +9380,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lillgoberget, Vb</t>
+          <t>Lillgodberget, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700336</v>
+        <v>700328</v>
       </c>
       <c r="R84" t="n">
-        <v>7114339</v>
+        <v>7114346</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9438,15 +9434,2609 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126865558</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>700326</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7114352</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126865559</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>700330</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7114328</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126865562</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>700345</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7114076</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126865563</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>700297</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7114112</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126865564</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>700282</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7114135</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126865566</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>700281</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7114184</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126865567</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>700281</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7114196</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126865568</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>700363</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7114098</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126867858</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>700318</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7114179</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126867860</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>700311</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7114124</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126867862</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>700364</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7114084</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126867869</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>700339</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7114086</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126867870</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>700316</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7114065</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126867871</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>700323</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7114124</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>126867872</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>700320</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7114336</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126868151</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>700306</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7114337</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>126868144</v>
+      </c>
+      <c r="B101" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>700167</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7114511</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>122746406</v>
+      </c>
+      <c r="B102" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Rödåmyrbrånet S, Vb</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>700361</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7114037</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>126864719</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>700137</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7114498</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>126865554</v>
+      </c>
+      <c r="B104" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>700221</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7114245</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Jennica Andersson, Anders Heggestad, Liam Sebestyén, kristina stenmarck, Klas Magnusson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>126867847</v>
+      </c>
+      <c r="B105" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>700230</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7114216</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>126868161</v>
+      </c>
+      <c r="B106" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>700362</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7114025</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, kristina stenmarck, Jennica Andersson, Alva Danielsson, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>126862629</v>
+      </c>
+      <c r="B107" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Lillgoberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>700301</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7114163</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
+      <c r="AX107" t="inlineStr">
         <is>
           <t>Liam Sebestyén, Roger Adolfsson, Alexandra Astafourova, Torbjörn Söderquist, Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY84" t="inlineStr">
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>126864715</v>
+      </c>
+      <c r="B108" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>700390</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7114130</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>126864720</v>
+      </c>
+      <c r="B109" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Lillgodberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>700382</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7114108</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Klas Magnusson, Jennica Andersson, kristina stenmarck, Liam Sebestyén, Anders Heggestad, Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -4645,7 +4645,7 @@
         <v>126868157</v>
       </c>
       <c r="B39" t="n">
-        <v>41138</v>
+        <v>41143</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 31193-2024 artfynd.xlsx
+++ b/artfynd/A 31193-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AZ109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864710</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864711</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868149</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126854059</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862588</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864698</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864714</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864715</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864687</t>
         </is>
       </c>
     </row>
@@ -1725,6 +1775,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864713</t>
         </is>
       </c>
     </row>
@@ -1843,6 +1898,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868132</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1954,6 +2014,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868136</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868139</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2176,6 +2246,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126852356</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863311</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2378,6 +2458,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864691</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2479,6 +2564,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864708</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2590,6 +2680,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126856511</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2691,6 +2786,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863310</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864686</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2893,6 +2998,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864705</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2994,6 +3104,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864744</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3095,6 +3210,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864745</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3196,6 +3316,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865569</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3297,6 +3422,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865570</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3398,6 +3528,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865571</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3499,6 +3634,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865572</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3600,6 +3740,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867880</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3701,6 +3846,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867881</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3802,6 +3952,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867882</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3903,6 +4058,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864724</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4004,6 +4164,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864725</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4105,6 +4270,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864720</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4216,6 +4386,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126851584</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4317,6 +4492,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864680</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4443,6 +4623,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868126</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4569,6 +4754,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868129</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4705,6 +4895,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868122</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4841,6 +5036,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868134</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4957,6 +5157,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868157</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5066,6 +5271,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864729</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5167,6 +5377,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863285</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5283,6 +5498,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868146</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5394,6 +5614,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126856078</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5495,6 +5720,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864706</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5596,6 +5826,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864707</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5697,6 +5932,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864746</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5798,6 +6038,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864747</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5899,6 +6144,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864748</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6000,6 +6250,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864750</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6101,6 +6356,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864751</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6202,6 +6462,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865575</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6303,6 +6568,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865578</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6404,6 +6674,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865555</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6505,6 +6780,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867856</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6616,6 +6896,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126851272</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6718,6 +7003,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862630</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6819,6 +7109,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862651</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6920,6 +7215,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862652</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7021,6 +7321,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862653</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7122,6 +7427,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862654</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7223,6 +7533,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862656</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7324,6 +7639,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862657</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7425,6 +7745,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863301</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7526,6 +7851,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863302</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7627,6 +7957,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863303</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7728,6 +8063,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126863304</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7834,6 +8174,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864683</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7952,6 +8297,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864699</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8066,6 +8416,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864700</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8180,6 +8535,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864701</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8294,6 +8654,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864702</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8408,6 +8773,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864703</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8521,6 +8891,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864704</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8622,6 +8997,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864733</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8727,6 +9107,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864734</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8826,6 +9211,11 @@
       <c r="AY78" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864735</t>
         </is>
       </c>
     </row>
@@ -8934,6 +9324,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864736</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9035,6 +9430,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864737</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9136,6 +9536,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864738</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9241,6 +9646,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864739</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9342,6 +9752,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864740</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9447,6 +9862,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864741</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9548,6 +9968,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865556</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9649,6 +10074,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865557</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9750,6 +10180,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865558</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9851,6 +10286,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865559</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9952,6 +10392,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865562</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10053,6 +10498,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865563</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10154,6 +10604,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865564</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10255,6 +10710,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865566</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10356,6 +10816,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865567</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10457,6 +10922,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865568</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10571,6 +11041,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867858</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10685,6 +11160,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867860</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10799,6 +11279,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867862</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10900,6 +11385,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867869</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11001,6 +11491,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867870</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11102,6 +11597,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867871</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11203,6 +11703,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867872</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11314,6 +11819,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868151</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11425,6 +11935,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868144</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11526,6 +12041,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746406</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11627,6 +12147,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126864719</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11728,6 +12253,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126865554</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11829,6 +12359,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126867847</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11940,6 +12475,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126868161</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12041,8 +12581,123 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126862629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>